--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F031A4B9-18A7-49AD-930A-50D4B413A350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC5BF65-EA33-4282-9FED-9F92A4F5ED39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="7" activeTab="16" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="864" firstSheet="9" activeTab="11" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="84">
   <si>
     <t>Red Bull Racing</t>
   </si>
@@ -701,9 +701,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -774,7 +774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -845,7 +845,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -916,7 +916,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -987,7 +987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1495,9 +1495,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1574,7 +1574,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -2265,7 +2265,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -2329,7 +2329,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -2691,7 +2691,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -2922,7 +2922,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -3267,10 +3267,10 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Y24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:Y22"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -3347,7 +3347,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -3819,30 +3819,74 @@
       <c r="C8" s="1">
         <v>17.399999999999999</v>
       </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-    </row>
-    <row r="9" spans="1:25" ht="15.75">
+      <c r="D8" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="F8" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>6</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="K8" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="L8" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="M8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="N8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="P8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R8" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="S8" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="T8" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="U8" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="V8" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="W8" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="X8" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3919,12 +3963,16 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="B10" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
       <c r="D10" s="1">
         <v>16.8</v>
       </c>
@@ -3992,7 +4040,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4069,731 +4117,767 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E12" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="F12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G12" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I12" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="J12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="M12" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="N12" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="O12" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="R12" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="S12" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="T12" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="U12" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V12" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="W12" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="X12" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="15.4">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1">
+        <v>13.1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>11.9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>11.3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10.1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J13" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K13" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="L13" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="M13" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="N13" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="P13" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="R13" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S13" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="T13" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="U13" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="V13" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="W13" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="X13" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="15.4">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="C14" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F14" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G14" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I14" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J14" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="L14" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="M14" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="O14" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="P14" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R14" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="S14" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T14" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="U14" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="V14" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="W14" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="X14" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15.4">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I15" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="J15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="M15" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="N15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="O15" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="P15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="R15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="S15" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="T15" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="U15" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="V15" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="W15" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="X15" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="15.4">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="F16" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="H16" s="1">
+        <v>6</v>
+      </c>
+      <c r="I16" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>6</v>
+      </c>
+      <c r="K16" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="L16" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="M16" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="O16" s="1">
+        <v>9</v>
+      </c>
+      <c r="P16" s="1">
         <v>9.6</v>
       </c>
-      <c r="C12" s="1">
-        <v>9</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-    </row>
-    <row r="13" spans="1:25" ht="15.75">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="1">
+      <c r="Q16" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="R16" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="S16" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="T16" s="1">
+        <v>8</v>
+      </c>
+      <c r="U16" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="V16" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="W16" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="X16" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="15.4">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="C17" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="G17" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H17" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I17" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="J17" s="1">
+        <v>7</v>
+      </c>
+      <c r="K17" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="M17" s="1">
+        <v>6</v>
+      </c>
+      <c r="N17" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="O17" s="1">
+        <v>6</v>
+      </c>
+      <c r="P17" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="R17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="S17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="T17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="U17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="V17" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="W17" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="X17" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="15.4">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="C18" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G18" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>5</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M18" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="N18" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="O18" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="P18" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="Q18" s="1">
         <v>8.1</v>
       </c>
-      <c r="C13" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="D13" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E13" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="F13" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="G13" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I13" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="J13" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="K13" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="M13" s="1">
+      <c r="R18" s="1">
         <v>7.9</v>
       </c>
-      <c r="N13" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="O13" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="P13" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>10.3</v>
-      </c>
-      <c r="R13" s="1">
-        <v>10.5</v>
-      </c>
-      <c r="S13" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="T13" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="U13" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="V13" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="W13" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="X13" s="1">
+      <c r="S18" s="1">
         <v>7.3</v>
       </c>
-      <c r="Y13" s="1">
+      <c r="T18" s="1">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" ht="15.75">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1">
-        <v>13.1</v>
-      </c>
-      <c r="C14" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="D14" s="1">
-        <v>11.9</v>
-      </c>
-      <c r="E14" s="1">
-        <v>11.3</v>
-      </c>
-      <c r="F14" s="1">
-        <v>10.7</v>
-      </c>
-      <c r="G14" s="1">
-        <v>10.1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="I14" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="J14" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K14" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="L14" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="M14" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="N14" s="1">
+      <c r="U18" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="V18" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="W18" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X18" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="15.4">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="D19" s="1">
+        <v>6</v>
+      </c>
+      <c r="E19" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>5</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="1:25" ht="15.4">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="K20" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="M20" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="N20" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="O20" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="P20" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="R20" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="S20" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="T20" s="1">
         <v>7.1</v>
       </c>
-      <c r="O14" s="1">
+      <c r="U20" s="1">
         <v>6.5</v>
       </c>
-      <c r="P14" s="1">
+      <c r="V20" s="1">
         <v>5.9</v>
       </c>
-      <c r="Q14" s="1">
+      <c r="W20" s="1">
         <v>5.7</v>
       </c>
-      <c r="R14" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="S14" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="T14" s="1">
+      <c r="X20" s="1">
         <v>6.3</v>
       </c>
-      <c r="U14" s="1">
+      <c r="Y20" s="1">
         <v>6.9</v>
       </c>
-      <c r="V14" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="W14" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="X14" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="15.75">
-      <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="D15" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="F15" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="G15" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="H15" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="I15" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="J15" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="K15" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="L15" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="M15" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="N15" s="1">
-        <v>8.9</v>
-      </c>
-      <c r="O15" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="P15" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="R15" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="S15" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="T15" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="U15" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="V15" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="W15" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="X15" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="15.75">
-      <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="C16" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="D16" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="E16" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="F16" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="G16" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="H16" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I16" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="J16" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="K16" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="L16" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="M16" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="N16" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="O16" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="P16" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="R16" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="S16" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="T16" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="U16" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="V16" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="W16" s="1">
-        <v>8.9</v>
-      </c>
-      <c r="X16" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="15.75">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="C17" s="1">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="E17" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="F17" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="G17" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="H17" s="1">
+    </row>
+    <row r="21" spans="1:25" ht="15.4">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="1">
         <v>6</v>
       </c>
-      <c r="I17" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="J17" s="1">
-        <v>6</v>
-      </c>
-      <c r="K17" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="L17" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="M17" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="N17" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="O17" s="1">
-        <v>9</v>
-      </c>
-      <c r="P17" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="R17" s="1">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="S17" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="T17" s="1">
-        <v>8</v>
-      </c>
-      <c r="U17" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="V17" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="W17" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="X17" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="15.75">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="1">
-        <v>11.8</v>
-      </c>
-      <c r="C18" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="D18" s="1">
-        <v>10.6</v>
-      </c>
-      <c r="E18" s="1">
-        <v>10</v>
-      </c>
-      <c r="F18" s="1">
-        <v>9.4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H18" s="1">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="I18" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="J18" s="1">
-        <v>7</v>
-      </c>
-      <c r="K18" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="L18" s="1">
-        <v>5.8</v>
-      </c>
-      <c r="M18" s="1">
-        <v>6</v>
-      </c>
-      <c r="N18" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="O18" s="1">
-        <v>6</v>
-      </c>
-      <c r="P18" s="1">
+      <c r="C21" s="1">
         <v>5.4</v>
       </c>
-      <c r="Q18" s="1">
+      <c r="D21" s="1">
         <v>4.8</v>
-      </c>
-      <c r="R18" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="S18" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="T18" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="U18" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="V18" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="W18" s="1">
-        <v>5.3</v>
-      </c>
-      <c r="X18" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="15.75">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="1">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="C19" s="1">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="D19" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="E19" s="1">
-        <v>7</v>
-      </c>
-      <c r="F19" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="G19" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="H19" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="I19" s="1">
-        <v>5</v>
-      </c>
-      <c r="J19" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="K19" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L19" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="M19" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="N19" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="O19" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="P19" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="R19" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="S19" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="T19" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="U19" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="V19" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="W19" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="X19" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Y19" s="1">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" ht="15.75">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="D20" s="1">
-        <v>6</v>
-      </c>
-      <c r="E20" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="F20" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="G20" s="1">
-        <v>5</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-    </row>
-    <row r="21" spans="1:25" ht="15.75">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="C21" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="D21" s="1">
-        <v>5</v>
       </c>
       <c r="E21" s="1">
         <v>4.5</v>
       </c>
       <c r="F21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M21" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="G21" s="1">
+      <c r="N21" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O21" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="P21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R21" s="1">
         <v>5.7</v>
       </c>
-      <c r="H21" s="1">
+      <c r="S21" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="T21" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="U21" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="V21" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="W21" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="X21" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="Y21" s="1">
         <v>5.5</v>
       </c>
-      <c r="I21" s="1">
-        <v>5.3</v>
-      </c>
-      <c r="J21" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="K21" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="L21" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="M21" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="N21" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="O21" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="P21" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="R21" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="S21" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="T21" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="U21" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="V21" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="W21" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="X21" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="15.75">
+    </row>
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="E22" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="F22" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>6.6</v>
-      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
       <c r="H22" s="1">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="I22" s="1">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J22" s="1">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K22" s="1">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="L22" s="1">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M22" s="1">
-        <v>4.5</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="N22" s="1">
         <v>4.5</v>
@@ -4805,172 +4889,30 @@
         <v>4.5</v>
       </c>
       <c r="Q22" s="1">
-        <v>5.0999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="R22" s="1">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="S22" s="1">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="T22" s="1">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="U22" s="1">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="V22" s="1">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
       <c r="W22" s="1">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="X22" s="1">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y22" s="1">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" ht="15.75">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" s="1">
-        <v>6</v>
-      </c>
-      <c r="C23" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="D23" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="E23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="F23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="G23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="H23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="J23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="K23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M23" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="N23" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="O23" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="P23" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="R23" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="S23" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="T23" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="U23" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="V23" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="W23" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="X23" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="Y23" s="1">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" ht="15.75">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="J24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="K24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L24" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="M24" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="N24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="O24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="P24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="R24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="S24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="T24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="U24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="V24" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="W24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="X24" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Y24" s="1">
         <v>4.5</v>
       </c>
     </row>
@@ -4985,9 +4927,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -5193,7 +5135,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>10</v>
@@ -5363,7 +5305,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>5.9</v>
@@ -5389,9 +5331,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -5462,7 +5404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -5533,7 +5475,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -5604,7 +5546,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -5675,7 +5617,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5746,7 +5688,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -5817,7 +5759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -5888,7 +5830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -5959,7 +5901,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -6030,7 +5972,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -6101,7 +6043,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -6172,7 +6114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -6243,7 +6185,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -6314,7 +6256,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -6355,7 +6297,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -6426,7 +6368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -6497,7 +6439,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -6568,7 +6510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -6605,7 +6547,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>42</v>
       </c>
@@ -6676,7 +6618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -6747,7 +6689,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -6794,7 +6736,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>47</v>
       </c>
@@ -6865,7 +6807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -6947,9 +6889,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -7026,7 +6968,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7103,7 +7045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -7180,7 +7122,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -7257,7 +7199,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -7288,7 +7230,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -7365,7 +7307,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -7440,7 +7382,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -7517,7 +7459,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -7594,7 +7536,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -7671,7 +7613,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -7704,7 +7646,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -7735,7 +7677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -7808,7 +7750,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -7885,7 +7827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -7926,7 +7868,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -8001,7 +7943,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -8078,7 +8020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -8143,7 +8085,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -8220,7 +8162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -8297,7 +8239,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -8374,7 +8316,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -8451,7 +8393,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -8528,7 +8470,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -8575,7 +8517,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -8632,7 +8574,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -8720,7 +8662,10 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="14.19921875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -10375,13 +10320,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="B1">
         <v>1</v>
       </c>
@@ -10391,11 +10336,8 @@
       <c r="D1">
         <v>3</v>
       </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -10409,7 +10351,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -10423,7 +10365,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -10437,7 +10379,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -10451,7 +10393,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -10465,7 +10407,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -10479,7 +10421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -10493,7 +10435,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -10507,7 +10449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10521,7 +10463,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -10535,7 +10477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -10549,7 +10491,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -10563,7 +10505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -10577,7 +10519,7 @@
         <v>-17</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10591,7 +10533,7 @@
         <v>-14</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -10711,7 +10653,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008844FF-9942-4BA0-9033-82ED2D862880}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
@@ -10990,9 +10932,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -11069,7 +11011,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11146,7 +11088,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -11223,7 +11165,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11300,7 +11242,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11377,7 +11319,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -11454,7 +11396,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -11531,7 +11473,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -11608,7 +11550,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -11685,7 +11627,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -11762,7 +11704,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -11850,7 +11792,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -11926,7 +11868,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -12003,7 +11945,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12080,7 +12022,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -12157,7 +12099,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -12234,7 +12176,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -12311,7 +12253,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -12388,7 +12330,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -12465,7 +12407,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -12542,7 +12484,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -12619,7 +12561,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -12707,7 +12649,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1">
@@ -12921,7 +12863,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="V1:AR11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="22:44">
       <c r="W1">
@@ -12991,7 +12933,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="22:44" ht="15.75">
+    <row r="2" spans="22:44" ht="15.4">
       <c r="V2" t="s">
         <v>0</v>
       </c>
@@ -13062,7 +13004,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="22:44" ht="15.75">
+    <row r="3" spans="22:44" ht="15.4">
       <c r="V3" t="s">
         <v>2</v>
       </c>
@@ -13133,7 +13075,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="22:44" ht="15.75">
+    <row r="4" spans="22:44" ht="15.4">
       <c r="V4" t="s">
         <v>3</v>
       </c>
@@ -13204,7 +13146,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="22:44" ht="15.75">
+    <row r="5" spans="22:44" ht="15.4">
       <c r="V5" t="s">
         <v>4</v>
       </c>
@@ -13275,7 +13217,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="22:44" ht="15.75">
+    <row r="6" spans="22:44" ht="15.4">
       <c r="V6" t="s">
         <v>1</v>
       </c>
@@ -13346,7 +13288,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="22:44" ht="15.75">
+    <row r="7" spans="22:44" ht="15.4">
       <c r="V7" t="s">
         <v>5</v>
       </c>
@@ -13417,7 +13359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="22:44" ht="15.75">
+    <row r="8" spans="22:44" ht="15.4">
       <c r="V8" t="s">
         <v>6</v>
       </c>
@@ -13488,7 +13430,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="22:44" ht="15.75">
+    <row r="9" spans="22:44" ht="15.4">
       <c r="V9" t="s">
         <v>7</v>
       </c>
@@ -13559,7 +13501,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="22:44" ht="15.75">
+    <row r="10" spans="22:44" ht="15.4">
       <c r="V10" t="s">
         <v>9</v>
       </c>
@@ -13630,7 +13572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="22:44" ht="15.75">
+    <row r="11" spans="22:44" ht="15.4">
       <c r="V11" t="s">
         <v>8</v>
       </c>
@@ -13712,7 +13654,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -13788,7 +13730,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -13865,7 +13807,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -13942,7 +13884,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14019,7 +13961,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -14096,7 +14038,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -14173,7 +14115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -14250,7 +14192,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -14327,7 +14269,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -14404,7 +14346,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -14481,7 +14423,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -14569,7 +14511,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="BR1:CP11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="70:94">
       <c r="BS1">
@@ -15425,13 +15367,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="B1">
         <v>1</v>
       </c>
@@ -15441,11 +15383,8 @@
       <c r="D1">
         <v>3</v>
       </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -15459,7 +15398,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -15473,7 +15412,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -15487,7 +15426,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -15501,7 +15440,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15515,7 +15454,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -15529,7 +15468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -15543,7 +15482,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -15557,7 +15496,7 @@
         <v>-4</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -15571,7 +15510,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -15585,7 +15524,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -15610,9 +15549,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1">
@@ -15683,7 +15622,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -15754,7 +15693,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -15825,7 +15764,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -15896,7 +15835,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -15967,7 +15906,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -16038,7 +15977,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -16109,7 +16048,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -16180,7 +16119,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -16251,7 +16190,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -16322,7 +16261,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -16393,7 +16332,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -16464,7 +16403,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -16535,7 +16474,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>47</v>
       </c>
@@ -16606,7 +16545,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -16677,7 +16616,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -16748,7 +16687,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -16819,7 +16758,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -16890,7 +16829,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -16927,7 +16866,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -16968,7 +16907,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -17015,7 +16954,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -17086,7 +17025,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>45</v>
       </c>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BC5BF65-EA33-4282-9FED-9F92A4F5ED39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF69F0-2F79-4E27-976C-C30B83A428A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="864" firstSheet="9" activeTab="11" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="5700" yWindow="675" windowWidth="16200" windowHeight="9307" tabRatio="864" firstSheet="11" activeTab="15" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,12 @@
     <sheet name="2025ConstructorPoints" sheetId="11" r:id="rId7"/>
     <sheet name="2026ConstructorPoints" sheetId="12" r:id="rId8"/>
     <sheet name="2023DriverPrice" sheetId="5" r:id="rId9"/>
-    <sheet name="2024DriverPrice" sheetId="6" r:id="rId10"/>
-    <sheet name="2025DriverPrice" sheetId="7" r:id="rId11"/>
-    <sheet name="2026DriverPrice" sheetId="8" r:id="rId12"/>
-    <sheet name="2023DriverPoints" sheetId="13" r:id="rId13"/>
-    <sheet name="2024DriverPoints" sheetId="14" r:id="rId14"/>
-    <sheet name="2025DriverPoints" sheetId="15" r:id="rId15"/>
+    <sheet name="2023DriverPoints" sheetId="13" r:id="rId10"/>
+    <sheet name="2024DriverPrice" sheetId="6" r:id="rId11"/>
+    <sheet name="2024DriverPoints" sheetId="14" r:id="rId12"/>
+    <sheet name="2025DriverPrice" sheetId="7" r:id="rId13"/>
+    <sheet name="2025DriverPoints" sheetId="15" r:id="rId14"/>
+    <sheet name="2026DriverPrice" sheetId="8" r:id="rId15"/>
     <sheet name="2026DriverPoints" sheetId="16" r:id="rId16"/>
     <sheet name="TEAMCONFIG" sheetId="17" r:id="rId17"/>
   </sheets>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="80">
   <si>
     <t>Red Bull Racing</t>
   </si>
@@ -138,9 +138,6 @@
     <t>Alexander Albon</t>
   </si>
   <si>
-    <t>Fernando Alonzo</t>
-  </si>
-  <si>
     <t>Lance Stroll</t>
   </si>
   <si>
@@ -168,13 +165,7 @@
     <t>Sergio Perez</t>
   </si>
   <si>
-    <t>Valteri Bottas</t>
-  </si>
-  <si>
     <t>Yuki Tsunoda</t>
-  </si>
-  <si>
-    <t>Pierre Gasley</t>
   </si>
   <si>
     <t>Fernando Alonso</t>
@@ -186,9 +177,6 @@
     <t>Kevin Magnussen</t>
   </si>
   <si>
-    <t>Guanyu Zhou</t>
-  </si>
-  <si>
     <t>Valtteri Bottas</t>
   </si>
   <si>
@@ -196,9 +184,6 @@
   </si>
   <si>
     <t>Daniel Ricciardo</t>
-  </si>
-  <si>
-    <t>Valtteri Botas</t>
   </si>
   <si>
     <t>Nyck De Vries</t>
@@ -307,6 +292,9 @@
   </si>
   <si>
     <t>PIA</t>
+  </si>
+  <si>
+    <t>Zhou Guanyu</t>
   </si>
 </sst>
 </file>
@@ -1490,6 +1478,1564 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380C4B9E-1EC8-4446-8DCE-B4EFA581E858}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:W23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>7</v>
+      </c>
+      <c r="H1">
+        <v>8</v>
+      </c>
+      <c r="I1">
+        <v>9</v>
+      </c>
+      <c r="J1">
+        <v>10</v>
+      </c>
+      <c r="K1">
+        <v>11</v>
+      </c>
+      <c r="L1">
+        <v>12</v>
+      </c>
+      <c r="M1">
+        <v>13</v>
+      </c>
+      <c r="N1">
+        <v>14</v>
+      </c>
+      <c r="O1">
+        <v>15</v>
+      </c>
+      <c r="P1">
+        <v>16</v>
+      </c>
+      <c r="Q1">
+        <v>17</v>
+      </c>
+      <c r="R1">
+        <v>18</v>
+      </c>
+      <c r="S1">
+        <v>19</v>
+      </c>
+      <c r="T1">
+        <v>20</v>
+      </c>
+      <c r="U1">
+        <v>21</v>
+      </c>
+      <c r="V1">
+        <v>22</v>
+      </c>
+      <c r="W1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15.4">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1">
+        <v>61</v>
+      </c>
+      <c r="D2" s="1">
+        <v>36</v>
+      </c>
+      <c r="E2" s="1">
+        <v>37</v>
+      </c>
+      <c r="F2" s="1">
+        <v>64</v>
+      </c>
+      <c r="G2" s="1">
+        <v>35</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46</v>
+      </c>
+      <c r="I2" s="1">
+        <v>35</v>
+      </c>
+      <c r="J2" s="1">
+        <v>56</v>
+      </c>
+      <c r="K2" s="1">
+        <v>46</v>
+      </c>
+      <c r="L2" s="1">
+        <v>46</v>
+      </c>
+      <c r="M2" s="1">
+        <v>68</v>
+      </c>
+      <c r="N2" s="1">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1">
+        <v>38</v>
+      </c>
+      <c r="P2" s="1">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1">
+        <v>62</v>
+      </c>
+      <c r="S2" s="1">
+        <v>53</v>
+      </c>
+      <c r="T2" s="1">
+        <v>42</v>
+      </c>
+      <c r="U2" s="1">
+        <v>45</v>
+      </c>
+      <c r="V2" s="1">
+        <v>44</v>
+      </c>
+      <c r="W2" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15.4">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="1">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1">
+        <v>52</v>
+      </c>
+      <c r="E3" s="1">
+        <v>61</v>
+      </c>
+      <c r="F3" s="1">
+        <v>28</v>
+      </c>
+      <c r="G3" s="1">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1">
+        <v>27</v>
+      </c>
+      <c r="I3" s="1">
+        <v>28</v>
+      </c>
+      <c r="J3" s="1">
+        <v>51</v>
+      </c>
+      <c r="K3" s="1">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1">
+        <v>39</v>
+      </c>
+      <c r="M3" s="1">
+        <v>7</v>
+      </c>
+      <c r="N3" s="1">
+        <v>30</v>
+      </c>
+      <c r="O3" s="1">
+        <v>30</v>
+      </c>
+      <c r="P3" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>-11</v>
+      </c>
+      <c r="R3" s="1">
+        <v>-3</v>
+      </c>
+      <c r="S3" s="1">
+        <v>32</v>
+      </c>
+      <c r="T3" s="1">
+        <v>-10</v>
+      </c>
+      <c r="U3" s="1">
+        <v>37</v>
+      </c>
+      <c r="V3" s="1">
+        <v>35</v>
+      </c>
+      <c r="W3" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15.4">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1">
+        <v>24</v>
+      </c>
+      <c r="G4" s="1">
+        <v>28</v>
+      </c>
+      <c r="H4" s="1">
+        <v>39</v>
+      </c>
+      <c r="I4" s="1">
+        <v>23</v>
+      </c>
+      <c r="J4" s="1">
+        <v>31</v>
+      </c>
+      <c r="K4" s="1">
+        <v>25</v>
+      </c>
+      <c r="L4" s="1">
+        <v>20</v>
+      </c>
+      <c r="M4" s="1">
+        <v>32</v>
+      </c>
+      <c r="N4" s="1">
+        <v>29</v>
+      </c>
+      <c r="O4" s="1">
+        <v>17</v>
+      </c>
+      <c r="P4" s="1">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>20</v>
+      </c>
+      <c r="R4" s="1">
+        <v>6</v>
+      </c>
+      <c r="S4" s="1">
+        <v>-4</v>
+      </c>
+      <c r="T4" s="1">
+        <v>41</v>
+      </c>
+      <c r="U4" s="1">
+        <v>13</v>
+      </c>
+      <c r="V4" s="1">
+        <v>26</v>
+      </c>
+      <c r="W4" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.4">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>6</v>
+      </c>
+      <c r="H5" s="1">
+        <v>-2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1">
+        <v>29</v>
+      </c>
+      <c r="K5" s="1">
+        <v>38</v>
+      </c>
+      <c r="L5" s="1">
+        <v>29</v>
+      </c>
+      <c r="M5" s="1">
+        <v>15</v>
+      </c>
+      <c r="N5" s="1">
+        <v>25</v>
+      </c>
+      <c r="O5" s="1">
+        <v>9</v>
+      </c>
+      <c r="P5" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>31</v>
+      </c>
+      <c r="R5" s="1">
+        <v>41</v>
+      </c>
+      <c r="S5" s="1">
+        <v>46</v>
+      </c>
+      <c r="T5" s="1">
+        <v>48</v>
+      </c>
+      <c r="U5" s="1">
+        <v>57</v>
+      </c>
+      <c r="V5" s="1">
+        <v>-14</v>
+      </c>
+      <c r="W5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15.4">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="1">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1">
+        <v>27</v>
+      </c>
+      <c r="F6" s="1">
+        <v>25</v>
+      </c>
+      <c r="G6" s="1">
+        <v>27</v>
+      </c>
+      <c r="H6" s="1">
+        <v>14</v>
+      </c>
+      <c r="I6" s="1">
+        <v>27</v>
+      </c>
+      <c r="J6" s="1">
+        <v>28</v>
+      </c>
+      <c r="K6" s="1">
+        <v>12</v>
+      </c>
+      <c r="L6" s="1">
+        <v>7</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>62</v>
+      </c>
+      <c r="O6" s="1">
+        <v>5</v>
+      </c>
+      <c r="P6" s="1">
+        <v>-1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>16</v>
+      </c>
+      <c r="R6" s="1">
+        <v>25</v>
+      </c>
+      <c r="S6" s="1">
+        <v>-9</v>
+      </c>
+      <c r="T6" s="1">
+        <v>-16</v>
+      </c>
+      <c r="U6" s="1">
+        <v>39</v>
+      </c>
+      <c r="V6" s="1">
+        <v>12</v>
+      </c>
+      <c r="W6" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15.4">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1">
+        <v>12</v>
+      </c>
+      <c r="D7" s="1">
+        <v>8</v>
+      </c>
+      <c r="E7" s="1">
+        <v>21</v>
+      </c>
+      <c r="F7" s="1">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1">
+        <v>19</v>
+      </c>
+      <c r="I7" s="1">
+        <v>22</v>
+      </c>
+      <c r="J7" s="1">
+        <v>31</v>
+      </c>
+      <c r="K7" s="1">
+        <v>4</v>
+      </c>
+      <c r="L7" s="1">
+        <v>12</v>
+      </c>
+      <c r="M7" s="1">
+        <v>-8</v>
+      </c>
+      <c r="N7" s="1">
+        <v>31</v>
+      </c>
+      <c r="O7" s="1">
+        <v>38</v>
+      </c>
+      <c r="P7" s="1">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>18</v>
+      </c>
+      <c r="R7" s="1">
+        <v>-14</v>
+      </c>
+      <c r="S7" s="1">
+        <v>32</v>
+      </c>
+      <c r="T7" s="1">
+        <v>19</v>
+      </c>
+      <c r="U7" s="1">
+        <v>21</v>
+      </c>
+      <c r="V7" s="1">
+        <v>34</v>
+      </c>
+      <c r="W7" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15.4">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1">
+        <v>16</v>
+      </c>
+      <c r="C8" s="1">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1">
+        <v>-7</v>
+      </c>
+      <c r="E8" s="1">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1">
+        <v>28</v>
+      </c>
+      <c r="G8" s="1">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1">
+        <v>31</v>
+      </c>
+      <c r="I8" s="1">
+        <v>-12</v>
+      </c>
+      <c r="J8" s="1">
+        <v>34</v>
+      </c>
+      <c r="K8" s="1">
+        <v>18</v>
+      </c>
+      <c r="L8" s="1">
+        <v>27</v>
+      </c>
+      <c r="M8" s="1">
+        <v>28</v>
+      </c>
+      <c r="N8" s="1">
+        <v>6</v>
+      </c>
+      <c r="O8" s="1">
+        <v>17</v>
+      </c>
+      <c r="P8" s="1">
+        <v>-2</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>14</v>
+      </c>
+      <c r="R8" s="1">
+        <v>37</v>
+      </c>
+      <c r="S8" s="1">
+        <v>25</v>
+      </c>
+      <c r="T8" s="1">
+        <v>18</v>
+      </c>
+      <c r="U8" s="1">
+        <v>1</v>
+      </c>
+      <c r="V8" s="1">
+        <v>14</v>
+      </c>
+      <c r="W8" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.4">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-11</v>
+      </c>
+      <c r="C9" s="1">
+        <v>27</v>
+      </c>
+      <c r="D9" s="1">
+        <v>-15</v>
+      </c>
+      <c r="E9" s="1">
+        <v>29</v>
+      </c>
+      <c r="F9" s="1">
+        <v>16</v>
+      </c>
+      <c r="G9" s="1">
+        <v>16</v>
+      </c>
+      <c r="H9" s="1">
+        <v>14</v>
+      </c>
+      <c r="I9" s="1">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1">
+        <v>32</v>
+      </c>
+      <c r="K9" s="1">
+        <v>6</v>
+      </c>
+      <c r="L9" s="1">
+        <v>12</v>
+      </c>
+      <c r="M9" s="1">
+        <v>26</v>
+      </c>
+      <c r="N9" s="1">
+        <v>-7</v>
+      </c>
+      <c r="O9" s="1">
+        <v>24</v>
+      </c>
+      <c r="P9" s="1">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>22</v>
+      </c>
+      <c r="R9" s="1">
+        <v>22</v>
+      </c>
+      <c r="S9" s="1">
+        <v>-10</v>
+      </c>
+      <c r="T9" s="1">
+        <v>24</v>
+      </c>
+      <c r="U9" s="1">
+        <v>-3</v>
+      </c>
+      <c r="V9" s="1">
+        <v>41</v>
+      </c>
+      <c r="W9" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15.4">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-16</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1">
+        <v>3</v>
+      </c>
+      <c r="J10" s="1">
+        <v>20</v>
+      </c>
+      <c r="K10" s="1">
+        <v>20</v>
+      </c>
+      <c r="L10" s="1">
+        <v>18</v>
+      </c>
+      <c r="M10" s="1">
+        <v>-7</v>
+      </c>
+      <c r="N10" s="1">
+        <v>18</v>
+      </c>
+      <c r="O10" s="1">
+        <v>15</v>
+      </c>
+      <c r="P10" s="1">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>35</v>
+      </c>
+      <c r="R10" s="1">
+        <v>56</v>
+      </c>
+      <c r="S10" s="1">
+        <v>-20</v>
+      </c>
+      <c r="T10" s="1">
+        <v>14</v>
+      </c>
+      <c r="U10" s="1">
+        <v>3</v>
+      </c>
+      <c r="V10" s="1">
+        <v>39</v>
+      </c>
+      <c r="W10" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15.4">
+      <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-14</v>
+      </c>
+      <c r="D11" s="1">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1">
+        <v>18</v>
+      </c>
+      <c r="F11" s="1">
+        <v>12</v>
+      </c>
+      <c r="G11" s="1">
+        <v>-17</v>
+      </c>
+      <c r="H11" s="1">
+        <v>16</v>
+      </c>
+      <c r="I11" s="1">
+        <v>14</v>
+      </c>
+      <c r="J11" s="1">
+        <v>25</v>
+      </c>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>12</v>
+      </c>
+      <c r="N11" s="1">
+        <v>10</v>
+      </c>
+      <c r="O11" s="1">
+        <v>7</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>-14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>17</v>
+      </c>
+      <c r="S11" s="1">
+        <v>10</v>
+      </c>
+      <c r="T11" s="1">
+        <v>8</v>
+      </c>
+      <c r="U11" s="1">
+        <v>28</v>
+      </c>
+      <c r="V11" s="1">
+        <v>39</v>
+      </c>
+      <c r="W11" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15.4">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="1">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1">
+        <v>10</v>
+      </c>
+      <c r="H12" s="1">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1">
+        <v>8</v>
+      </c>
+      <c r="J12" s="1">
+        <v>7</v>
+      </c>
+      <c r="K12" s="1">
+        <v>-3</v>
+      </c>
+      <c r="L12" s="1">
+        <v>-19</v>
+      </c>
+      <c r="M12" s="1">
+        <v>17</v>
+      </c>
+      <c r="N12" s="1">
+        <v>39</v>
+      </c>
+      <c r="O12" s="1">
+        <v>3</v>
+      </c>
+      <c r="P12" s="1">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>7</v>
+      </c>
+      <c r="R12" s="1">
+        <v>11</v>
+      </c>
+      <c r="S12" s="1">
+        <v>22</v>
+      </c>
+      <c r="T12" s="1">
+        <v>10</v>
+      </c>
+      <c r="U12" s="1">
+        <v>24</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1</v>
+      </c>
+      <c r="W12" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15.4">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-13</v>
+      </c>
+      <c r="F13" s="1">
+        <v>16</v>
+      </c>
+      <c r="G13" s="1">
+        <v>-4</v>
+      </c>
+      <c r="H13" s="1">
+        <v>11</v>
+      </c>
+      <c r="I13" s="1">
+        <v>8</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4</v>
+      </c>
+      <c r="K13" s="1">
+        <v>3</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1">
+        <v>7</v>
+      </c>
+      <c r="N13" s="1">
+        <v>16</v>
+      </c>
+      <c r="O13" s="1">
+        <v>-20</v>
+      </c>
+      <c r="P13" s="1">
+        <v>-17</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>2</v>
+      </c>
+      <c r="R13" s="1">
+        <v>11</v>
+      </c>
+      <c r="S13" s="1">
+        <v>30</v>
+      </c>
+      <c r="T13" s="1">
+        <v>20</v>
+      </c>
+      <c r="U13" s="1">
+        <v>22</v>
+      </c>
+      <c r="V13" s="1">
+        <v>14</v>
+      </c>
+      <c r="W13" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15.4">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1">
+        <v>2</v>
+      </c>
+      <c r="M14" s="1">
+        <v>7</v>
+      </c>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1">
+        <v>12</v>
+      </c>
+      <c r="U14" s="1">
+        <v>10</v>
+      </c>
+      <c r="V14" s="1">
+        <v>6</v>
+      </c>
+      <c r="W14" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15.4">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="1">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1">
+        <v>15</v>
+      </c>
+      <c r="E15" s="1">
+        <v>-10</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1">
+        <v>11</v>
+      </c>
+      <c r="H15" s="1">
+        <v>16</v>
+      </c>
+      <c r="I15" s="1">
+        <v>4</v>
+      </c>
+      <c r="J15" s="1">
+        <v>10</v>
+      </c>
+      <c r="K15" s="1">
+        <v>6</v>
+      </c>
+      <c r="L15" s="1">
+        <v>-4</v>
+      </c>
+      <c r="M15" s="1">
+        <v>18</v>
+      </c>
+      <c r="N15" s="1">
+        <v>-9</v>
+      </c>
+      <c r="O15" s="1">
+        <v>3</v>
+      </c>
+      <c r="P15" s="1">
+        <v>11</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>8</v>
+      </c>
+      <c r="R15" s="1">
+        <v>19</v>
+      </c>
+      <c r="S15" s="1">
+        <v>2</v>
+      </c>
+      <c r="T15" s="1">
+        <v>2</v>
+      </c>
+      <c r="U15" s="1">
+        <v>-11</v>
+      </c>
+      <c r="V15" s="1">
+        <v>12</v>
+      </c>
+      <c r="W15" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="15.4">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1">
+        <v>13</v>
+      </c>
+      <c r="C16" s="1">
+        <v>-17</v>
+      </c>
+      <c r="D16" s="1">
+        <v>-15</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5</v>
+      </c>
+      <c r="I16" s="1">
+        <v>22</v>
+      </c>
+      <c r="J16" s="1">
+        <v>11</v>
+      </c>
+      <c r="K16" s="1">
+        <v>8</v>
+      </c>
+      <c r="L16" s="1">
+        <v>8</v>
+      </c>
+      <c r="M16" s="1">
+        <v>19</v>
+      </c>
+      <c r="N16" s="1">
+        <v>17</v>
+      </c>
+      <c r="O16" s="1">
+        <v>12</v>
+      </c>
+      <c r="P16" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>-15</v>
+      </c>
+      <c r="R16" s="1">
+        <v>23</v>
+      </c>
+      <c r="S16" s="1">
+        <v>14</v>
+      </c>
+      <c r="T16" s="1">
+        <v>13</v>
+      </c>
+      <c r="U16" s="1">
+        <v>-11</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="15.4">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="1">
+        <v>-17</v>
+      </c>
+      <c r="C17" s="1">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1">
+        <v>7</v>
+      </c>
+      <c r="F17" s="1">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1">
+        <v>32</v>
+      </c>
+      <c r="H17" s="1">
+        <v>9</v>
+      </c>
+      <c r="I17" s="1">
+        <v>11</v>
+      </c>
+      <c r="J17" s="1">
+        <v>9</v>
+      </c>
+      <c r="K17" s="1">
+        <v>-18</v>
+      </c>
+      <c r="L17" s="1">
+        <v>-19</v>
+      </c>
+      <c r="M17" s="1">
+        <v>23</v>
+      </c>
+      <c r="N17" s="1">
+        <v>26</v>
+      </c>
+      <c r="O17" s="1">
+        <v>-18</v>
+      </c>
+      <c r="P17" s="1">
+        <v>-13</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>10</v>
+      </c>
+      <c r="R17" s="1">
+        <v>2</v>
+      </c>
+      <c r="S17" s="1">
+        <v>-10</v>
+      </c>
+      <c r="T17" s="1">
+        <v>10</v>
+      </c>
+      <c r="U17" s="1">
+        <v>17</v>
+      </c>
+      <c r="V17" s="1">
+        <v>40</v>
+      </c>
+      <c r="W17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15.4">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1">
+        <v>19</v>
+      </c>
+      <c r="O18" s="1">
+        <v>5</v>
+      </c>
+      <c r="P18" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>5</v>
+      </c>
+      <c r="R18" s="1">
+        <v>-16</v>
+      </c>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.4">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="1">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1">
+        <v>9</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>13</v>
+      </c>
+      <c r="K19" s="1">
+        <v>-19</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="1">
+        <v>9</v>
+      </c>
+      <c r="N19" s="1">
+        <v>14</v>
+      </c>
+      <c r="O19" s="1">
+        <v>1</v>
+      </c>
+      <c r="P19" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>4</v>
+      </c>
+      <c r="R19" s="1">
+        <v>23</v>
+      </c>
+      <c r="S19" s="1">
+        <v>12</v>
+      </c>
+      <c r="T19" s="1">
+        <v>-16</v>
+      </c>
+      <c r="U19" s="1">
+        <v>-21</v>
+      </c>
+      <c r="V19" s="1">
+        <v>5</v>
+      </c>
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15.4">
+      <c r="A20" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="1">
+        <v>11</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="1">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1">
+        <v>7</v>
+      </c>
+      <c r="H20" s="1">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>-4</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>13</v>
+      </c>
+      <c r="N20" s="1">
+        <v>11</v>
+      </c>
+      <c r="O20" s="1">
+        <v>-2</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>10</v>
+      </c>
+      <c r="R20" s="1">
+        <v>-18</v>
+      </c>
+      <c r="S20" s="1">
+        <v>17</v>
+      </c>
+      <c r="T20" s="1">
+        <v>8</v>
+      </c>
+      <c r="U20" s="1">
+        <v>-1</v>
+      </c>
+      <c r="V20" s="1">
+        <v>2</v>
+      </c>
+      <c r="W20" s="1">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="15.4">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1">
+        <v>7</v>
+      </c>
+      <c r="D21" s="1">
+        <v>3</v>
+      </c>
+      <c r="E21" s="1">
+        <v>-15</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <v>6</v>
+      </c>
+      <c r="I21" s="1">
+        <v>-1</v>
+      </c>
+      <c r="J21" s="1">
+        <v>9</v>
+      </c>
+      <c r="K21" s="1">
+        <v>3</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.4">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="1">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1">
+        <v>-2</v>
+      </c>
+      <c r="D22" s="1">
+        <v>12</v>
+      </c>
+      <c r="E22" s="1">
+        <v>-1</v>
+      </c>
+      <c r="F22" s="1">
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <v>10</v>
+      </c>
+      <c r="H22" s="1">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1">
+        <v>5</v>
+      </c>
+      <c r="K22" s="1">
+        <v>-5</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>7</v>
+      </c>
+      <c r="N22" s="1">
+        <v>14</v>
+      </c>
+      <c r="O22" s="1">
+        <v>8</v>
+      </c>
+      <c r="P22" s="1">
+        <v>-18</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>-17</v>
+      </c>
+      <c r="R22" s="1">
+        <v>15</v>
+      </c>
+      <c r="S22" s="1">
+        <v>10</v>
+      </c>
+      <c r="T22" s="1">
+        <v>2</v>
+      </c>
+      <c r="U22" s="1">
+        <v>-19</v>
+      </c>
+      <c r="V22" s="1">
+        <v>-5</v>
+      </c>
+      <c r="W22" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15.4">
+      <c r="A23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="1">
+        <v>11</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>5</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-19</v>
+      </c>
+      <c r="J23" s="1">
+        <v>19</v>
+      </c>
+      <c r="K23" s="1">
+        <v>6</v>
+      </c>
+      <c r="L23" s="1">
+        <v>2</v>
+      </c>
+      <c r="M23" s="1">
+        <v>3</v>
+      </c>
+      <c r="N23" s="1">
+        <v>-18</v>
+      </c>
+      <c r="O23" s="1">
+        <v>3</v>
+      </c>
+      <c r="P23" s="1">
+        <v>6</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>-21</v>
+      </c>
+      <c r="R23" s="1">
+        <v>-34</v>
+      </c>
+      <c r="S23" s="1">
+        <v>16</v>
+      </c>
+      <c r="T23" s="1">
+        <v>6</v>
+      </c>
+      <c r="U23" s="1">
+        <v>12</v>
+      </c>
+      <c r="V23" s="1">
+        <v>-3</v>
+      </c>
+      <c r="W23" s="1">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A560054F-8325-4548-A325-7EA890904AF0}">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -1807,7 +3353,7 @@
     </row>
     <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1">
         <v>20.8</v>
@@ -2190,7 +3736,7 @@
     </row>
     <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1">
         <v>15.8</v>
@@ -2267,7 +3813,7 @@
     </row>
     <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -2300,7 +3846,7 @@
     </row>
     <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1">
@@ -2331,7 +3877,7 @@
     </row>
     <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1">
         <v>10.7</v>
@@ -2408,7 +3954,7 @@
     </row>
     <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -2439,7 +3985,7 @@
     </row>
     <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2480,7 +4026,7 @@
     </row>
     <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1">
         <v>7.8</v>
@@ -2555,7 +4101,7 @@
     </row>
     <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1">
         <v>6.2</v>
@@ -2628,7 +4174,7 @@
     </row>
     <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1">
         <v>9</v>
@@ -2693,7 +4239,7 @@
     </row>
     <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" s="1">
         <v>8</v>
@@ -2847,7 +4393,7 @@
     </row>
     <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1">
         <v>6.4</v>
@@ -3001,7 +4547,7 @@
     </row>
     <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B23" s="1">
         <v>6.6</v>
@@ -3078,7 +4624,7 @@
     </row>
     <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B24" s="1">
         <v>6.4</v>
@@ -3155,7 +4701,7 @@
     </row>
     <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -3202,7 +4748,7 @@
     </row>
     <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B26" s="1">
         <v>5.5</v>
@@ -3262,3628 +4808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF024181-75C9-4540-9E3A-D879D3018BB2}">
-  <sheetPr>
-    <tabColor theme="6" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>6</v>
-      </c>
-      <c r="H1">
-        <v>7</v>
-      </c>
-      <c r="I1">
-        <v>8</v>
-      </c>
-      <c r="J1">
-        <v>9</v>
-      </c>
-      <c r="K1">
-        <v>10</v>
-      </c>
-      <c r="L1">
-        <v>11</v>
-      </c>
-      <c r="M1">
-        <v>12</v>
-      </c>
-      <c r="N1">
-        <v>13</v>
-      </c>
-      <c r="O1">
-        <v>14</v>
-      </c>
-      <c r="P1">
-        <v>15</v>
-      </c>
-      <c r="Q1">
-        <v>16</v>
-      </c>
-      <c r="R1">
-        <v>17</v>
-      </c>
-      <c r="S1">
-        <v>18</v>
-      </c>
-      <c r="T1">
-        <v>19</v>
-      </c>
-      <c r="U1">
-        <v>20</v>
-      </c>
-      <c r="V1">
-        <v>21</v>
-      </c>
-      <c r="W1">
-        <v>22</v>
-      </c>
-      <c r="X1">
-        <v>23</v>
-      </c>
-      <c r="Y1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="15.4">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1">
-        <v>29</v>
-      </c>
-      <c r="C2" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="D2" s="1">
-        <v>29.6</v>
-      </c>
-      <c r="E2" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="F2" s="1">
-        <v>30</v>
-      </c>
-      <c r="G2" s="1">
-        <v>30.1</v>
-      </c>
-      <c r="H2" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="I2" s="1">
-        <v>30.7</v>
-      </c>
-      <c r="J2" s="1">
-        <v>31</v>
-      </c>
-      <c r="K2" s="1">
-        <v>31.1</v>
-      </c>
-      <c r="L2" s="1">
-        <v>31</v>
-      </c>
-      <c r="M2" s="1">
-        <v>30.9</v>
-      </c>
-      <c r="N2" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="O2" s="1">
-        <v>31.1</v>
-      </c>
-      <c r="P2" s="1">
-        <v>31.4</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>31.3</v>
-      </c>
-      <c r="R2" s="1">
-        <v>31.2</v>
-      </c>
-      <c r="S2" s="1">
-        <v>30.9</v>
-      </c>
-      <c r="T2" s="1">
-        <v>30.8</v>
-      </c>
-      <c r="U2" s="1">
-        <v>30.5</v>
-      </c>
-      <c r="V2" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="W2" s="1">
-        <v>30.5</v>
-      </c>
-      <c r="X2" s="1">
-        <v>30.4</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>30.3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" ht="15.4">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="1">
-        <v>28.4</v>
-      </c>
-      <c r="C3" s="1">
-        <v>28.5</v>
-      </c>
-      <c r="D3" s="1">
-        <v>28.6</v>
-      </c>
-      <c r="E3" s="1">
-        <v>28.7</v>
-      </c>
-      <c r="F3" s="1">
-        <v>28.8</v>
-      </c>
-      <c r="G3" s="1">
-        <v>28.9</v>
-      </c>
-      <c r="H3" s="1">
-        <v>28.8</v>
-      </c>
-      <c r="I3" s="1">
-        <v>29.1</v>
-      </c>
-      <c r="J3" s="1">
-        <v>29.2</v>
-      </c>
-      <c r="K3" s="1">
-        <v>29.3</v>
-      </c>
-      <c r="L3" s="1">
-        <v>29.2</v>
-      </c>
-      <c r="M3" s="1">
-        <v>28.9</v>
-      </c>
-      <c r="N3" s="1">
-        <v>28.6</v>
-      </c>
-      <c r="O3" s="1">
-        <v>28.3</v>
-      </c>
-      <c r="P3" s="1">
-        <v>28.2</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>28.1</v>
-      </c>
-      <c r="R3" s="1">
-        <v>28.2</v>
-      </c>
-      <c r="S3" s="1">
-        <v>28.5</v>
-      </c>
-      <c r="T3" s="1">
-        <v>28.8</v>
-      </c>
-      <c r="U3" s="1">
-        <v>29.1</v>
-      </c>
-      <c r="V3" s="1">
-        <v>29.2</v>
-      </c>
-      <c r="W3" s="1">
-        <v>29.5</v>
-      </c>
-      <c r="X3" s="1">
-        <v>29.8</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>30.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="15.4">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="1">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1">
-        <v>22.7</v>
-      </c>
-      <c r="D4" s="1">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1">
-        <v>23.1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>23.4</v>
-      </c>
-      <c r="G4" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="H4" s="1">
-        <v>24</v>
-      </c>
-      <c r="I4" s="1">
-        <v>24.3</v>
-      </c>
-      <c r="J4" s="1">
-        <v>24.6</v>
-      </c>
-      <c r="K4" s="1">
-        <v>24.9</v>
-      </c>
-      <c r="L4" s="1">
-        <v>25.2</v>
-      </c>
-      <c r="M4" s="1">
-        <v>25.5</v>
-      </c>
-      <c r="N4" s="1">
-        <v>25.8</v>
-      </c>
-      <c r="O4" s="1">
-        <v>26.1</v>
-      </c>
-      <c r="P4" s="1">
-        <v>26.4</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>26.7</v>
-      </c>
-      <c r="R4" s="1">
-        <v>27</v>
-      </c>
-      <c r="S4" s="1">
-        <v>26.9</v>
-      </c>
-      <c r="T4" s="1">
-        <v>26.6</v>
-      </c>
-      <c r="U4" s="1">
-        <v>26.3</v>
-      </c>
-      <c r="V4" s="1">
-        <v>26</v>
-      </c>
-      <c r="W4" s="1">
-        <v>25.7</v>
-      </c>
-      <c r="X4" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>25.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" ht="15.4">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="1">
-        <v>25.9</v>
-      </c>
-      <c r="C5" s="1">
-        <v>25.6</v>
-      </c>
-      <c r="D5" s="1">
-        <v>25.3</v>
-      </c>
-      <c r="E5" s="1">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1">
-        <v>24.7</v>
-      </c>
-      <c r="G5" s="1">
-        <v>24.6</v>
-      </c>
-      <c r="H5" s="1">
-        <v>24.3</v>
-      </c>
-      <c r="I5" s="1">
-        <v>24</v>
-      </c>
-      <c r="J5" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="K5" s="1">
-        <v>24.2</v>
-      </c>
-      <c r="L5" s="1">
-        <v>24.3</v>
-      </c>
-      <c r="M5" s="1">
-        <v>24.4</v>
-      </c>
-      <c r="N5" s="1">
-        <v>24.1</v>
-      </c>
-      <c r="O5" s="1">
-        <v>24</v>
-      </c>
-      <c r="P5" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>23.6</v>
-      </c>
-      <c r="R5" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="S5" s="1">
-        <v>23</v>
-      </c>
-      <c r="T5" s="1">
-        <v>22.9</v>
-      </c>
-      <c r="U5" s="1">
-        <v>23</v>
-      </c>
-      <c r="V5" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="W5" s="1">
-        <v>23.4</v>
-      </c>
-      <c r="X5" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="15.4">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1">
-        <v>24.2</v>
-      </c>
-      <c r="C6" s="1">
-        <v>23.9</v>
-      </c>
-      <c r="D6" s="1">
-        <v>23.6</v>
-      </c>
-      <c r="E6" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>23.2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="H6" s="1">
-        <v>23.6</v>
-      </c>
-      <c r="I6" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="J6" s="1">
-        <v>23.8</v>
-      </c>
-      <c r="K6" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="L6" s="1">
-        <v>23.6</v>
-      </c>
-      <c r="M6" s="1">
-        <v>23.5</v>
-      </c>
-      <c r="N6" s="1">
-        <v>23.4</v>
-      </c>
-      <c r="O6" s="1">
-        <v>23.7</v>
-      </c>
-      <c r="P6" s="1">
-        <v>23.8</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>23.5</v>
-      </c>
-      <c r="R6" s="1">
-        <v>23.2</v>
-      </c>
-      <c r="S6" s="1">
-        <v>22.9</v>
-      </c>
-      <c r="T6" s="1">
-        <v>22.8</v>
-      </c>
-      <c r="U6" s="1">
-        <v>22.7</v>
-      </c>
-      <c r="V6" s="1">
-        <v>22.8</v>
-      </c>
-      <c r="W6" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="X6" s="1">
-        <v>22.2</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>21.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="15.4">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="1">
-        <v>21</v>
-      </c>
-      <c r="C7" s="1">
-        <v>21.1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>21.4</v>
-      </c>
-      <c r="E7" s="1">
-        <v>21.7</v>
-      </c>
-      <c r="F7" s="1">
-        <v>22</v>
-      </c>
-      <c r="G7" s="1">
-        <v>22.1</v>
-      </c>
-      <c r="H7" s="1">
-        <v>22.2</v>
-      </c>
-      <c r="I7" s="1">
-        <v>22.3</v>
-      </c>
-      <c r="J7" s="1">
-        <v>22.2</v>
-      </c>
-      <c r="K7" s="1">
-        <v>21.9</v>
-      </c>
-      <c r="L7" s="1">
-        <v>22</v>
-      </c>
-      <c r="M7" s="1">
-        <v>22.3</v>
-      </c>
-      <c r="N7" s="1">
-        <v>22.4</v>
-      </c>
-      <c r="O7" s="1">
-        <v>22.3</v>
-      </c>
-      <c r="P7" s="1">
-        <v>22.4</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="R7" s="1">
-        <v>22.6</v>
-      </c>
-      <c r="S7" s="1">
-        <v>22.7</v>
-      </c>
-      <c r="T7" s="1">
-        <v>23</v>
-      </c>
-      <c r="U7" s="1">
-        <v>23.3</v>
-      </c>
-      <c r="V7" s="1">
-        <v>23.4</v>
-      </c>
-      <c r="W7" s="1">
-        <v>23.5</v>
-      </c>
-      <c r="X7" s="1">
-        <v>23.6</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>23.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="15.4">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="1">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="D8" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="E8" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="F8" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="G8" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="H8" s="1">
-        <v>6</v>
-      </c>
-      <c r="I8" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="J8" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="K8" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="L8" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="M8" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="N8" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="O8" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="P8" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="R8" s="1">
-        <v>5.3</v>
-      </c>
-      <c r="S8" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="T8" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="U8" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="V8" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="W8" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="X8" s="1">
-        <v>5.3</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="15.4">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="1">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="C9" s="1">
-        <v>19</v>
-      </c>
-      <c r="D9" s="1">
-        <v>19.3</v>
-      </c>
-      <c r="E9" s="1">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="F9" s="1">
-        <v>19.7</v>
-      </c>
-      <c r="G9" s="1">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="H9" s="1">
-        <v>19.5</v>
-      </c>
-      <c r="I9" s="1">
-        <v>19.2</v>
-      </c>
-      <c r="J9" s="1">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="K9" s="1">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="L9" s="1">
-        <v>18.3</v>
-      </c>
-      <c r="M9" s="1">
-        <v>17.7</v>
-      </c>
-      <c r="N9" s="1">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="O9" s="1">
-        <v>16.5</v>
-      </c>
-      <c r="P9" s="1">
-        <v>15.9</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>15.7</v>
-      </c>
-      <c r="R9" s="1">
-        <v>15.1</v>
-      </c>
-      <c r="S9" s="1">
-        <v>14.9</v>
-      </c>
-      <c r="T9" s="1">
-        <v>15.1</v>
-      </c>
-      <c r="U9" s="1">
-        <v>15.7</v>
-      </c>
-      <c r="V9" s="1">
-        <v>16.3</v>
-      </c>
-      <c r="W9" s="1">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="X9" s="1">
-        <v>17.5</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>18.100000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="15.4">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="C10" s="1">
-        <v>9</v>
-      </c>
-      <c r="D10" s="1">
-        <v>16.8</v>
-      </c>
-      <c r="E10" s="1">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="F10" s="1">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="G10" s="1">
-        <v>15.8</v>
-      </c>
-      <c r="H10" s="1">
-        <v>15.2</v>
-      </c>
-      <c r="I10" s="1">
-        <v>14.6</v>
-      </c>
-      <c r="J10" s="1">
-        <v>14.4</v>
-      </c>
-      <c r="K10" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="L10" s="1">
-        <v>13.2</v>
-      </c>
-      <c r="M10" s="1">
-        <v>13</v>
-      </c>
-      <c r="N10" s="1">
-        <v>12.4</v>
-      </c>
-      <c r="O10" s="1">
-        <v>11.8</v>
-      </c>
-      <c r="P10" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>10.6</v>
-      </c>
-      <c r="R10" s="1">
-        <v>10</v>
-      </c>
-      <c r="S10" s="1">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="T10" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="U10" s="1">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="V10" s="1">
-        <v>10.8</v>
-      </c>
-      <c r="W10" s="1">
-        <v>11.4</v>
-      </c>
-      <c r="X10" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>11.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="15.4">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="1">
-        <v>12</v>
-      </c>
-      <c r="C11" s="1">
-        <v>12.6</v>
-      </c>
-      <c r="D11" s="1">
-        <v>12.8</v>
-      </c>
-      <c r="E11" s="1">
-        <v>13</v>
-      </c>
-      <c r="F11" s="1">
-        <v>12.8</v>
-      </c>
-      <c r="G11" s="1">
-        <v>12.6</v>
-      </c>
-      <c r="H11" s="1">
-        <v>12.8</v>
-      </c>
-      <c r="I11" s="1">
-        <v>13.4</v>
-      </c>
-      <c r="J11" s="1">
-        <v>13.6</v>
-      </c>
-      <c r="K11" s="1">
-        <v>13</v>
-      </c>
-      <c r="L11" s="1">
-        <v>12.4</v>
-      </c>
-      <c r="M11" s="1">
-        <v>11.8</v>
-      </c>
-      <c r="N11" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="O11" s="1">
-        <v>10.6</v>
-      </c>
-      <c r="P11" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>11.8</v>
-      </c>
-      <c r="R11" s="1">
-        <v>12.4</v>
-      </c>
-      <c r="S11" s="1">
-        <v>13</v>
-      </c>
-      <c r="T11" s="1">
-        <v>12.8</v>
-      </c>
-      <c r="U11" s="1">
-        <v>13</v>
-      </c>
-      <c r="V11" s="1">
-        <v>13.2</v>
-      </c>
-      <c r="W11" s="1">
-        <v>13.8</v>
-      </c>
-      <c r="X11" s="1">
-        <v>13.2</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="15.4">
-      <c r="A12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="C12" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="D12" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E12" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="F12" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="G12" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="H12" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="I12" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="J12" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="K12" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="M12" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="N12" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="O12" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="P12" s="1">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>10.3</v>
-      </c>
-      <c r="R12" s="1">
-        <v>10.5</v>
-      </c>
-      <c r="S12" s="1">
-        <v>9.9</v>
-      </c>
-      <c r="T12" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="U12" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="V12" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="W12" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="X12" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" ht="15.4">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1">
-        <v>13.1</v>
-      </c>
-      <c r="C13" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>11.9</v>
-      </c>
-      <c r="E13" s="1">
-        <v>11.3</v>
-      </c>
-      <c r="F13" s="1">
-        <v>10.7</v>
-      </c>
-      <c r="G13" s="1">
-        <v>10.1</v>
-      </c>
-      <c r="H13" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="I13" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="J13" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="K13" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="L13" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="M13" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="N13" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="O13" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="P13" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="R13" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="S13" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="T13" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="U13" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="V13" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="W13" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="X13" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" ht="15.4">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="C14" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="D14" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="F14" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="G14" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="I14" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="J14" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="K14" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="L14" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="M14" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="N14" s="1">
-        <v>8.9</v>
-      </c>
-      <c r="O14" s="1">
-        <v>9.1</v>
-      </c>
-      <c r="P14" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="R14" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="S14" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="T14" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="U14" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="V14" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="W14" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="X14" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="15.4">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="C15" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="D15" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="E15" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="F15" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="G15" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="H15" s="1">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="I15" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="J15" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="K15" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="L15" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="M15" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="N15" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="O15" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="P15" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="R15" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="S15" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="T15" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="U15" s="1">
-        <v>7.7</v>
-      </c>
-      <c r="V15" s="1">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="W15" s="1">
-        <v>8.9</v>
-      </c>
-      <c r="X15" s="1">
-        <v>9.5</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>9.3000000000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="15.4">
-      <c r="A16" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="C16" s="1">
-        <v>7</v>
-      </c>
-      <c r="D16" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="E16" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="F16" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="G16" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="H16" s="1">
-        <v>6</v>
-      </c>
-      <c r="I16" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="J16" s="1">
-        <v>6</v>
-      </c>
-      <c r="K16" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="L16" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="M16" s="1">
-        <v>7.8</v>
-      </c>
-      <c r="N16" s="1">
-        <v>8.4</v>
-      </c>
-      <c r="O16" s="1">
-        <v>9</v>
-      </c>
-      <c r="P16" s="1">
-        <v>9.6</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="R16" s="1">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="S16" s="1">
-        <v>8.6</v>
-      </c>
-      <c r="T16" s="1">
-        <v>8</v>
-      </c>
-      <c r="U16" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="V16" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="W16" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="X16" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" ht="15.4">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="1">
-        <v>11.8</v>
-      </c>
-      <c r="C17" s="1">
-        <v>11.2</v>
-      </c>
-      <c r="D17" s="1">
-        <v>10.6</v>
-      </c>
-      <c r="E17" s="1">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1">
-        <v>9.4</v>
-      </c>
-      <c r="G17" s="1">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H17" s="1">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="I17" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="J17" s="1">
-        <v>7</v>
-      </c>
-      <c r="K17" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="L17" s="1">
-        <v>5.8</v>
-      </c>
-      <c r="M17" s="1">
-        <v>6</v>
-      </c>
-      <c r="N17" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="O17" s="1">
-        <v>6</v>
-      </c>
-      <c r="P17" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="R17" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="S17" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="T17" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="U17" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="V17" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="W17" s="1">
-        <v>5.3</v>
-      </c>
-      <c r="X17" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" ht="15.4">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="1">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="C18" s="1">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="D18" s="1">
-        <v>7.6</v>
-      </c>
-      <c r="E18" s="1">
-        <v>7</v>
-      </c>
-      <c r="F18" s="1">
-        <v>6.4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="H18" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="I18" s="1">
-        <v>5</v>
-      </c>
-      <c r="J18" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="K18" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L18" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="M18" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="N18" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="O18" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="P18" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>8.1</v>
-      </c>
-      <c r="R18" s="1">
-        <v>7.9</v>
-      </c>
-      <c r="S18" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="T18" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="U18" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="V18" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="W18" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="X18" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" ht="15.4">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="1">
-        <v>7.2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>6.6</v>
-      </c>
-      <c r="D19" s="1">
-        <v>6</v>
-      </c>
-      <c r="E19" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="F19" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="G19" s="1">
-        <v>5</v>
-      </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-    </row>
-    <row r="20" spans="1:25" ht="15.4">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="1">
-        <v>6.2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>5.6</v>
-      </c>
-      <c r="D20" s="1">
-        <v>5</v>
-      </c>
-      <c r="E20" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="F20" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="G20" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="I20" s="1">
-        <v>5.3</v>
-      </c>
-      <c r="J20" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="K20" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="L20" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="M20" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="N20" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="O20" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="P20" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="R20" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="S20" s="1">
-        <v>6.9</v>
-      </c>
-      <c r="T20" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="U20" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="V20" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="W20" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="X20" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="Y20" s="1">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" ht="15.4">
-      <c r="A21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="1">
-        <v>6</v>
-      </c>
-      <c r="C21" s="1">
-        <v>5.4</v>
-      </c>
-      <c r="D21" s="1">
-        <v>4.8</v>
-      </c>
-      <c r="E21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="F21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="G21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="H21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="J21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="K21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="M21" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="N21" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="O21" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="P21" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="R21" s="1">
-        <v>5.7</v>
-      </c>
-      <c r="S21" s="1">
-        <v>5.9</v>
-      </c>
-      <c r="T21" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="U21" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="V21" s="1">
-        <v>7.3</v>
-      </c>
-      <c r="W21" s="1">
-        <v>6.7</v>
-      </c>
-      <c r="X21" s="1">
-        <v>6.1</v>
-      </c>
-      <c r="Y21" s="1">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="15.4">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="I22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="J22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="K22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="L22" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="M22" s="1">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="N22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="O22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="P22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="R22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="S22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="T22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="U22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="V22" s="1">
-        <v>4.7</v>
-      </c>
-      <c r="W22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="X22" s="1">
-        <v>4.5</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>4.5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E702A3C-7203-446F-AEDA-1B0D838A20DB}">
-  <sheetPr>
-    <tabColor theme="6" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2">
-        <v>27.7</v>
-      </c>
-      <c r="C2">
-        <v>28</v>
-      </c>
-      <c r="D2">
-        <v>28.1</v>
-      </c>
-      <c r="E2">
-        <v>28.2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3">
-        <v>27.4</v>
-      </c>
-      <c r="C3">
-        <v>27.7</v>
-      </c>
-      <c r="D3">
-        <v>28</v>
-      </c>
-      <c r="E3">
-        <v>28.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4">
-        <v>27.2</v>
-      </c>
-      <c r="C4">
-        <v>27.1</v>
-      </c>
-      <c r="D4">
-        <v>26.8</v>
-      </c>
-      <c r="E4">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>25.5</v>
-      </c>
-      <c r="C5">
-        <v>25.2</v>
-      </c>
-      <c r="D5">
-        <v>24.9</v>
-      </c>
-      <c r="E5">
-        <v>24.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6">
-        <v>23.2</v>
-      </c>
-      <c r="C6">
-        <v>23.5</v>
-      </c>
-      <c r="D6">
-        <v>23.8</v>
-      </c>
-      <c r="E6">
-        <v>24.1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7">
-        <v>22.8</v>
-      </c>
-      <c r="C7">
-        <v>23.1</v>
-      </c>
-      <c r="D7">
-        <v>23.4</v>
-      </c>
-      <c r="E7">
-        <v>23.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8">
-        <v>22.5</v>
-      </c>
-      <c r="C8">
-        <v>22.6</v>
-      </c>
-      <c r="D8">
-        <v>22.9</v>
-      </c>
-      <c r="E8">
-        <v>23.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9">
-        <v>15.1</v>
-      </c>
-      <c r="C9">
-        <v>14.5</v>
-      </c>
-      <c r="D9">
-        <v>13.9</v>
-      </c>
-      <c r="E9">
-        <v>13.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10">
-        <v>12</v>
-      </c>
-      <c r="C10">
-        <v>12.2</v>
-      </c>
-      <c r="D10">
-        <v>12.8</v>
-      </c>
-      <c r="E10">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11">
-        <v>11.8</v>
-      </c>
-      <c r="C11">
-        <v>11.6</v>
-      </c>
-      <c r="D11">
-        <v>12.2</v>
-      </c>
-      <c r="E11">
-        <v>12.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12">
-        <v>11.6</v>
-      </c>
-      <c r="C12">
-        <v>11.4</v>
-      </c>
-      <c r="D12">
-        <v>10.8</v>
-      </c>
-      <c r="E12">
-        <v>10.199999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>9.4</v>
-      </c>
-      <c r="D13">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E13">
-        <v>8.1999999999999993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>7.4</v>
-      </c>
-      <c r="D14">
-        <v>6.8</v>
-      </c>
-      <c r="E14">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15">
-        <v>7.4</v>
-      </c>
-      <c r="C15">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <v>8.6</v>
-      </c>
-      <c r="E15">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16">
-        <v>7.3</v>
-      </c>
-      <c r="C16">
-        <v>7.9</v>
-      </c>
-      <c r="D16">
-        <v>8.5</v>
-      </c>
-      <c r="E16">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17">
-        <v>6.8</v>
-      </c>
-      <c r="C17">
-        <v>6.2</v>
-      </c>
-      <c r="D17">
-        <v>5.6</v>
-      </c>
-      <c r="E17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18">
-        <v>6.5</v>
-      </c>
-      <c r="C18">
-        <v>6.3</v>
-      </c>
-      <c r="D18">
-        <v>6.9</v>
-      </c>
-      <c r="E18">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19">
-        <v>6.4</v>
-      </c>
-      <c r="C19">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>6.4</v>
-      </c>
-      <c r="E19">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20">
-        <v>6.2</v>
-      </c>
-      <c r="C20">
-        <v>6.8</v>
-      </c>
-      <c r="D20">
-        <v>7.4</v>
-      </c>
-      <c r="E20">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21">
-        <v>6.2</v>
-      </c>
-      <c r="C21">
-        <v>6.4</v>
-      </c>
-      <c r="D21">
-        <v>7</v>
-      </c>
-      <c r="E21">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22">
-        <v>6</v>
-      </c>
-      <c r="C22">
-        <v>5.8</v>
-      </c>
-      <c r="D22">
-        <v>6.4</v>
-      </c>
-      <c r="E22">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23">
-        <v>5.9</v>
-      </c>
-      <c r="C23">
-        <v>5.3</v>
-      </c>
-      <c r="D23">
-        <v>4.7</v>
-      </c>
-      <c r="E23">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{380C4B9E-1EC8-4446-8DCE-B4EFA581E858}">
-  <sheetPr>
-    <tabColor theme="6" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:23">
-      <c r="B1">
-        <v>1</v>
-      </c>
-      <c r="C1">
-        <v>2</v>
-      </c>
-      <c r="D1">
-        <v>3</v>
-      </c>
-      <c r="E1">
-        <v>4</v>
-      </c>
-      <c r="F1">
-        <v>5</v>
-      </c>
-      <c r="G1">
-        <v>7</v>
-      </c>
-      <c r="H1">
-        <v>8</v>
-      </c>
-      <c r="I1">
-        <v>9</v>
-      </c>
-      <c r="J1">
-        <v>10</v>
-      </c>
-      <c r="K1">
-        <v>11</v>
-      </c>
-      <c r="L1">
-        <v>12</v>
-      </c>
-      <c r="M1">
-        <v>13</v>
-      </c>
-      <c r="N1">
-        <v>14</v>
-      </c>
-      <c r="O1">
-        <v>15</v>
-      </c>
-      <c r="P1">
-        <v>16</v>
-      </c>
-      <c r="Q1">
-        <v>17</v>
-      </c>
-      <c r="R1">
-        <v>18</v>
-      </c>
-      <c r="S1">
-        <v>19</v>
-      </c>
-      <c r="T1">
-        <v>20</v>
-      </c>
-      <c r="U1">
-        <v>21</v>
-      </c>
-      <c r="V1">
-        <v>22</v>
-      </c>
-      <c r="W1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="15.4">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="1">
-        <v>35</v>
-      </c>
-      <c r="C2" s="1">
-        <v>61</v>
-      </c>
-      <c r="D2" s="1">
-        <v>36</v>
-      </c>
-      <c r="E2" s="1">
-        <v>37</v>
-      </c>
-      <c r="F2" s="1">
-        <v>64</v>
-      </c>
-      <c r="G2" s="1">
-        <v>35</v>
-      </c>
-      <c r="H2" s="1">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1">
-        <v>35</v>
-      </c>
-      <c r="J2" s="1">
-        <v>56</v>
-      </c>
-      <c r="K2" s="1">
-        <v>46</v>
-      </c>
-      <c r="L2" s="1">
-        <v>46</v>
-      </c>
-      <c r="M2" s="1">
-        <v>68</v>
-      </c>
-      <c r="N2" s="1">
-        <v>46</v>
-      </c>
-      <c r="O2" s="1">
-        <v>38</v>
-      </c>
-      <c r="P2" s="1">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>47</v>
-      </c>
-      <c r="R2" s="1">
-        <v>62</v>
-      </c>
-      <c r="S2" s="1">
-        <v>53</v>
-      </c>
-      <c r="T2" s="1">
-        <v>42</v>
-      </c>
-      <c r="U2" s="1">
-        <v>45</v>
-      </c>
-      <c r="V2" s="1">
-        <v>44</v>
-      </c>
-      <c r="W2" s="1">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="15.4">
-      <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="1">
-        <v>28</v>
-      </c>
-      <c r="C3" s="1">
-        <v>36</v>
-      </c>
-      <c r="D3" s="1">
-        <v>52</v>
-      </c>
-      <c r="E3" s="1">
-        <v>61</v>
-      </c>
-      <c r="F3" s="1">
-        <v>28</v>
-      </c>
-      <c r="G3" s="1">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1">
-        <v>27</v>
-      </c>
-      <c r="I3" s="1">
-        <v>28</v>
-      </c>
-      <c r="J3" s="1">
-        <v>51</v>
-      </c>
-      <c r="K3" s="1">
-        <v>26</v>
-      </c>
-      <c r="L3" s="1">
-        <v>39</v>
-      </c>
-      <c r="M3" s="1">
-        <v>7</v>
-      </c>
-      <c r="N3" s="1">
-        <v>30</v>
-      </c>
-      <c r="O3" s="1">
-        <v>30</v>
-      </c>
-      <c r="P3" s="1">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>-11</v>
-      </c>
-      <c r="R3" s="1">
-        <v>-3</v>
-      </c>
-      <c r="S3" s="1">
-        <v>32</v>
-      </c>
-      <c r="T3" s="1">
-        <v>-10</v>
-      </c>
-      <c r="U3" s="1">
-        <v>37</v>
-      </c>
-      <c r="V3" s="1">
-        <v>35</v>
-      </c>
-      <c r="W3" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="15.4">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="1">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1">
-        <v>29</v>
-      </c>
-      <c r="E4" s="1">
-        <v>19</v>
-      </c>
-      <c r="F4" s="1">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1">
-        <v>28</v>
-      </c>
-      <c r="H4" s="1">
-        <v>39</v>
-      </c>
-      <c r="I4" s="1">
-        <v>23</v>
-      </c>
-      <c r="J4" s="1">
-        <v>31</v>
-      </c>
-      <c r="K4" s="1">
-        <v>25</v>
-      </c>
-      <c r="L4" s="1">
-        <v>20</v>
-      </c>
-      <c r="M4" s="1">
-        <v>32</v>
-      </c>
-      <c r="N4" s="1">
-        <v>29</v>
-      </c>
-      <c r="O4" s="1">
-        <v>17</v>
-      </c>
-      <c r="P4" s="1">
-        <v>39</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>20</v>
-      </c>
-      <c r="R4" s="1">
-        <v>6</v>
-      </c>
-      <c r="S4" s="1">
-        <v>-4</v>
-      </c>
-      <c r="T4" s="1">
-        <v>41</v>
-      </c>
-      <c r="U4" s="1">
-        <v>13</v>
-      </c>
-      <c r="V4" s="1">
-        <v>26</v>
-      </c>
-      <c r="W4" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="15.4">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="C5" s="1">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1">
-        <v>19</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1">
-        <v>6</v>
-      </c>
-      <c r="H5" s="1">
-        <v>-2</v>
-      </c>
-      <c r="I5" s="1">
-        <v>2</v>
-      </c>
-      <c r="J5" s="1">
-        <v>29</v>
-      </c>
-      <c r="K5" s="1">
-        <v>38</v>
-      </c>
-      <c r="L5" s="1">
-        <v>29</v>
-      </c>
-      <c r="M5" s="1">
-        <v>15</v>
-      </c>
-      <c r="N5" s="1">
-        <v>25</v>
-      </c>
-      <c r="O5" s="1">
-        <v>9</v>
-      </c>
-      <c r="P5" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>31</v>
-      </c>
-      <c r="R5" s="1">
-        <v>41</v>
-      </c>
-      <c r="S5" s="1">
-        <v>46</v>
-      </c>
-      <c r="T5" s="1">
-        <v>48</v>
-      </c>
-      <c r="U5" s="1">
-        <v>57</v>
-      </c>
-      <c r="V5" s="1">
-        <v>-14</v>
-      </c>
-      <c r="W5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="15.4">
-      <c r="A6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="1">
-        <v>39</v>
-      </c>
-      <c r="C6" s="1">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1">
-        <v>23</v>
-      </c>
-      <c r="E6" s="1">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1">
-        <v>25</v>
-      </c>
-      <c r="G6" s="1">
-        <v>27</v>
-      </c>
-      <c r="H6" s="1">
-        <v>14</v>
-      </c>
-      <c r="I6" s="1">
-        <v>27</v>
-      </c>
-      <c r="J6" s="1">
-        <v>28</v>
-      </c>
-      <c r="K6" s="1">
-        <v>12</v>
-      </c>
-      <c r="L6" s="1">
-        <v>7</v>
-      </c>
-      <c r="M6" s="1">
-        <v>2</v>
-      </c>
-      <c r="N6" s="1">
-        <v>62</v>
-      </c>
-      <c r="O6" s="1">
-        <v>5</v>
-      </c>
-      <c r="P6" s="1">
-        <v>-1</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>16</v>
-      </c>
-      <c r="R6" s="1">
-        <v>25</v>
-      </c>
-      <c r="S6" s="1">
-        <v>-9</v>
-      </c>
-      <c r="T6" s="1">
-        <v>-16</v>
-      </c>
-      <c r="U6" s="1">
-        <v>39</v>
-      </c>
-      <c r="V6" s="1">
-        <v>12</v>
-      </c>
-      <c r="W6" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="15.4">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="1">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1">
-        <v>12</v>
-      </c>
-      <c r="D7" s="1">
-        <v>8</v>
-      </c>
-      <c r="E7" s="1">
-        <v>21</v>
-      </c>
-      <c r="F7" s="1">
-        <v>20</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6</v>
-      </c>
-      <c r="H7" s="1">
-        <v>19</v>
-      </c>
-      <c r="I7" s="1">
-        <v>22</v>
-      </c>
-      <c r="J7" s="1">
-        <v>31</v>
-      </c>
-      <c r="K7" s="1">
-        <v>4</v>
-      </c>
-      <c r="L7" s="1">
-        <v>12</v>
-      </c>
-      <c r="M7" s="1">
-        <v>-8</v>
-      </c>
-      <c r="N7" s="1">
-        <v>31</v>
-      </c>
-      <c r="O7" s="1">
-        <v>38</v>
-      </c>
-      <c r="P7" s="1">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>18</v>
-      </c>
-      <c r="R7" s="1">
-        <v>-14</v>
-      </c>
-      <c r="S7" s="1">
-        <v>32</v>
-      </c>
-      <c r="T7" s="1">
-        <v>19</v>
-      </c>
-      <c r="U7" s="1">
-        <v>21</v>
-      </c>
-      <c r="V7" s="1">
-        <v>34</v>
-      </c>
-      <c r="W7" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="15.4">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="1">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1">
-        <v>18</v>
-      </c>
-      <c r="D8" s="1">
-        <v>-7</v>
-      </c>
-      <c r="E8" s="1">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1">
-        <v>28</v>
-      </c>
-      <c r="G8" s="1">
-        <v>16</v>
-      </c>
-      <c r="H8" s="1">
-        <v>31</v>
-      </c>
-      <c r="I8" s="1">
-        <v>-12</v>
-      </c>
-      <c r="J8" s="1">
-        <v>34</v>
-      </c>
-      <c r="K8" s="1">
-        <v>18</v>
-      </c>
-      <c r="L8" s="1">
-        <v>27</v>
-      </c>
-      <c r="M8" s="1">
-        <v>28</v>
-      </c>
-      <c r="N8" s="1">
-        <v>6</v>
-      </c>
-      <c r="O8" s="1">
-        <v>17</v>
-      </c>
-      <c r="P8" s="1">
-        <v>-2</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>14</v>
-      </c>
-      <c r="R8" s="1">
-        <v>37</v>
-      </c>
-      <c r="S8" s="1">
-        <v>25</v>
-      </c>
-      <c r="T8" s="1">
-        <v>18</v>
-      </c>
-      <c r="U8" s="1">
-        <v>1</v>
-      </c>
-      <c r="V8" s="1">
-        <v>14</v>
-      </c>
-      <c r="W8" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="15.4">
-      <c r="A9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1">
-        <v>-11</v>
-      </c>
-      <c r="C9" s="1">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1">
-        <v>-15</v>
-      </c>
-      <c r="E9" s="1">
-        <v>29</v>
-      </c>
-      <c r="F9" s="1">
-        <v>16</v>
-      </c>
-      <c r="G9" s="1">
-        <v>16</v>
-      </c>
-      <c r="H9" s="1">
-        <v>14</v>
-      </c>
-      <c r="I9" s="1">
-        <v>19</v>
-      </c>
-      <c r="J9" s="1">
-        <v>32</v>
-      </c>
-      <c r="K9" s="1">
-        <v>6</v>
-      </c>
-      <c r="L9" s="1">
-        <v>12</v>
-      </c>
-      <c r="M9" s="1">
-        <v>26</v>
-      </c>
-      <c r="N9" s="1">
-        <v>-7</v>
-      </c>
-      <c r="O9" s="1">
-        <v>24</v>
-      </c>
-      <c r="P9" s="1">
-        <v>22</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>22</v>
-      </c>
-      <c r="R9" s="1">
-        <v>22</v>
-      </c>
-      <c r="S9" s="1">
-        <v>-10</v>
-      </c>
-      <c r="T9" s="1">
-        <v>24</v>
-      </c>
-      <c r="U9" s="1">
-        <v>-3</v>
-      </c>
-      <c r="V9" s="1">
-        <v>41</v>
-      </c>
-      <c r="W9" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="15.4">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1">
-        <v>-16</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>16</v>
-      </c>
-      <c r="E10" s="1">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-      <c r="H10" s="1">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1">
-        <v>3</v>
-      </c>
-      <c r="J10" s="1">
-        <v>20</v>
-      </c>
-      <c r="K10" s="1">
-        <v>20</v>
-      </c>
-      <c r="L10" s="1">
-        <v>18</v>
-      </c>
-      <c r="M10" s="1">
-        <v>-7</v>
-      </c>
-      <c r="N10" s="1">
-        <v>18</v>
-      </c>
-      <c r="O10" s="1">
-        <v>15</v>
-      </c>
-      <c r="P10" s="1">
-        <v>24</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>35</v>
-      </c>
-      <c r="R10" s="1">
-        <v>56</v>
-      </c>
-      <c r="S10" s="1">
-        <v>-20</v>
-      </c>
-      <c r="T10" s="1">
-        <v>14</v>
-      </c>
-      <c r="U10" s="1">
-        <v>3</v>
-      </c>
-      <c r="V10" s="1">
-        <v>39</v>
-      </c>
-      <c r="W10" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="15.4">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="1">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1">
-        <v>-14</v>
-      </c>
-      <c r="D11" s="1">
-        <v>21</v>
-      </c>
-      <c r="E11" s="1">
-        <v>18</v>
-      </c>
-      <c r="F11" s="1">
-        <v>12</v>
-      </c>
-      <c r="G11" s="1">
-        <v>-17</v>
-      </c>
-      <c r="H11" s="1">
-        <v>16</v>
-      </c>
-      <c r="I11" s="1">
-        <v>14</v>
-      </c>
-      <c r="J11" s="1">
-        <v>25</v>
-      </c>
-      <c r="K11" s="1">
-        <v>2</v>
-      </c>
-      <c r="L11" s="1">
-        <v>9</v>
-      </c>
-      <c r="M11" s="1">
-        <v>12</v>
-      </c>
-      <c r="N11" s="1">
-        <v>10</v>
-      </c>
-      <c r="O11" s="1">
-        <v>7</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>-14</v>
-      </c>
-      <c r="R11" s="1">
-        <v>17</v>
-      </c>
-      <c r="S11" s="1">
-        <v>10</v>
-      </c>
-      <c r="T11" s="1">
-        <v>8</v>
-      </c>
-      <c r="U11" s="1">
-        <v>28</v>
-      </c>
-      <c r="V11" s="1">
-        <v>39</v>
-      </c>
-      <c r="W11" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="15.4">
-      <c r="A12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1">
-        <v>20</v>
-      </c>
-      <c r="C12" s="1">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>17</v>
-      </c>
-      <c r="F12" s="1">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1">
-        <v>10</v>
-      </c>
-      <c r="H12" s="1">
-        <v>14</v>
-      </c>
-      <c r="I12" s="1">
-        <v>8</v>
-      </c>
-      <c r="J12" s="1">
-        <v>7</v>
-      </c>
-      <c r="K12" s="1">
-        <v>-3</v>
-      </c>
-      <c r="L12" s="1">
-        <v>-19</v>
-      </c>
-      <c r="M12" s="1">
-        <v>17</v>
-      </c>
-      <c r="N12" s="1">
-        <v>39</v>
-      </c>
-      <c r="O12" s="1">
-        <v>3</v>
-      </c>
-      <c r="P12" s="1">
-        <v>21</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>7</v>
-      </c>
-      <c r="R12" s="1">
-        <v>11</v>
-      </c>
-      <c r="S12" s="1">
-        <v>22</v>
-      </c>
-      <c r="T12" s="1">
-        <v>10</v>
-      </c>
-      <c r="U12" s="1">
-        <v>24</v>
-      </c>
-      <c r="V12" s="1">
-        <v>1</v>
-      </c>
-      <c r="W12" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="15.4">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="1">
-        <v>8</v>
-      </c>
-      <c r="C13" s="1">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1">
-        <v>7</v>
-      </c>
-      <c r="E13" s="1">
-        <v>-13</v>
-      </c>
-      <c r="F13" s="1">
-        <v>16</v>
-      </c>
-      <c r="G13" s="1">
-        <v>-4</v>
-      </c>
-      <c r="H13" s="1">
-        <v>11</v>
-      </c>
-      <c r="I13" s="1">
-        <v>8</v>
-      </c>
-      <c r="J13" s="1">
-        <v>4</v>
-      </c>
-      <c r="K13" s="1">
-        <v>3</v>
-      </c>
-      <c r="L13" s="1">
-        <v>5</v>
-      </c>
-      <c r="M13" s="1">
-        <v>7</v>
-      </c>
-      <c r="N13" s="1">
-        <v>16</v>
-      </c>
-      <c r="O13" s="1">
-        <v>-20</v>
-      </c>
-      <c r="P13" s="1">
-        <v>-17</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>2</v>
-      </c>
-      <c r="R13" s="1">
-        <v>11</v>
-      </c>
-      <c r="S13" s="1">
-        <v>30</v>
-      </c>
-      <c r="T13" s="1">
-        <v>20</v>
-      </c>
-      <c r="U13" s="1">
-        <v>22</v>
-      </c>
-      <c r="V13" s="1">
-        <v>14</v>
-      </c>
-      <c r="W13" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="15.4">
-      <c r="A14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1">
-        <v>2</v>
-      </c>
-      <c r="M14" s="1">
-        <v>7</v>
-      </c>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1">
-        <v>1</v>
-      </c>
-      <c r="T14" s="1">
-        <v>12</v>
-      </c>
-      <c r="U14" s="1">
-        <v>10</v>
-      </c>
-      <c r="V14" s="1">
-        <v>6</v>
-      </c>
-      <c r="W14" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" ht="15.4">
-      <c r="A15" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="1">
-        <v>15</v>
-      </c>
-      <c r="C15" s="1">
-        <v>6</v>
-      </c>
-      <c r="D15" s="1">
-        <v>15</v>
-      </c>
-      <c r="E15" s="1">
-        <v>-10</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1">
-        <v>11</v>
-      </c>
-      <c r="H15" s="1">
-        <v>16</v>
-      </c>
-      <c r="I15" s="1">
-        <v>4</v>
-      </c>
-      <c r="J15" s="1">
-        <v>10</v>
-      </c>
-      <c r="K15" s="1">
-        <v>6</v>
-      </c>
-      <c r="L15" s="1">
-        <v>-4</v>
-      </c>
-      <c r="M15" s="1">
-        <v>18</v>
-      </c>
-      <c r="N15" s="1">
-        <v>-9</v>
-      </c>
-      <c r="O15" s="1">
-        <v>3</v>
-      </c>
-      <c r="P15" s="1">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>8</v>
-      </c>
-      <c r="R15" s="1">
-        <v>19</v>
-      </c>
-      <c r="S15" s="1">
-        <v>2</v>
-      </c>
-      <c r="T15" s="1">
-        <v>2</v>
-      </c>
-      <c r="U15" s="1">
-        <v>-11</v>
-      </c>
-      <c r="V15" s="1">
-        <v>12</v>
-      </c>
-      <c r="W15" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="15.4">
-      <c r="A16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="1">
-        <v>13</v>
-      </c>
-      <c r="C16" s="1">
-        <v>-17</v>
-      </c>
-      <c r="D16" s="1">
-        <v>-15</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
-      </c>
-      <c r="F16" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>5</v>
-      </c>
-      <c r="I16" s="1">
-        <v>22</v>
-      </c>
-      <c r="J16" s="1">
-        <v>11</v>
-      </c>
-      <c r="K16" s="1">
-        <v>8</v>
-      </c>
-      <c r="L16" s="1">
-        <v>8</v>
-      </c>
-      <c r="M16" s="1">
-        <v>19</v>
-      </c>
-      <c r="N16" s="1">
-        <v>17</v>
-      </c>
-      <c r="O16" s="1">
-        <v>12</v>
-      </c>
-      <c r="P16" s="1">
-        <v>12</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>-15</v>
-      </c>
-      <c r="R16" s="1">
-        <v>23</v>
-      </c>
-      <c r="S16" s="1">
-        <v>14</v>
-      </c>
-      <c r="T16" s="1">
-        <v>13</v>
-      </c>
-      <c r="U16" s="1">
-        <v>-11</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
-      </c>
-      <c r="W16" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="15.4">
-      <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="1">
-        <v>-17</v>
-      </c>
-      <c r="C17" s="1">
-        <v>7</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>7</v>
-      </c>
-      <c r="F17" s="1">
-        <v>8</v>
-      </c>
-      <c r="G17" s="1">
-        <v>32</v>
-      </c>
-      <c r="H17" s="1">
-        <v>9</v>
-      </c>
-      <c r="I17" s="1">
-        <v>11</v>
-      </c>
-      <c r="J17" s="1">
-        <v>9</v>
-      </c>
-      <c r="K17" s="1">
-        <v>-18</v>
-      </c>
-      <c r="L17" s="1">
-        <v>-19</v>
-      </c>
-      <c r="M17" s="1">
-        <v>23</v>
-      </c>
-      <c r="N17" s="1">
-        <v>26</v>
-      </c>
-      <c r="O17" s="1">
-        <v>-18</v>
-      </c>
-      <c r="P17" s="1">
-        <v>-13</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>10</v>
-      </c>
-      <c r="R17" s="1">
-        <v>2</v>
-      </c>
-      <c r="S17" s="1">
-        <v>-10</v>
-      </c>
-      <c r="T17" s="1">
-        <v>10</v>
-      </c>
-      <c r="U17" s="1">
-        <v>17</v>
-      </c>
-      <c r="V17" s="1">
-        <v>40</v>
-      </c>
-      <c r="W17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="15.4">
-      <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1">
-        <v>19</v>
-      </c>
-      <c r="O18" s="1">
-        <v>5</v>
-      </c>
-      <c r="P18" s="1">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>5</v>
-      </c>
-      <c r="R18" s="1">
-        <v>-16</v>
-      </c>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-    </row>
-    <row r="19" spans="1:23" ht="15.4">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="1">
-        <v>8</v>
-      </c>
-      <c r="C19" s="1">
-        <v>9</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1">
-        <v>16</v>
-      </c>
-      <c r="F19" s="1">
-        <v>6</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1</v>
-      </c>
-      <c r="H19" s="1">
-        <v>9</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>13</v>
-      </c>
-      <c r="K19" s="1">
-        <v>-19</v>
-      </c>
-      <c r="L19" s="1">
-        <v>5</v>
-      </c>
-      <c r="M19" s="1">
-        <v>9</v>
-      </c>
-      <c r="N19" s="1">
-        <v>14</v>
-      </c>
-      <c r="O19" s="1">
-        <v>1</v>
-      </c>
-      <c r="P19" s="1">
-        <v>8</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>4</v>
-      </c>
-      <c r="R19" s="1">
-        <v>23</v>
-      </c>
-      <c r="S19" s="1">
-        <v>12</v>
-      </c>
-      <c r="T19" s="1">
-        <v>-16</v>
-      </c>
-      <c r="U19" s="1">
-        <v>-21</v>
-      </c>
-      <c r="V19" s="1">
-        <v>5</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="15.4">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="1">
-        <v>-1</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1">
-        <v>11</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2</v>
-      </c>
-      <c r="F20" s="1">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1">
-        <v>7</v>
-      </c>
-      <c r="H20" s="1">
-        <v>3</v>
-      </c>
-      <c r="I20" s="1">
-        <v>-1</v>
-      </c>
-      <c r="J20" s="1">
-        <v>-4</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>13</v>
-      </c>
-      <c r="N20" s="1">
-        <v>11</v>
-      </c>
-      <c r="O20" s="1">
-        <v>-2</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>10</v>
-      </c>
-      <c r="R20" s="1">
-        <v>-18</v>
-      </c>
-      <c r="S20" s="1">
-        <v>17</v>
-      </c>
-      <c r="T20" s="1">
-        <v>8</v>
-      </c>
-      <c r="U20" s="1">
-        <v>-1</v>
-      </c>
-      <c r="V20" s="1">
-        <v>2</v>
-      </c>
-      <c r="W20" s="1">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" ht="15.4">
-      <c r="A21" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="1">
-        <v>8</v>
-      </c>
-      <c r="C21" s="1">
-        <v>7</v>
-      </c>
-      <c r="D21" s="1">
-        <v>3</v>
-      </c>
-      <c r="E21" s="1">
-        <v>-15</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>6</v>
-      </c>
-      <c r="I21" s="1">
-        <v>-1</v>
-      </c>
-      <c r="J21" s="1">
-        <v>9</v>
-      </c>
-      <c r="K21" s="1">
-        <v>3</v>
-      </c>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-    </row>
-    <row r="22" spans="1:23" ht="15.4">
-      <c r="A22" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="1">
-        <v>13</v>
-      </c>
-      <c r="C22" s="1">
-        <v>-2</v>
-      </c>
-      <c r="D22" s="1">
-        <v>12</v>
-      </c>
-      <c r="E22" s="1">
-        <v>-1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>10</v>
-      </c>
-      <c r="H22" s="1">
-        <v>2</v>
-      </c>
-      <c r="I22" s="1">
-        <v>6</v>
-      </c>
-      <c r="J22" s="1">
-        <v>5</v>
-      </c>
-      <c r="K22" s="1">
-        <v>-5</v>
-      </c>
-      <c r="L22" s="1">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1">
-        <v>7</v>
-      </c>
-      <c r="N22" s="1">
-        <v>14</v>
-      </c>
-      <c r="O22" s="1">
-        <v>8</v>
-      </c>
-      <c r="P22" s="1">
-        <v>-18</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>-17</v>
-      </c>
-      <c r="R22" s="1">
-        <v>15</v>
-      </c>
-      <c r="S22" s="1">
-        <v>10</v>
-      </c>
-      <c r="T22" s="1">
-        <v>2</v>
-      </c>
-      <c r="U22" s="1">
-        <v>-19</v>
-      </c>
-      <c r="V22" s="1">
-        <v>-5</v>
-      </c>
-      <c r="W22" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" ht="15.4">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="1">
-        <v>11</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1">
-        <v>5</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1">
-        <v>-19</v>
-      </c>
-      <c r="J23" s="1">
-        <v>19</v>
-      </c>
-      <c r="K23" s="1">
-        <v>6</v>
-      </c>
-      <c r="L23" s="1">
-        <v>2</v>
-      </c>
-      <c r="M23" s="1">
-        <v>3</v>
-      </c>
-      <c r="N23" s="1">
-        <v>-18</v>
-      </c>
-      <c r="O23" s="1">
-        <v>3</v>
-      </c>
-      <c r="P23" s="1">
-        <v>6</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>-21</v>
-      </c>
-      <c r="R23" s="1">
-        <v>-34</v>
-      </c>
-      <c r="S23" s="1">
-        <v>16</v>
-      </c>
-      <c r="T23" s="1">
-        <v>6</v>
-      </c>
-      <c r="U23" s="1">
-        <v>12</v>
-      </c>
-      <c r="V23" s="1">
-        <v>-3</v>
-      </c>
-      <c r="W23" s="1">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C709F97C-B718-4ECA-9F57-0E1176793480}">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -7201,7 +5126,7 @@
     </row>
     <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1">
@@ -7538,7 +5463,7 @@
     </row>
     <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1">
         <v>31</v>
@@ -7615,7 +5540,7 @@
     </row>
     <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -7648,7 +5573,7 @@
     </row>
     <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -7679,7 +5604,7 @@
     </row>
     <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1">
         <v>7</v>
@@ -7752,7 +5677,7 @@
     </row>
     <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B14" s="1">
         <v>7</v>
@@ -7829,7 +5754,7 @@
     </row>
     <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -7870,7 +5795,7 @@
     </row>
     <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1">
         <v>7</v>
@@ -7945,7 +5870,7 @@
     </row>
     <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B17" s="1">
         <v>11</v>
@@ -7954,7 +5879,7 @@
         <v>-2</v>
       </c>
       <c r="D17" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E17" s="1">
         <v>-17</v>
@@ -8022,7 +5947,7 @@
     </row>
     <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1">
         <v>5</v>
@@ -8164,7 +6089,7 @@
     </row>
     <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1">
         <v>8</v>
@@ -8241,7 +6166,7 @@
     </row>
     <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1">
         <v>-3</v>
@@ -8318,7 +6243,7 @@
     </row>
     <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B22" s="1">
         <v>-1</v>
@@ -8395,7 +6320,7 @@
     </row>
     <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B23" s="1">
         <v>0</v>
@@ -8472,7 +6397,7 @@
     </row>
     <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -8519,7 +6444,7 @@
     </row>
     <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B25" s="1">
         <v>3</v>
@@ -8656,7 +6581,1666 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF024181-75C9-4540-9E3A-D879D3018BB2}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:Y22"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+      <c r="N1">
+        <v>13</v>
+      </c>
+      <c r="O1">
+        <v>14</v>
+      </c>
+      <c r="P1">
+        <v>15</v>
+      </c>
+      <c r="Q1">
+        <v>16</v>
+      </c>
+      <c r="R1">
+        <v>17</v>
+      </c>
+      <c r="S1">
+        <v>18</v>
+      </c>
+      <c r="T1">
+        <v>19</v>
+      </c>
+      <c r="U1">
+        <v>20</v>
+      </c>
+      <c r="V1">
+        <v>21</v>
+      </c>
+      <c r="W1">
+        <v>22</v>
+      </c>
+      <c r="X1">
+        <v>23</v>
+      </c>
+      <c r="Y1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="15.4">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1">
+        <v>29</v>
+      </c>
+      <c r="C2" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="D2" s="1">
+        <v>29.6</v>
+      </c>
+      <c r="E2" s="1">
+        <v>29.9</v>
+      </c>
+      <c r="F2" s="1">
+        <v>30</v>
+      </c>
+      <c r="G2" s="1">
+        <v>30.1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>30.7</v>
+      </c>
+      <c r="J2" s="1">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1">
+        <v>31.1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>31</v>
+      </c>
+      <c r="M2" s="1">
+        <v>30.9</v>
+      </c>
+      <c r="N2" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="O2" s="1">
+        <v>31.1</v>
+      </c>
+      <c r="P2" s="1">
+        <v>31.4</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>31.3</v>
+      </c>
+      <c r="R2" s="1">
+        <v>31.2</v>
+      </c>
+      <c r="S2" s="1">
+        <v>30.9</v>
+      </c>
+      <c r="T2" s="1">
+        <v>30.8</v>
+      </c>
+      <c r="U2" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="V2" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="W2" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="X2" s="1">
+        <v>30.4</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="15.4">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="1">
+        <v>28.4</v>
+      </c>
+      <c r="C3" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="D3" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>28.7</v>
+      </c>
+      <c r="F3" s="1">
+        <v>28.8</v>
+      </c>
+      <c r="G3" s="1">
+        <v>28.9</v>
+      </c>
+      <c r="H3" s="1">
+        <v>28.8</v>
+      </c>
+      <c r="I3" s="1">
+        <v>29.1</v>
+      </c>
+      <c r="J3" s="1">
+        <v>29.2</v>
+      </c>
+      <c r="K3" s="1">
+        <v>29.3</v>
+      </c>
+      <c r="L3" s="1">
+        <v>29.2</v>
+      </c>
+      <c r="M3" s="1">
+        <v>28.9</v>
+      </c>
+      <c r="N3" s="1">
+        <v>28.6</v>
+      </c>
+      <c r="O3" s="1">
+        <v>28.3</v>
+      </c>
+      <c r="P3" s="1">
+        <v>28.2</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>28.1</v>
+      </c>
+      <c r="R3" s="1">
+        <v>28.2</v>
+      </c>
+      <c r="S3" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="T3" s="1">
+        <v>28.8</v>
+      </c>
+      <c r="U3" s="1">
+        <v>29.1</v>
+      </c>
+      <c r="V3" s="1">
+        <v>29.2</v>
+      </c>
+      <c r="W3" s="1">
+        <v>29.5</v>
+      </c>
+      <c r="X3" s="1">
+        <v>29.8</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="15.4">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1">
+        <v>23</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22.7</v>
+      </c>
+      <c r="D4" s="1">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1">
+        <v>23.1</v>
+      </c>
+      <c r="F4" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="G4" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="H4" s="1">
+        <v>24</v>
+      </c>
+      <c r="I4" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="J4" s="1">
+        <v>24.6</v>
+      </c>
+      <c r="K4" s="1">
+        <v>24.9</v>
+      </c>
+      <c r="L4" s="1">
+        <v>25.2</v>
+      </c>
+      <c r="M4" s="1">
+        <v>25.5</v>
+      </c>
+      <c r="N4" s="1">
+        <v>25.8</v>
+      </c>
+      <c r="O4" s="1">
+        <v>26.1</v>
+      </c>
+      <c r="P4" s="1">
+        <v>26.4</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>26.7</v>
+      </c>
+      <c r="R4" s="1">
+        <v>27</v>
+      </c>
+      <c r="S4" s="1">
+        <v>26.9</v>
+      </c>
+      <c r="T4" s="1">
+        <v>26.6</v>
+      </c>
+      <c r="U4" s="1">
+        <v>26.3</v>
+      </c>
+      <c r="V4" s="1">
+        <v>26</v>
+      </c>
+      <c r="W4" s="1">
+        <v>25.7</v>
+      </c>
+      <c r="X4" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="15.4">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1">
+        <v>25.9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>25.6</v>
+      </c>
+      <c r="D5" s="1">
+        <v>25.3</v>
+      </c>
+      <c r="E5" s="1">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1">
+        <v>24.7</v>
+      </c>
+      <c r="G5" s="1">
+        <v>24.6</v>
+      </c>
+      <c r="H5" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>24</v>
+      </c>
+      <c r="J5" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="K5" s="1">
+        <v>24.2</v>
+      </c>
+      <c r="L5" s="1">
+        <v>24.3</v>
+      </c>
+      <c r="M5" s="1">
+        <v>24.4</v>
+      </c>
+      <c r="N5" s="1">
+        <v>24.1</v>
+      </c>
+      <c r="O5" s="1">
+        <v>24</v>
+      </c>
+      <c r="P5" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="R5" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="S5" s="1">
+        <v>23</v>
+      </c>
+      <c r="T5" s="1">
+        <v>22.9</v>
+      </c>
+      <c r="U5" s="1">
+        <v>23</v>
+      </c>
+      <c r="V5" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="W5" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="X5" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="Y5" s="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="15.4">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1">
+        <v>24.2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>23.9</v>
+      </c>
+      <c r="D6" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="E6" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="F6" s="1">
+        <v>23.2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="I6" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="J6" s="1">
+        <v>23.8</v>
+      </c>
+      <c r="K6" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="L6" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="M6" s="1">
+        <v>23.5</v>
+      </c>
+      <c r="N6" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="O6" s="1">
+        <v>23.7</v>
+      </c>
+      <c r="P6" s="1">
+        <v>23.8</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>23.5</v>
+      </c>
+      <c r="R6" s="1">
+        <v>23.2</v>
+      </c>
+      <c r="S6" s="1">
+        <v>22.9</v>
+      </c>
+      <c r="T6" s="1">
+        <v>22.8</v>
+      </c>
+      <c r="U6" s="1">
+        <v>22.7</v>
+      </c>
+      <c r="V6" s="1">
+        <v>22.8</v>
+      </c>
+      <c r="W6" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="X6" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="15.4">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1">
+        <v>21.1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>21.4</v>
+      </c>
+      <c r="E7" s="1">
+        <v>21.7</v>
+      </c>
+      <c r="F7" s="1">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1">
+        <v>22.1</v>
+      </c>
+      <c r="H7" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>22.3</v>
+      </c>
+      <c r="J7" s="1">
+        <v>22.2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>21.9</v>
+      </c>
+      <c r="L7" s="1">
+        <v>22</v>
+      </c>
+      <c r="M7" s="1">
+        <v>22.3</v>
+      </c>
+      <c r="N7" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="O7" s="1">
+        <v>22.3</v>
+      </c>
+      <c r="P7" s="1">
+        <v>22.4</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="R7" s="1">
+        <v>22.6</v>
+      </c>
+      <c r="S7" s="1">
+        <v>22.7</v>
+      </c>
+      <c r="T7" s="1">
+        <v>23</v>
+      </c>
+      <c r="U7" s="1">
+        <v>23.3</v>
+      </c>
+      <c r="V7" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="W7" s="1">
+        <v>23.5</v>
+      </c>
+      <c r="X7" s="1">
+        <v>23.6</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="15.4">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="1">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D8" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="F8" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="H8" s="1">
+        <v>6</v>
+      </c>
+      <c r="I8" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="K8" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="L8" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="M8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="N8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="P8" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R8" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="S8" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="T8" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="U8" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="V8" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="W8" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="X8" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="15.4">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="C9" s="1">
+        <v>19</v>
+      </c>
+      <c r="D9" s="1">
+        <v>19.3</v>
+      </c>
+      <c r="E9" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="F9" s="1">
+        <v>19.7</v>
+      </c>
+      <c r="G9" s="1">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="J9" s="1">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="K9" s="1">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="L9" s="1">
+        <v>18.3</v>
+      </c>
+      <c r="M9" s="1">
+        <v>17.7</v>
+      </c>
+      <c r="N9" s="1">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="O9" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="P9" s="1">
+        <v>15.9</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="R9" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="S9" s="1">
+        <v>14.9</v>
+      </c>
+      <c r="T9" s="1">
+        <v>15.1</v>
+      </c>
+      <c r="U9" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="V9" s="1">
+        <v>16.3</v>
+      </c>
+      <c r="W9" s="1">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="X9" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15.4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>16.8</v>
+      </c>
+      <c r="E10" s="1">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="F10" s="1">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="G10" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="H10" s="1">
+        <v>15.2</v>
+      </c>
+      <c r="I10" s="1">
+        <v>14.6</v>
+      </c>
+      <c r="J10" s="1">
+        <v>14.4</v>
+      </c>
+      <c r="K10" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="L10" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="M10" s="1">
+        <v>13</v>
+      </c>
+      <c r="N10" s="1">
+        <v>12.4</v>
+      </c>
+      <c r="O10" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="P10" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="R10" s="1">
+        <v>10</v>
+      </c>
+      <c r="S10" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="T10" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="U10" s="1">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="V10" s="1">
+        <v>10.8</v>
+      </c>
+      <c r="W10" s="1">
+        <v>11.4</v>
+      </c>
+      <c r="X10" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="15.4">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1">
+        <v>12.6</v>
+      </c>
+      <c r="D11" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="E11" s="1">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="G11" s="1">
+        <v>12.6</v>
+      </c>
+      <c r="H11" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="I11" s="1">
+        <v>13.4</v>
+      </c>
+      <c r="J11" s="1">
+        <v>13.6</v>
+      </c>
+      <c r="K11" s="1">
+        <v>13</v>
+      </c>
+      <c r="L11" s="1">
+        <v>12.4</v>
+      </c>
+      <c r="M11" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="O11" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="P11" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="R11" s="1">
+        <v>12.4</v>
+      </c>
+      <c r="S11" s="1">
+        <v>13</v>
+      </c>
+      <c r="T11" s="1">
+        <v>12.8</v>
+      </c>
+      <c r="U11" s="1">
+        <v>13</v>
+      </c>
+      <c r="V11" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="W11" s="1">
+        <v>13.8</v>
+      </c>
+      <c r="X11" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="15.4">
+      <c r="A12" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E12" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="F12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G12" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="I12" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="J12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="M12" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="N12" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="O12" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="P12" s="1">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>10.3</v>
+      </c>
+      <c r="R12" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="S12" s="1">
+        <v>9.9</v>
+      </c>
+      <c r="T12" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="U12" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V12" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="W12" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="X12" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="Y12" s="1">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="15.4">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="1">
+        <v>13.1</v>
+      </c>
+      <c r="C13" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>11.9</v>
+      </c>
+      <c r="E13" s="1">
+        <v>11.3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10.7</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10.1</v>
+      </c>
+      <c r="H13" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="I13" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J13" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="K13" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="L13" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="M13" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="N13" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="O13" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="P13" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="R13" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="S13" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="T13" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="U13" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="V13" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="W13" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="X13" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="Y13" s="1">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="15.4">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="C14" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F14" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G14" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="I14" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="J14" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="K14" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="L14" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="M14" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="O14" s="1">
+        <v>9.1</v>
+      </c>
+      <c r="P14" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="R14" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="S14" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="T14" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="U14" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="V14" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="W14" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="X14" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15.4">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="G15" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="1">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I15" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="J15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="M15" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="N15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="O15" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="P15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="R15" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="S15" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="T15" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="U15" s="1">
+        <v>7.7</v>
+      </c>
+      <c r="V15" s="1">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="W15" s="1">
+        <v>8.9</v>
+      </c>
+      <c r="X15" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="15.4">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="C16" s="1">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="F16" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="G16" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="H16" s="1">
+        <v>6</v>
+      </c>
+      <c r="I16" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>6</v>
+      </c>
+      <c r="K16" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="L16" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="M16" s="1">
+        <v>7.8</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.4</v>
+      </c>
+      <c r="O16" s="1">
+        <v>9</v>
+      </c>
+      <c r="P16" s="1">
+        <v>9.6</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="R16" s="1">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="S16" s="1">
+        <v>8.6</v>
+      </c>
+      <c r="T16" s="1">
+        <v>8</v>
+      </c>
+      <c r="U16" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="V16" s="1">
+        <v>6.8</v>
+      </c>
+      <c r="W16" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="X16" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="15.4">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1">
+        <v>11.8</v>
+      </c>
+      <c r="C17" s="1">
+        <v>11.2</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10.6</v>
+      </c>
+      <c r="E17" s="1">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1">
+        <v>9.4</v>
+      </c>
+      <c r="G17" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H17" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I17" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="J17" s="1">
+        <v>7</v>
+      </c>
+      <c r="K17" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5.8</v>
+      </c>
+      <c r="M17" s="1">
+        <v>6</v>
+      </c>
+      <c r="N17" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="O17" s="1">
+        <v>6</v>
+      </c>
+      <c r="P17" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="R17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="S17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="T17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="U17" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="V17" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="W17" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="X17" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="15.4">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="C18" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D18" s="1">
+        <v>7.6</v>
+      </c>
+      <c r="E18" s="1">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>6.4</v>
+      </c>
+      <c r="G18" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>5</v>
+      </c>
+      <c r="J18" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="M18" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="N18" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="O18" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="P18" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>8.1</v>
+      </c>
+      <c r="R18" s="1">
+        <v>7.9</v>
+      </c>
+      <c r="S18" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="T18" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="U18" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="V18" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="W18" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X18" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="15.4">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="1">
+        <v>7.2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="D19" s="1">
+        <v>6</v>
+      </c>
+      <c r="E19" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="F19" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>5</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+    </row>
+    <row r="20" spans="1:25" ht="15.4">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="1">
+        <v>6.2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5.3</v>
+      </c>
+      <c r="J20" s="1">
+        <v>5.5</v>
+      </c>
+      <c r="K20" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="L20" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="M20" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="N20" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="O20" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="P20" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="R20" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="S20" s="1">
+        <v>6.9</v>
+      </c>
+      <c r="T20" s="1">
+        <v>7.1</v>
+      </c>
+      <c r="U20" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="V20" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="W20" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="X20" s="1">
+        <v>6.3</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="15.4">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>5.4</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="E21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="M21" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="N21" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O21" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="P21" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R21" s="1">
+        <v>5.7</v>
+      </c>
+      <c r="S21" s="1">
+        <v>5.9</v>
+      </c>
+      <c r="T21" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="U21" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="V21" s="1">
+        <v>7.3</v>
+      </c>
+      <c r="W21" s="1">
+        <v>6.7</v>
+      </c>
+      <c r="X21" s="1">
+        <v>6.1</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="15.4">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="J22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="K22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="L22" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="M22" s="1">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="N22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="O22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="P22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="R22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="S22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="T22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="U22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="V22" s="1">
+        <v>4.7</v>
+      </c>
+      <c r="W22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="X22" s="1">
+        <v>4.5</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>4.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23388CBA-D6C2-4068-A34F-1B77189175D1}">
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
@@ -9282,7 +8866,7 @@
     </row>
     <row r="9" spans="1:25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -9436,7 +9020,7 @@
     </row>
     <row r="11" spans="1:25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2">
         <v>0</v>
@@ -9513,7 +9097,7 @@
     </row>
     <row r="12" spans="1:25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="2">
         <v>8</v>
@@ -9590,7 +9174,7 @@
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2">
         <v>20</v>
@@ -9667,7 +9251,7 @@
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2">
         <v>16</v>
@@ -9898,7 +9482,7 @@
     </row>
     <row r="17" spans="1:25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="2">
         <v>-17</v>
@@ -9975,7 +9559,7 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2">
         <v>1</v>
@@ -10052,7 +9636,7 @@
     </row>
     <row r="19" spans="1:25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2">
         <v>-20</v>
@@ -10129,7 +9713,7 @@
     </row>
     <row r="20" spans="1:25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2">
         <v>-18</v>
@@ -10206,7 +9790,7 @@
     </row>
     <row r="21" spans="1:25">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -10271,7 +9855,7 @@
     </row>
     <row r="22" spans="1:25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2">
         <v>-20</v>
@@ -10309,6 +9893,410 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E702A3C-7203-446F-AEDA-1B0D838A20DB}">
+  <sheetPr>
+    <tabColor theme="6" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>27.7</v>
+      </c>
+      <c r="C2">
+        <v>28</v>
+      </c>
+      <c r="D2">
+        <v>28.1</v>
+      </c>
+      <c r="E2">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>27.4</v>
+      </c>
+      <c r="C3">
+        <v>27.7</v>
+      </c>
+      <c r="D3">
+        <v>28</v>
+      </c>
+      <c r="E3">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>27.2</v>
+      </c>
+      <c r="C4">
+        <v>27.1</v>
+      </c>
+      <c r="D4">
+        <v>26.8</v>
+      </c>
+      <c r="E4">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>25.5</v>
+      </c>
+      <c r="C5">
+        <v>25.2</v>
+      </c>
+      <c r="D5">
+        <v>24.9</v>
+      </c>
+      <c r="E5">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
+        <v>23.2</v>
+      </c>
+      <c r="C6">
+        <v>23.5</v>
+      </c>
+      <c r="D6">
+        <v>23.8</v>
+      </c>
+      <c r="E6">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
+        <v>22.8</v>
+      </c>
+      <c r="C7">
+        <v>23.1</v>
+      </c>
+      <c r="D7">
+        <v>23.4</v>
+      </c>
+      <c r="E7">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>22.5</v>
+      </c>
+      <c r="C8">
+        <v>22.6</v>
+      </c>
+      <c r="D8">
+        <v>22.9</v>
+      </c>
+      <c r="E8">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9">
+        <v>15.1</v>
+      </c>
+      <c r="C9">
+        <v>14.5</v>
+      </c>
+      <c r="D9">
+        <v>13.9</v>
+      </c>
+      <c r="E9">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>12.2</v>
+      </c>
+      <c r="D10">
+        <v>12.8</v>
+      </c>
+      <c r="E10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11">
+        <v>11.8</v>
+      </c>
+      <c r="C11">
+        <v>11.6</v>
+      </c>
+      <c r="D11">
+        <v>12.2</v>
+      </c>
+      <c r="E11">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12">
+        <v>11.6</v>
+      </c>
+      <c r="C12">
+        <v>11.4</v>
+      </c>
+      <c r="D12">
+        <v>10.8</v>
+      </c>
+      <c r="E12">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>9.4</v>
+      </c>
+      <c r="D13">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E13">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>7.4</v>
+      </c>
+      <c r="D14">
+        <v>6.8</v>
+      </c>
+      <c r="E14">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15">
+        <v>7.4</v>
+      </c>
+      <c r="C15">
+        <v>8</v>
+      </c>
+      <c r="D15">
+        <v>8.6</v>
+      </c>
+      <c r="E15">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16">
+        <v>7.3</v>
+      </c>
+      <c r="C16">
+        <v>7.9</v>
+      </c>
+      <c r="D16">
+        <v>8.5</v>
+      </c>
+      <c r="E16">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17">
+        <v>6.8</v>
+      </c>
+      <c r="C17">
+        <v>6.2</v>
+      </c>
+      <c r="D17">
+        <v>5.6</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18">
+        <v>6.5</v>
+      </c>
+      <c r="C18">
+        <v>6.3</v>
+      </c>
+      <c r="D18">
+        <v>6.9</v>
+      </c>
+      <c r="E18">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19">
+        <v>6.4</v>
+      </c>
+      <c r="C19">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>6.4</v>
+      </c>
+      <c r="E19">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20">
+        <v>6.2</v>
+      </c>
+      <c r="C20">
+        <v>6.8</v>
+      </c>
+      <c r="D20">
+        <v>7.4</v>
+      </c>
+      <c r="E20">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21">
+        <v>6.2</v>
+      </c>
+      <c r="C21">
+        <v>6.4</v>
+      </c>
+      <c r="D21">
+        <v>7</v>
+      </c>
+      <c r="E21">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>6</v>
+      </c>
+      <c r="C22">
+        <v>5.8</v>
+      </c>
+      <c r="D22">
+        <v>6.4</v>
+      </c>
+      <c r="E22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23">
+        <v>5.9</v>
+      </c>
+      <c r="C23">
+        <v>5.3</v>
+      </c>
+      <c r="D23">
+        <v>4.7</v>
+      </c>
+      <c r="E23">
+        <v>4.0999999999999996</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10493,7 +10481,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>-14</v>
@@ -10507,7 +10495,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>-23</v>
@@ -10521,7 +10509,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15">
         <v>20</v>
@@ -10535,7 +10523,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16">
         <v>9</v>
@@ -10549,7 +10537,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17">
         <v>-20</v>
@@ -10563,7 +10551,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18">
         <v>5</v>
@@ -10577,7 +10565,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B19">
         <v>13</v>
@@ -10591,7 +10579,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20">
         <v>15</v>
@@ -10605,7 +10593,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21">
         <v>6</v>
@@ -10619,7 +10607,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -10633,7 +10621,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B23">
         <v>-16</v>
@@ -10657,45 +10645,45 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" t="s">
         <v>49</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>50</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>53</v>
       </c>
-      <c r="F1" t="s">
+      <c r="K1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>55</v>
-      </c>
-      <c r="H1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" t="s">
-        <v>58</v>
-      </c>
-      <c r="K1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B2">
         <v>2026</v>
@@ -10704,36 +10692,36 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" t="s">
         <v>63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" t="s">
-        <v>66</v>
-      </c>
-      <c r="J2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>2026</v>
@@ -10742,36 +10730,36 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" t="s">
         <v>67</v>
-      </c>
-      <c r="K3" t="s">
-        <v>63</v>
-      </c>
-      <c r="L3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>2026</v>
@@ -10780,36 +10768,36 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" t="s">
         <v>63</v>
-      </c>
-      <c r="G4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" t="s">
-        <v>63</v>
-      </c>
-      <c r="L4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B5">
         <v>2026</v>
@@ -10818,36 +10806,36 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G5" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="L5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B6">
         <v>2026</v>
@@ -10856,36 +10844,36 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B7">
         <v>2026</v>
@@ -10894,31 +10882,31 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s">
         <v>78</v>
       </c>
-      <c r="J7" t="s">
-        <v>79</v>
-      </c>
-      <c r="K7" t="s">
-        <v>83</v>
-      </c>
       <c r="L7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -15837,7 +15825,7 @@
     </row>
     <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1">
         <v>18</v>
@@ -16121,7 +16109,7 @@
     </row>
     <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1">
         <v>8.3000000000000007</v>
@@ -16192,7 +16180,7 @@
     </row>
     <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1">
         <v>9.4</v>
@@ -16405,7 +16393,7 @@
     </row>
     <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B13" s="1">
         <v>7.5</v>
@@ -16476,7 +16464,7 @@
     </row>
     <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1">
         <v>7.8</v>
@@ -16618,7 +16606,7 @@
     </row>
     <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1">
         <v>6.7</v>
@@ -16689,7 +16677,7 @@
     </row>
     <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="B17" s="1">
         <v>4.9000000000000004</v>
@@ -16760,7 +16748,7 @@
     </row>
     <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1">
         <v>4.8</v>
@@ -16831,7 +16819,7 @@
     </row>
     <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -16868,7 +16856,7 @@
     </row>
     <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -16909,7 +16897,7 @@
     </row>
     <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B21" s="1">
         <v>5</v>
@@ -16956,7 +16944,7 @@
     </row>
     <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1">
         <v>4.3</v>
@@ -17027,7 +17015,7 @@
     </row>
     <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B23" s="1">
         <v>4</v>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44FF69F0-2F79-4E27-976C-C30B83A428A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E27BF5-1AD3-40BB-A12E-136B99E4CE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="675" windowWidth="16200" windowHeight="9307" tabRatio="864" firstSheet="11" activeTab="15" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="11" activeTab="14" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -689,9 +689,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -762,7 +762,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -833,7 +833,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -904,7 +904,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -975,7 +975,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1117,7 +1117,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1483,9 +1483,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1556,7 +1556,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2195,7 +2195,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.4">
+    <row r="12" spans="1:23" ht="15.75">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2337,7 +2337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.4">
+    <row r="13" spans="1:23" ht="15.75">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.4">
+    <row r="14" spans="1:23" ht="15.75">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.4">
+    <row r="15" spans="1:23" ht="15.75">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.4">
+    <row r="16" spans="1:23" ht="15.75">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.4">
+    <row r="17" spans="1:23" ht="15.75">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.4">
+    <row r="18" spans="1:23" ht="15.75">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -2699,7 +2699,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="15.4">
+    <row r="19" spans="1:23" ht="15.75">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.4">
+    <row r="20" spans="1:23" ht="15.75">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.4">
+    <row r="21" spans="1:23" ht="15.75">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -2888,7 +2888,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.4">
+    <row r="22" spans="1:23" ht="15.75">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.4">
+    <row r="23" spans="1:23" ht="15.75">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -3041,9 +3041,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -3120,7 +3120,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3657,7 +3657,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -3844,7 +3844,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -3875,7 +3875,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -4237,7 +4237,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4391,7 +4391,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.4">
+    <row r="23" spans="1:25" ht="15.75">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -4622,7 +4622,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.4">
+    <row r="24" spans="1:25" ht="15.75">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.4">
+    <row r="25" spans="1:25" ht="15.75">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.4">
+    <row r="26" spans="1:25" ht="15.75">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -4814,9 +4814,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -4893,7 +4893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -5124,7 +5124,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -5155,7 +5155,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -5571,7 +5571,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -5602,7 +5602,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -6010,7 +6010,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -6087,7 +6087,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -6241,7 +6241,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.4">
+    <row r="23" spans="1:25" ht="15.75">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -6395,7 +6395,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.4">
+    <row r="24" spans="1:25" ht="15.75">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.4">
+    <row r="25" spans="1:25" ht="15.75">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -6499,7 +6499,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="15.4">
+    <row r="26" spans="1:25" ht="15.75">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -6587,9 +6587,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -6666,7 +6666,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6820,7 +6820,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -6897,7 +6897,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -7205,7 +7205,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -7282,7 +7282,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -7590,7 +7590,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -7667,7 +7667,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -7821,7 +7821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7975,7 +7975,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -8016,7 +8016,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -8246,9 +8246,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -9904,13 +9904,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1">
         <v>1</v>
       </c>
@@ -9923,8 +9923,11 @@
       <c r="E1">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -9940,8 +9943,11 @@
       <c r="E2">
         <v>28.2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9957,8 +9963,11 @@
       <c r="E3">
         <v>28.3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -9974,8 +9983,11 @@
       <c r="E4">
         <v>26.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -9991,8 +10003,11 @@
       <c r="E5">
         <v>24.6</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -10008,8 +10023,11 @@
       <c r="E6">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -10025,8 +10043,11 @@
       <c r="E7">
         <v>23.7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -10042,8 +10063,11 @@
       <c r="E8">
         <v>23.2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -10059,8 +10083,11 @@
       <c r="E9">
         <v>13.3</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10076,8 +10103,11 @@
       <c r="E10">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -10093,8 +10123,11 @@
       <c r="E11">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -10110,8 +10143,11 @@
       <c r="E12">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -10127,8 +10163,11 @@
       <c r="E13">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -10144,8 +10183,11 @@
       <c r="E14">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -10161,8 +10203,11 @@
       <c r="E15">
         <v>9.1999999999999993</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -10178,8 +10223,11 @@
       <c r="E16">
         <v>9.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10195,8 +10243,11 @@
       <c r="E17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -10212,8 +10263,11 @@
       <c r="E18">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -10229,8 +10283,11 @@
       <c r="E19">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -10246,8 +10303,11 @@
       <c r="E20">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -10263,8 +10323,11 @@
       <c r="E21">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -10280,8 +10343,11 @@
       <c r="E22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -10296,6 +10362,9 @@
       </c>
       <c r="E23">
         <v>4.0999999999999996</v>
+      </c>
+      <c r="F23">
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -10308,13 +10377,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1">
         <v>1</v>
       </c>
@@ -10324,8 +10393,11 @@
       <c r="D1">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -10338,8 +10410,11 @@
       <c r="D2">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -10352,8 +10427,11 @@
       <c r="D3">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -10366,8 +10444,11 @@
       <c r="D4">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -10380,8 +10461,11 @@
       <c r="D5">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -10394,8 +10478,11 @@
       <c r="D6">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -10408,8 +10495,11 @@
       <c r="D7">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -10422,8 +10512,11 @@
       <c r="D8">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -10436,8 +10529,11 @@
       <c r="D9">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10450,8 +10546,11 @@
       <c r="D10">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -10464,8 +10563,11 @@
       <c r="D11">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -10478,8 +10580,11 @@
       <c r="D12">
         <v>-1</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -10492,8 +10597,11 @@
       <c r="D13">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -10506,8 +10614,11 @@
       <c r="D14">
         <v>-17</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -10520,8 +10631,11 @@
       <c r="D15">
         <v>-14</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -10534,8 +10648,11 @@
       <c r="D16">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10548,8 +10665,11 @@
       <c r="D17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>-29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -10562,8 +10682,11 @@
       <c r="D18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -10576,8 +10699,11 @@
       <c r="D19">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -10590,8 +10716,11 @@
       <c r="D20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -10604,8 +10733,11 @@
       <c r="D21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -10618,8 +10750,11 @@
       <c r="D22">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -10631,6 +10766,9 @@
       </c>
       <c r="D23">
         <v>2</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10641,7 +10779,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008844FF-9942-4BA0-9033-82ED2D862880}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
@@ -10920,9 +11058,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -10999,7 +11137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11076,7 +11214,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -11153,7 +11291,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11230,7 +11368,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11307,7 +11445,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -11384,7 +11522,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -11461,7 +11599,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -11538,7 +11676,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -11615,7 +11753,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -11692,7 +11830,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -11780,7 +11918,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -11856,7 +11994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -11933,7 +12071,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12010,7 +12148,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -12087,7 +12225,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -12164,7 +12302,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -12241,7 +12379,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -12318,7 +12456,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -12395,7 +12533,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -12472,7 +12610,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -12549,7 +12687,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -12637,7 +12775,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="B1">
@@ -12851,7 +12989,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="V1:AR11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="22:44">
       <c r="W1">
@@ -12921,7 +13059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="22:44" ht="15.4">
+    <row r="2" spans="22:44" ht="15.75">
       <c r="V2" t="s">
         <v>0</v>
       </c>
@@ -12992,7 +13130,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="22:44" ht="15.4">
+    <row r="3" spans="22:44" ht="15.75">
       <c r="V3" t="s">
         <v>2</v>
       </c>
@@ -13063,7 +13201,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="22:44" ht="15.4">
+    <row r="4" spans="22:44" ht="15.75">
       <c r="V4" t="s">
         <v>3</v>
       </c>
@@ -13134,7 +13272,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="22:44" ht="15.4">
+    <row r="5" spans="22:44" ht="15.75">
       <c r="V5" t="s">
         <v>4</v>
       </c>
@@ -13205,7 +13343,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="22:44" ht="15.4">
+    <row r="6" spans="22:44" ht="15.75">
       <c r="V6" t="s">
         <v>1</v>
       </c>
@@ -13276,7 +13414,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="22:44" ht="15.4">
+    <row r="7" spans="22:44" ht="15.75">
       <c r="V7" t="s">
         <v>5</v>
       </c>
@@ -13347,7 +13485,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="22:44" ht="15.4">
+    <row r="8" spans="22:44" ht="15.75">
       <c r="V8" t="s">
         <v>6</v>
       </c>
@@ -13418,7 +13556,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="22:44" ht="15.4">
+    <row r="9" spans="22:44" ht="15.75">
       <c r="V9" t="s">
         <v>7</v>
       </c>
@@ -13489,7 +13627,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="22:44" ht="15.4">
+    <row r="10" spans="22:44" ht="15.75">
       <c r="V10" t="s">
         <v>9</v>
       </c>
@@ -13560,7 +13698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="22:44" ht="15.4">
+    <row r="11" spans="22:44" ht="15.75">
       <c r="V11" t="s">
         <v>8</v>
       </c>
@@ -13642,7 +13780,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -13718,7 +13856,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -13795,7 +13933,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -13872,7 +14010,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13949,7 +14087,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -14026,7 +14164,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -14103,7 +14241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -14180,7 +14318,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -14257,7 +14395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -14334,7 +14472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -14411,7 +14549,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -14499,7 +14637,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="BR1:CP11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="70:94">
       <c r="BS1">
@@ -15356,9 +15494,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -15537,9 +15675,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1">
@@ -15610,7 +15748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -15681,7 +15819,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -15752,7 +15890,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -15823,7 +15961,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -15894,7 +16032,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -15965,7 +16103,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -16036,7 +16174,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -16107,7 +16245,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -16178,7 +16316,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -16249,7 +16387,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -16320,7 +16458,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.4">
+    <row r="12" spans="1:23" ht="15.75">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -16391,7 +16529,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.4">
+    <row r="13" spans="1:23" ht="15.75">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -16462,7 +16600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.4">
+    <row r="14" spans="1:23" ht="15.75">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -16533,7 +16671,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.4">
+    <row r="15" spans="1:23" ht="15.75">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -16604,7 +16742,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.4">
+    <row r="16" spans="1:23" ht="15.75">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -16675,7 +16813,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.4">
+    <row r="17" spans="1:23" ht="15.75">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -16746,7 +16884,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.4">
+    <row r="18" spans="1:23" ht="15.75">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -16817,7 +16955,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.4">
+    <row r="19" spans="1:23" ht="15.75">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -16854,7 +16992,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" ht="15.4">
+    <row r="20" spans="1:23" ht="15.75">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -16895,7 +17033,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.4">
+    <row r="21" spans="1:23" ht="15.75">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -16942,7 +17080,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.4">
+    <row r="22" spans="1:23" ht="15.75">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -17013,7 +17151,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.4">
+    <row r="23" spans="1:23" ht="15.75">
       <c r="A23" t="s">
         <v>41</v>
       </c>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E27BF5-1AD3-40BB-A12E-136B99E4CE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE86E263-1D2E-4458-9534-3A0137ACD6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="11" activeTab="14" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="11" activeTab="15" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -9921,10 +9921,10 @@
         <v>3</v>
       </c>
       <c r="E1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F1">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -10394,7 +10394,7 @@
         <v>3</v>
       </c>
       <c r="E1">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5">

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE86E263-1D2E-4458-9534-3A0137ACD6EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3DB95D-C8CE-4418-8532-9F9FAC556734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="11" activeTab="15" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="3060" yWindow="1650" windowWidth="21600" windowHeight="11055" tabRatio="864" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -12774,10 +12774,10 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1">
         <v>1</v>
       </c>
@@ -12788,10 +12788,13 @@
         <v>3</v>
       </c>
       <c r="E1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>6</v>
+      </c>
+      <c r="F1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -12807,8 +12810,11 @@
       <c r="E2">
         <v>30.2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -12824,8 +12830,11 @@
       <c r="E3">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -12841,8 +12850,11 @@
       <c r="E4">
         <v>29.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -12858,8 +12870,11 @@
       <c r="E5">
         <v>24.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -12875,8 +12890,11 @@
       <c r="E6">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -12892,8 +12910,11 @@
       <c r="E7">
         <v>13.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -12909,8 +12930,11 @@
       <c r="E8">
         <v>8.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -12926,8 +12950,11 @@
       <c r="E9">
         <v>9.1999999999999993</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -12943,8 +12970,11 @@
       <c r="E10">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -12960,8 +12990,11 @@
       <c r="E11">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -12976,6 +13009,9 @@
       </c>
       <c r="E12">
         <v>5</v>
+      </c>
+      <c r="F12">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -12988,784 +13024,784 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="V1:AR11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="22:44">
+    <row r="1" spans="1:23">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>7</v>
+      </c>
+      <c r="H1">
+        <v>8</v>
+      </c>
+      <c r="I1">
+        <v>9</v>
+      </c>
+      <c r="J1">
+        <v>10</v>
+      </c>
+      <c r="K1">
+        <v>11</v>
+      </c>
+      <c r="L1">
+        <v>12</v>
+      </c>
+      <c r="M1">
+        <v>13</v>
+      </c>
+      <c r="N1">
+        <v>14</v>
+      </c>
+      <c r="O1">
+        <v>15</v>
+      </c>
+      <c r="P1">
+        <v>16</v>
+      </c>
+      <c r="Q1">
+        <v>17</v>
+      </c>
+      <c r="R1">
+        <v>18</v>
+      </c>
+      <c r="S1">
+        <v>19</v>
+      </c>
+      <c r="T1">
+        <v>20</v>
+      </c>
+      <c r="U1">
+        <v>21</v>
+      </c>
+      <c r="V1">
+        <v>22</v>
+      </c>
       <c r="W1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15.75">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <v>78</v>
+      </c>
+      <c r="C2" s="1">
+        <v>95</v>
+      </c>
+      <c r="D2" s="1">
+        <v>98</v>
+      </c>
+      <c r="E2" s="1">
+        <v>108</v>
+      </c>
+      <c r="F2" s="1">
+        <v>97</v>
+      </c>
+      <c r="G2" s="1">
+        <v>63</v>
+      </c>
+      <c r="H2" s="1">
+        <v>96</v>
+      </c>
+      <c r="I2" s="1">
+        <v>86</v>
+      </c>
+      <c r="J2" s="1">
+        <v>112</v>
+      </c>
+      <c r="K2" s="1">
+        <v>77</v>
+      </c>
+      <c r="L2" s="1">
+        <v>95</v>
+      </c>
+      <c r="M2" s="1">
+        <v>80</v>
+      </c>
+      <c r="N2" s="1">
+        <v>101</v>
+      </c>
+      <c r="O2" s="1">
+        <v>81</v>
+      </c>
+      <c r="P2" s="1">
+        <v>54</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>46</v>
+      </c>
+      <c r="R2" s="1">
+        <v>64</v>
+      </c>
+      <c r="S2" s="1">
+        <v>95</v>
+      </c>
+      <c r="T2" s="1">
+        <v>45</v>
+      </c>
+      <c r="U2" s="1">
+        <v>105</v>
+      </c>
+      <c r="V2" s="1">
+        <v>84</v>
+      </c>
+      <c r="W2" s="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15.75">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1">
+        <v>44</v>
+      </c>
+      <c r="D3" s="1">
+        <v>32</v>
+      </c>
+      <c r="E3" s="1">
+        <v>49</v>
+      </c>
+      <c r="F3" s="1">
+        <v>57</v>
+      </c>
+      <c r="G3" s="1">
+        <v>54</v>
+      </c>
+      <c r="H3" s="1">
+        <v>65</v>
+      </c>
+      <c r="I3" s="1">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1">
+        <v>70</v>
+      </c>
+      <c r="K3" s="1">
+        <v>53</v>
+      </c>
+      <c r="L3" s="1">
+        <v>52</v>
+      </c>
+      <c r="M3" s="1">
+        <v>70</v>
+      </c>
+      <c r="N3" s="1">
+        <v>40</v>
+      </c>
+      <c r="O3" s="1">
+        <v>44</v>
+      </c>
+      <c r="P3" s="1">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>44</v>
+      </c>
+      <c r="R3" s="1">
+        <v>53</v>
+      </c>
+      <c r="S3" s="1">
+        <v>21</v>
+      </c>
+      <c r="T3" s="1">
+        <v>69</v>
+      </c>
+      <c r="U3" s="1">
+        <v>24</v>
+      </c>
+      <c r="V3" s="1">
+        <v>45</v>
+      </c>
+      <c r="W3" s="1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15.75">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1">
+        <v>59</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>63</v>
+      </c>
+      <c r="F4" s="1">
+        <v>56</v>
+      </c>
+      <c r="G4" s="1">
+        <v>37</v>
+      </c>
+      <c r="H4" s="1">
+        <v>38</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46</v>
+      </c>
+      <c r="J4" s="1">
+        <v>73</v>
+      </c>
+      <c r="K4" s="1">
+        <v>25</v>
+      </c>
+      <c r="L4" s="1">
+        <v>32</v>
+      </c>
+      <c r="M4" s="1">
+        <v>38</v>
+      </c>
+      <c r="N4" s="1">
+        <v>34</v>
+      </c>
+      <c r="O4" s="1">
+        <v>67</v>
+      </c>
+      <c r="P4" s="1">
+        <v>70</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>65</v>
+      </c>
+      <c r="R4" s="1">
+        <v>18</v>
+      </c>
+      <c r="S4" s="1">
+        <v>25</v>
+      </c>
+      <c r="T4" s="1">
+        <v>63</v>
+      </c>
+      <c r="U4" s="1">
+        <v>28</v>
+      </c>
+      <c r="V4" s="1">
+        <v>78</v>
+      </c>
+      <c r="W4" s="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.75">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>-16</v>
+      </c>
+      <c r="C5" s="1">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1">
+        <v>11</v>
+      </c>
+      <c r="I5" s="1">
+        <v>15</v>
+      </c>
+      <c r="J5" s="1">
+        <v>54</v>
+      </c>
+      <c r="K5" s="1">
+        <v>68</v>
+      </c>
+      <c r="L5" s="1">
+        <v>62</v>
+      </c>
+      <c r="M5" s="1">
+        <v>18</v>
+      </c>
+      <c r="N5" s="1">
+        <v>56</v>
+      </c>
+      <c r="O5" s="1">
+        <v>44</v>
+      </c>
+      <c r="P5" s="1">
+        <v>64</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>66</v>
+      </c>
+      <c r="R5" s="1">
+        <v>110</v>
+      </c>
+      <c r="S5" s="1">
+        <v>36</v>
+      </c>
+      <c r="T5" s="1">
+        <v>57</v>
+      </c>
+      <c r="U5" s="1">
+        <v>65</v>
+      </c>
+      <c r="V5" s="1">
+        <v>34</v>
+      </c>
+      <c r="W5" s="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15.75">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="X1">
+      <c r="B6" s="1">
+        <v>56</v>
+      </c>
+      <c r="C6" s="1">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1">
+        <v>54</v>
+      </c>
+      <c r="E6" s="1">
+        <v>55</v>
+      </c>
+      <c r="F6" s="1">
+        <v>42</v>
+      </c>
+      <c r="G6" s="1">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1">
+        <v>40</v>
+      </c>
+      <c r="I6" s="1">
+        <v>46</v>
+      </c>
+      <c r="J6" s="1">
+        <v>63</v>
+      </c>
+      <c r="K6" s="1">
+        <v>22</v>
+      </c>
+      <c r="L6" s="1">
+        <v>21</v>
+      </c>
+      <c r="M6" s="1">
+        <v>24</v>
+      </c>
+      <c r="N6" s="1">
+        <v>67</v>
+      </c>
+      <c r="O6" s="1">
+        <v>17</v>
+      </c>
+      <c r="P6" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>7</v>
+      </c>
+      <c r="R6" s="1">
+        <v>47</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1">
+        <v>-7</v>
+      </c>
+      <c r="U6" s="1">
+        <v>77</v>
+      </c>
+      <c r="V6" s="1">
+        <v>56</v>
+      </c>
+      <c r="W6" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15.75">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1">
+        <v>28</v>
+      </c>
+      <c r="G7" s="1">
+        <v>42</v>
+      </c>
+      <c r="H7" s="1">
+        <v>33</v>
+      </c>
+      <c r="I7" s="1">
+        <v>24</v>
+      </c>
+      <c r="J7" s="1">
+        <v>21</v>
+      </c>
+      <c r="K7" s="1">
+        <v>-16</v>
+      </c>
+      <c r="L7" s="1">
+        <v>-35</v>
+      </c>
+      <c r="M7" s="1">
+        <v>43</v>
+      </c>
+      <c r="N7" s="1">
+        <v>66</v>
+      </c>
+      <c r="O7" s="1">
+        <v>-16</v>
+      </c>
+      <c r="P7" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>20</v>
+      </c>
+      <c r="R7" s="1">
+        <v>23</v>
+      </c>
+      <c r="S7" s="1">
+        <v>27</v>
+      </c>
+      <c r="T7" s="1">
+        <v>21</v>
+      </c>
+      <c r="U7" s="1">
+        <v>44</v>
+      </c>
+      <c r="V7" s="1">
+        <v>46</v>
+      </c>
+      <c r="W7" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15.75">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1">
+        <v>13</v>
+      </c>
+      <c r="E8" s="1">
+        <v>-23</v>
+      </c>
+      <c r="F8" s="1">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1">
+        <v>6</v>
+      </c>
+      <c r="J8" s="1">
+        <v>20</v>
+      </c>
+      <c r="K8" s="1">
+        <v>5</v>
+      </c>
+      <c r="L8" s="1">
+        <v>8</v>
+      </c>
+      <c r="M8" s="1">
+        <v>18</v>
+      </c>
+      <c r="N8" s="1">
+        <v>40</v>
+      </c>
+      <c r="O8" s="1">
+        <v>-12</v>
+      </c>
+      <c r="P8" s="1">
+        <v>-4</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>15</v>
+      </c>
+      <c r="R8" s="1">
+        <v>-4</v>
+      </c>
+      <c r="S8" s="1">
+        <v>34</v>
+      </c>
+      <c r="T8" s="1">
+        <v>42</v>
+      </c>
+      <c r="U8" s="1">
+        <v>31</v>
+      </c>
+      <c r="V8" s="1">
+        <v>26</v>
+      </c>
+      <c r="W8" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="15.75">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-10</v>
+      </c>
+      <c r="F9" s="1">
+        <v>8</v>
+      </c>
+      <c r="G9" s="1">
+        <v>22</v>
+      </c>
+      <c r="H9" s="1">
+        <v>19</v>
+      </c>
+      <c r="I9" s="1">
+        <v>11</v>
+      </c>
+      <c r="J9" s="1">
+        <v>16</v>
+      </c>
+      <c r="K9" s="1">
+        <v>-5</v>
+      </c>
+      <c r="L9" s="1">
+        <v>6</v>
+      </c>
+      <c r="M9" s="1">
+        <v>26</v>
+      </c>
+      <c r="N9" s="1">
+        <v>4</v>
+      </c>
+      <c r="O9" s="1">
+        <v>12</v>
+      </c>
+      <c r="P9" s="1">
+        <v>-8</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>-10</v>
+      </c>
+      <c r="R9" s="1">
+        <v>39</v>
+      </c>
+      <c r="S9" s="1">
+        <v>15</v>
+      </c>
+      <c r="T9" s="1">
+        <v>14</v>
+      </c>
+      <c r="U9" s="1">
+        <v>-31</v>
+      </c>
+      <c r="V9" s="1">
+        <v>12</v>
+      </c>
+      <c r="W9" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15.75">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1">
+        <v>18</v>
+      </c>
+      <c r="E10" s="1">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1">
+        <v>7</v>
+      </c>
+      <c r="H10" s="1">
+        <v>17</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4</v>
+      </c>
+      <c r="J10" s="1">
+        <v>14</v>
+      </c>
+      <c r="K10" s="1">
+        <v>-18</v>
+      </c>
+      <c r="L10" s="1">
+        <v>10</v>
+      </c>
+      <c r="M10" s="1">
+        <v>23</v>
+      </c>
+      <c r="N10" s="1">
+        <v>26</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>15</v>
+      </c>
+      <c r="R10" s="1">
+        <v>6</v>
+      </c>
+      <c r="S10" s="1">
+        <v>30</v>
+      </c>
+      <c r="T10" s="1">
+        <v>-7</v>
+      </c>
+      <c r="U10" s="1">
+        <v>-19</v>
+      </c>
+      <c r="V10" s="1">
+        <v>12</v>
+      </c>
+      <c r="W10" s="1">
         <v>2</v>
       </c>
-      <c r="Y1">
-        <v>3</v>
-      </c>
-      <c r="Z1">
-        <v>4</v>
-      </c>
-      <c r="AA1">
+    </row>
+    <row r="11" spans="1:23" ht="15.75">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1">
+        <v>-16</v>
+      </c>
+      <c r="D11" s="1">
+        <v>-5</v>
+      </c>
+      <c r="E11" s="1">
         <v>5</v>
       </c>
-      <c r="AB1">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>-2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>35</v>
+      </c>
+      <c r="K11" s="1">
+        <v>19</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>21</v>
+      </c>
+      <c r="N11" s="1">
+        <v>9</v>
+      </c>
+      <c r="O11" s="1">
+        <v>20</v>
+      </c>
+      <c r="P11" s="1">
+        <v>19</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>-35</v>
+      </c>
+      <c r="R11" s="1">
+        <v>-10</v>
+      </c>
+      <c r="S11" s="1">
+        <v>29</v>
+      </c>
+      <c r="T11" s="1">
+        <v>20</v>
+      </c>
+      <c r="U11" s="1">
+        <v>2</v>
+      </c>
+      <c r="V11" s="1">
         <v>7</v>
       </c>
-      <c r="AC1">
-        <v>8</v>
-      </c>
-      <c r="AD1">
-        <v>9</v>
-      </c>
-      <c r="AE1">
-        <v>10</v>
-      </c>
-      <c r="AF1">
-        <v>11</v>
-      </c>
-      <c r="AG1">
-        <v>12</v>
-      </c>
-      <c r="AH1">
-        <v>13</v>
-      </c>
-      <c r="AI1">
-        <v>14</v>
-      </c>
-      <c r="AJ1">
-        <v>15</v>
-      </c>
-      <c r="AK1">
-        <v>16</v>
-      </c>
-      <c r="AL1">
-        <v>17</v>
-      </c>
-      <c r="AM1">
-        <v>18</v>
-      </c>
-      <c r="AN1">
-        <v>19</v>
-      </c>
-      <c r="AO1">
-        <v>20</v>
-      </c>
-      <c r="AP1">
-        <v>21</v>
-      </c>
-      <c r="AQ1">
-        <v>22</v>
-      </c>
-      <c r="AR1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="22:44" ht="15.75">
-      <c r="V2" t="s">
-        <v>0</v>
-      </c>
-      <c r="W2" s="1">
-        <v>78</v>
-      </c>
-      <c r="X2" s="1">
-        <v>95</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>98</v>
-      </c>
-      <c r="Z2" s="1">
-        <v>108</v>
-      </c>
-      <c r="AA2" s="1">
-        <v>97</v>
-      </c>
-      <c r="AB2" s="1">
-        <v>63</v>
-      </c>
-      <c r="AC2" s="1">
-        <v>96</v>
-      </c>
-      <c r="AD2" s="1">
-        <v>86</v>
-      </c>
-      <c r="AE2" s="1">
-        <v>112</v>
-      </c>
-      <c r="AF2" s="1">
-        <v>77</v>
-      </c>
-      <c r="AG2" s="1">
-        <v>95</v>
-      </c>
-      <c r="AH2" s="1">
-        <v>80</v>
-      </c>
-      <c r="AI2" s="1">
-        <v>101</v>
-      </c>
-      <c r="AJ2" s="1">
-        <v>81</v>
-      </c>
-      <c r="AK2" s="1">
-        <v>54</v>
-      </c>
-      <c r="AL2" s="1">
-        <v>46</v>
-      </c>
-      <c r="AM2" s="1">
-        <v>64</v>
-      </c>
-      <c r="AN2" s="1">
-        <v>95</v>
-      </c>
-      <c r="AO2" s="1">
-        <v>45</v>
-      </c>
-      <c r="AP2" s="1">
-        <v>105</v>
-      </c>
-      <c r="AQ2" s="1">
-        <v>84</v>
-      </c>
-      <c r="AR2" s="1">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="22:44" ht="15.75">
-      <c r="V3" t="s">
-        <v>2</v>
-      </c>
-      <c r="W3" s="1">
-        <v>45</v>
-      </c>
-      <c r="X3" s="1">
-        <v>44</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>32</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>49</v>
-      </c>
-      <c r="AA3" s="1">
-        <v>57</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>54</v>
-      </c>
-      <c r="AC3" s="1">
-        <v>65</v>
-      </c>
-      <c r="AD3" s="1">
-        <v>21</v>
-      </c>
-      <c r="AE3" s="1">
-        <v>70</v>
-      </c>
-      <c r="AF3" s="1">
-        <v>53</v>
-      </c>
-      <c r="AG3" s="1">
-        <v>52</v>
-      </c>
-      <c r="AH3" s="1">
-        <v>70</v>
-      </c>
-      <c r="AI3" s="1">
-        <v>40</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>44</v>
-      </c>
-      <c r="AK3" s="1">
-        <v>47</v>
-      </c>
-      <c r="AL3" s="1">
-        <v>44</v>
-      </c>
-      <c r="AM3" s="1">
-        <v>53</v>
-      </c>
-      <c r="AN3" s="1">
-        <v>21</v>
-      </c>
-      <c r="AO3" s="1">
-        <v>69</v>
-      </c>
-      <c r="AP3" s="1">
-        <v>24</v>
-      </c>
-      <c r="AQ3" s="1">
-        <v>45</v>
-      </c>
-      <c r="AR3" s="1">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="22:44" ht="15.75">
-      <c r="V4" t="s">
-        <v>3</v>
-      </c>
-      <c r="W4" s="1">
-        <v>31</v>
-      </c>
-      <c r="X4" s="1">
-        <v>59</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>3</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>63</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>56</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>37</v>
-      </c>
-      <c r="AC4" s="1">
-        <v>38</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>46</v>
-      </c>
-      <c r="AE4" s="1">
-        <v>73</v>
-      </c>
-      <c r="AF4" s="1">
-        <v>25</v>
-      </c>
-      <c r="AG4" s="1">
-        <v>32</v>
-      </c>
-      <c r="AH4" s="1">
-        <v>38</v>
-      </c>
-      <c r="AI4" s="1">
-        <v>34</v>
-      </c>
-      <c r="AJ4" s="1">
-        <v>67</v>
-      </c>
-      <c r="AK4" s="1">
-        <v>70</v>
-      </c>
-      <c r="AL4" s="1">
-        <v>65</v>
-      </c>
-      <c r="AM4" s="1">
-        <v>18</v>
-      </c>
-      <c r="AN4" s="1">
-        <v>25</v>
-      </c>
-      <c r="AO4" s="1">
-        <v>63</v>
-      </c>
-      <c r="AP4" s="1">
-        <v>28</v>
-      </c>
-      <c r="AQ4" s="1">
-        <v>78</v>
-      </c>
-      <c r="AR4" s="1">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="22:44" ht="15.75">
-      <c r="V5" t="s">
-        <v>4</v>
-      </c>
-      <c r="W5" s="1">
-        <v>-16</v>
-      </c>
-      <c r="X5" s="1">
-        <v>14</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>36</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>23</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>8</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>15</v>
-      </c>
-      <c r="AC5" s="1">
-        <v>11</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>15</v>
-      </c>
-      <c r="AE5" s="1">
-        <v>54</v>
-      </c>
-      <c r="AF5" s="1">
-        <v>68</v>
-      </c>
-      <c r="AG5" s="1">
-        <v>62</v>
-      </c>
-      <c r="AH5" s="1">
-        <v>18</v>
-      </c>
-      <c r="AI5" s="1">
-        <v>56</v>
-      </c>
-      <c r="AJ5" s="1">
-        <v>44</v>
-      </c>
-      <c r="AK5" s="1">
-        <v>64</v>
-      </c>
-      <c r="AL5" s="1">
-        <v>66</v>
-      </c>
-      <c r="AM5" s="1">
-        <v>110</v>
-      </c>
-      <c r="AN5" s="1">
-        <v>36</v>
-      </c>
-      <c r="AO5" s="1">
-        <v>57</v>
-      </c>
-      <c r="AP5" s="1">
-        <v>65</v>
-      </c>
-      <c r="AQ5" s="1">
-        <v>34</v>
-      </c>
-      <c r="AR5" s="1">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="22:44" ht="15.75">
-      <c r="V6" t="s">
-        <v>1</v>
-      </c>
-      <c r="W6" s="1">
-        <v>56</v>
-      </c>
-      <c r="X6" s="1">
-        <v>19</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>54</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>55</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>42</v>
-      </c>
-      <c r="AB6" s="1">
-        <v>15</v>
-      </c>
-      <c r="AC6" s="1">
-        <v>40</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>46</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>63</v>
-      </c>
-      <c r="AF6" s="1">
-        <v>22</v>
-      </c>
-      <c r="AG6" s="1">
-        <v>21</v>
-      </c>
-      <c r="AH6" s="1">
-        <v>24</v>
-      </c>
-      <c r="AI6" s="1">
-        <v>67</v>
-      </c>
-      <c r="AJ6" s="1">
-        <v>17</v>
-      </c>
-      <c r="AK6" s="1">
-        <v>4</v>
-      </c>
-      <c r="AL6" s="1">
-        <v>7</v>
-      </c>
-      <c r="AM6" s="1">
-        <v>47</v>
-      </c>
-      <c r="AN6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="1">
-        <v>-7</v>
-      </c>
-      <c r="AP6" s="1">
-        <v>77</v>
-      </c>
-      <c r="AQ6" s="1">
-        <v>56</v>
-      </c>
-      <c r="AR6" s="1">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="22:44" ht="15.75">
-      <c r="V7" t="s">
-        <v>5</v>
-      </c>
-      <c r="W7" s="1">
-        <v>8</v>
-      </c>
-      <c r="X7" s="1">
-        <v>28</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>11</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>25</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>28</v>
-      </c>
-      <c r="AB7" s="1">
-        <v>42</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>33</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>24</v>
-      </c>
-      <c r="AE7" s="1">
-        <v>21</v>
-      </c>
-      <c r="AF7" s="1">
-        <v>-16</v>
-      </c>
-      <c r="AG7" s="1">
-        <v>-35</v>
-      </c>
-      <c r="AH7" s="1">
-        <v>43</v>
-      </c>
-      <c r="AI7" s="1">
-        <v>66</v>
-      </c>
-      <c r="AJ7" s="1">
-        <v>-16</v>
-      </c>
-      <c r="AK7" s="1">
-        <v>13</v>
-      </c>
-      <c r="AL7" s="1">
-        <v>20</v>
-      </c>
-      <c r="AM7" s="1">
-        <v>23</v>
-      </c>
-      <c r="AN7" s="1">
-        <v>27</v>
-      </c>
-      <c r="AO7" s="1">
-        <v>21</v>
-      </c>
-      <c r="AP7" s="1">
-        <v>44</v>
-      </c>
-      <c r="AQ7" s="1">
-        <v>46</v>
-      </c>
-      <c r="AR7" s="1">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="22:44" ht="15.75">
-      <c r="V8" t="s">
-        <v>6</v>
-      </c>
-      <c r="W8" s="1">
-        <v>17</v>
-      </c>
-      <c r="X8" s="1">
-        <v>15</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>13</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>-23</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>17</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="1">
-        <v>20</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>6</v>
-      </c>
-      <c r="AE8" s="1">
-        <v>20</v>
-      </c>
-      <c r="AF8" s="1">
-        <v>5</v>
-      </c>
-      <c r="AG8" s="1">
-        <v>8</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>18</v>
-      </c>
-      <c r="AI8" s="1">
-        <v>40</v>
-      </c>
-      <c r="AJ8" s="1">
-        <v>-12</v>
-      </c>
-      <c r="AK8" s="1">
-        <v>-4</v>
-      </c>
-      <c r="AL8" s="1">
-        <v>15</v>
-      </c>
-      <c r="AM8" s="1">
-        <v>-4</v>
-      </c>
-      <c r="AN8" s="1">
-        <v>34</v>
-      </c>
-      <c r="AO8" s="1">
-        <v>42</v>
-      </c>
-      <c r="AP8" s="1">
-        <v>31</v>
-      </c>
-      <c r="AQ8" s="1">
-        <v>26</v>
-      </c>
-      <c r="AR8" s="1">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="22:44" ht="15.75">
-      <c r="V9" t="s">
-        <v>7</v>
-      </c>
-      <c r="W9" s="1">
-        <v>31</v>
-      </c>
-      <c r="X9" s="1">
-        <v>7</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>26</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>-10</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>22</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>19</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>11</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>16</v>
-      </c>
-      <c r="AF9" s="1">
-        <v>-5</v>
-      </c>
-      <c r="AG9" s="1">
-        <v>6</v>
-      </c>
-      <c r="AH9" s="1">
-        <v>26</v>
-      </c>
-      <c r="AI9" s="1">
-        <v>4</v>
-      </c>
-      <c r="AJ9" s="1">
-        <v>12</v>
-      </c>
-      <c r="AK9" s="1">
-        <v>-8</v>
-      </c>
-      <c r="AL9" s="1">
-        <v>-10</v>
-      </c>
-      <c r="AM9" s="1">
-        <v>39</v>
-      </c>
-      <c r="AN9" s="1">
-        <v>15</v>
-      </c>
-      <c r="AO9" s="1">
-        <v>14</v>
-      </c>
-      <c r="AP9" s="1">
-        <v>-31</v>
-      </c>
-      <c r="AQ9" s="1">
-        <v>12</v>
-      </c>
-      <c r="AR9" s="1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="22:44" ht="15.75">
-      <c r="V10" t="s">
-        <v>9</v>
-      </c>
-      <c r="W10" s="1">
-        <v>12</v>
-      </c>
-      <c r="X10" s="1">
-        <v>13</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>18</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>17</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>15</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>7</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>17</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>4</v>
-      </c>
-      <c r="AE10" s="1">
-        <v>14</v>
-      </c>
-      <c r="AF10" s="1">
-        <v>-18</v>
-      </c>
-      <c r="AG10" s="1">
-        <v>10</v>
-      </c>
-      <c r="AH10" s="1">
-        <v>23</v>
-      </c>
-      <c r="AI10" s="1">
-        <v>26</v>
-      </c>
-      <c r="AJ10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="1">
-        <v>18</v>
-      </c>
-      <c r="AL10" s="1">
-        <v>15</v>
-      </c>
-      <c r="AM10" s="1">
-        <v>6</v>
-      </c>
-      <c r="AN10" s="1">
-        <v>30</v>
-      </c>
-      <c r="AO10" s="1">
-        <v>-7</v>
-      </c>
-      <c r="AP10" s="1">
-        <v>-19</v>
-      </c>
-      <c r="AQ10" s="1">
-        <v>12</v>
-      </c>
-      <c r="AR10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="22:44" ht="15.75">
-      <c r="V11" t="s">
-        <v>8</v>
-      </c>
       <c r="W11" s="1">
-        <v>25</v>
-      </c>
-      <c r="X11" s="1">
-        <v>-16</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>-5</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="1">
-        <v>5</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>-2</v>
-      </c>
-      <c r="AE11" s="1">
-        <v>35</v>
-      </c>
-      <c r="AF11" s="1">
-        <v>19</v>
-      </c>
-      <c r="AG11" s="1">
-        <v>9</v>
-      </c>
-      <c r="AH11" s="1">
-        <v>21</v>
-      </c>
-      <c r="AI11" s="1">
-        <v>9</v>
-      </c>
-      <c r="AJ11" s="1">
-        <v>20</v>
-      </c>
-      <c r="AK11" s="1">
-        <v>19</v>
-      </c>
-      <c r="AL11" s="1">
-        <v>-35</v>
-      </c>
-      <c r="AM11" s="1">
-        <v>-10</v>
-      </c>
-      <c r="AN11" s="1">
-        <v>29</v>
-      </c>
-      <c r="AO11" s="1">
-        <v>20</v>
-      </c>
-      <c r="AP11" s="1">
-        <v>2</v>
-      </c>
-      <c r="AQ11" s="1">
-        <v>7</v>
-      </c>
-      <c r="AR11" s="1">
         <v>12</v>
       </c>
     </row>
@@ -14636,850 +14672,850 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="BR1:CP11"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="70:94">
-      <c r="BS1">
+    <row r="1" spans="1:25">
+      <c r="B1">
         <v>1</v>
       </c>
-      <c r="BT1">
+      <c r="C1">
         <v>2</v>
       </c>
-      <c r="BU1">
+      <c r="D1">
         <v>3</v>
       </c>
-      <c r="BV1">
+      <c r="E1">
         <v>4</v>
       </c>
-      <c r="BW1">
+      <c r="F1">
         <v>5</v>
       </c>
-      <c r="BX1">
+      <c r="G1">
         <v>6</v>
       </c>
-      <c r="BY1">
+      <c r="H1">
         <v>7</v>
       </c>
-      <c r="BZ1">
+      <c r="I1">
         <v>8</v>
       </c>
-      <c r="CA1">
+      <c r="J1">
         <v>9</v>
       </c>
-      <c r="CB1">
+      <c r="K1">
         <v>10</v>
       </c>
-      <c r="CC1">
+      <c r="L1">
         <v>11</v>
       </c>
-      <c r="CD1">
+      <c r="M1">
         <v>12</v>
       </c>
-      <c r="CE1">
+      <c r="N1">
         <v>13</v>
       </c>
-      <c r="CF1">
+      <c r="O1">
         <v>14</v>
       </c>
-      <c r="CG1">
+      <c r="P1">
         <v>15</v>
       </c>
-      <c r="CH1">
+      <c r="Q1">
         <v>16</v>
       </c>
-      <c r="CI1">
+      <c r="R1">
         <v>17</v>
       </c>
-      <c r="CJ1">
+      <c r="S1">
         <v>18</v>
       </c>
-      <c r="CK1">
+      <c r="T1">
         <v>19</v>
       </c>
-      <c r="CL1">
+      <c r="U1">
         <v>20</v>
       </c>
-      <c r="CM1">
+      <c r="V1">
         <v>21</v>
       </c>
-      <c r="CN1">
+      <c r="W1">
         <v>22</v>
       </c>
-      <c r="CO1">
+      <c r="X1">
         <v>23</v>
       </c>
-      <c r="CP1">
+      <c r="Y1">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="70:94">
-      <c r="BR2" t="s">
+    <row r="2" spans="1:25">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="BS2" s="2">
+      <c r="B2" s="2">
         <v>71</v>
       </c>
-      <c r="BT2" s="2">
+      <c r="C2" s="2">
         <v>101</v>
       </c>
-      <c r="BU2" s="2">
+      <c r="D2" s="2">
         <v>71</v>
       </c>
-      <c r="BV2" s="2">
+      <c r="E2" s="2">
         <v>92</v>
       </c>
-      <c r="BW2" s="2">
+      <c r="F2" s="2">
         <v>86</v>
       </c>
-      <c r="BX2" s="2">
+      <c r="G2" s="2">
         <v>118</v>
       </c>
-      <c r="BY2" s="2">
+      <c r="H2" s="2">
         <v>82</v>
       </c>
-      <c r="BZ2" s="2">
+      <c r="I2" s="2">
         <v>83</v>
       </c>
-      <c r="CA2" s="2">
+      <c r="J2" s="2">
         <v>88</v>
       </c>
-      <c r="CB2" s="2">
+      <c r="K2" s="2">
         <v>40</v>
       </c>
-      <c r="CC2" s="2">
+      <c r="L2" s="2">
         <v>100</v>
       </c>
-      <c r="CD2" s="2">
+      <c r="M2" s="2">
         <v>90</v>
       </c>
-      <c r="CE2" s="2">
+      <c r="N2" s="2">
         <v>93</v>
       </c>
-      <c r="CF2" s="2">
+      <c r="O2" s="2">
         <v>100</v>
       </c>
-      <c r="CG2" s="2">
+      <c r="P2" s="2">
         <v>52</v>
       </c>
-      <c r="CH2" s="2">
+      <c r="Q2" s="2">
         <v>97</v>
       </c>
-      <c r="CI2" s="2">
+      <c r="R2" s="2">
         <v>6</v>
       </c>
-      <c r="CJ2" s="2">
+      <c r="S2" s="2">
         <v>64</v>
       </c>
-      <c r="CK2" s="2">
+      <c r="T2" s="2">
         <v>22</v>
       </c>
-      <c r="CL2" s="2">
+      <c r="U2" s="2">
         <v>86</v>
       </c>
-      <c r="CM2" s="2">
+      <c r="V2" s="2">
         <v>63</v>
       </c>
-      <c r="CN2" s="2">
+      <c r="W2" s="2">
         <v>-34</v>
       </c>
-      <c r="CO2" s="2">
+      <c r="X2" s="2">
         <v>96</v>
       </c>
-      <c r="CP2" s="2">
+      <c r="Y2" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="70:94">
-      <c r="BR3" t="s">
+    <row r="3" spans="1:25">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-      <c r="BS3" s="2">
+      <c r="B3" s="2">
         <v>19</v>
       </c>
-      <c r="BT3" s="2">
+      <c r="C3" s="2">
         <v>67</v>
       </c>
-      <c r="BU3" s="2">
+      <c r="D3" s="2">
         <v>46</v>
       </c>
-      <c r="BV3" s="2">
+      <c r="E3" s="2">
         <v>46</v>
       </c>
-      <c r="BW3" s="2">
+      <c r="F3" s="2">
         <v>21</v>
       </c>
-      <c r="BX3" s="2">
+      <c r="G3" s="2">
         <v>60</v>
       </c>
-      <c r="BY3" s="2">
+      <c r="H3" s="2">
         <v>71</v>
       </c>
-      <c r="BZ3" s="2">
+      <c r="I3" s="2">
         <v>23</v>
       </c>
-      <c r="CA3" s="2">
+      <c r="J3" s="2">
         <v>28</v>
       </c>
-      <c r="CB3" s="2">
+      <c r="K3" s="2">
         <v>51</v>
       </c>
-      <c r="CC3" s="2">
+      <c r="L3" s="2">
         <v>1</v>
       </c>
-      <c r="CD3" s="2">
+      <c r="M3" s="2">
         <v>41</v>
       </c>
-      <c r="CE3" s="2">
+      <c r="N3" s="2">
         <v>55</v>
       </c>
-      <c r="CF3" s="2">
+      <c r="O3" s="2">
         <v>39</v>
       </c>
-      <c r="CG3" s="2">
+      <c r="P3" s="2">
         <v>47</v>
       </c>
-      <c r="CH3" s="2">
+      <c r="Q3" s="2">
         <v>56</v>
       </c>
-      <c r="CI3" s="2">
+      <c r="R3" s="2">
         <v>85</v>
       </c>
-      <c r="CJ3" s="2">
+      <c r="S3" s="2">
         <v>51</v>
       </c>
-      <c r="CK3" s="2">
+      <c r="T3" s="2">
         <v>92</v>
       </c>
-      <c r="CL3" s="2">
+      <c r="U3" s="2">
         <v>36</v>
       </c>
-      <c r="CM3" s="2">
+      <c r="V3" s="2">
         <v>88</v>
       </c>
-      <c r="CN3" s="2">
+      <c r="W3" s="2">
         <v>85</v>
       </c>
-      <c r="CO3" s="2">
+      <c r="X3" s="2">
         <v>67</v>
       </c>
-      <c r="CP3" s="2">
+      <c r="Y3" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="70:94">
-      <c r="BR4" t="s">
+    <row r="4" spans="1:25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="BS4" s="2">
+      <c r="B4" s="2">
         <v>67</v>
       </c>
-      <c r="BT4" s="2">
+      <c r="C4" s="2">
         <v>69</v>
       </c>
-      <c r="BU4" s="2">
+      <c r="D4" s="2">
         <v>56</v>
       </c>
-      <c r="BV4" s="2">
+      <c r="E4" s="2">
         <v>60</v>
       </c>
-      <c r="BW4" s="2">
+      <c r="F4" s="2">
         <v>46</v>
       </c>
-      <c r="BX4" s="2">
+      <c r="G4" s="2">
         <v>51</v>
       </c>
-      <c r="BY4" s="2">
+      <c r="H4" s="2">
         <v>6</v>
       </c>
-      <c r="BZ4" s="2">
+      <c r="I4" s="2">
         <v>9</v>
       </c>
-      <c r="CA4" s="2">
+      <c r="J4" s="2">
         <v>24</v>
       </c>
-      <c r="CB4" s="2">
+      <c r="K4" s="2">
         <v>87</v>
       </c>
-      <c r="CC4" s="2">
+      <c r="L4" s="2">
         <v>19</v>
       </c>
-      <c r="CD4" s="2">
+      <c r="M4" s="2">
         <v>7</v>
       </c>
-      <c r="CE4" s="2">
+      <c r="N4" s="2">
         <v>50</v>
       </c>
-      <c r="CF4" s="2">
+      <c r="O4" s="2">
         <v>54</v>
       </c>
-      <c r="CG4" s="2">
+      <c r="P4" s="2">
         <v>30</v>
       </c>
-      <c r="CH4" s="2">
+      <c r="Q4" s="2">
         <v>37</v>
       </c>
-      <c r="CI4" s="2">
+      <c r="R4" s="2">
         <v>67</v>
       </c>
-      <c r="CJ4" s="2">
+      <c r="S4" s="2">
         <v>67</v>
       </c>
-      <c r="CK4" s="2">
+      <c r="T4" s="2">
         <v>61</v>
       </c>
-      <c r="CL4" s="2">
+      <c r="U4" s="2">
         <v>58</v>
       </c>
-      <c r="CM4" s="2">
+      <c r="V4" s="2">
         <v>91</v>
       </c>
-      <c r="CN4" s="2">
+      <c r="W4" s="2">
         <v>77</v>
       </c>
-      <c r="CO4" s="2">
+      <c r="X4" s="2">
         <v>57</v>
       </c>
-      <c r="CP4" s="2">
+      <c r="Y4" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="70:94">
-      <c r="BR5" t="s">
+    <row r="5" spans="1:25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="BS5" s="2">
+      <c r="B5" s="2">
         <v>36</v>
       </c>
-      <c r="BT5" s="2">
+      <c r="C5" s="2">
         <v>-23</v>
       </c>
-      <c r="BU5" s="2">
+      <c r="D5" s="2">
         <v>56</v>
       </c>
-      <c r="BV5" s="2">
+      <c r="E5" s="2">
         <v>73</v>
       </c>
-      <c r="BW5" s="2">
+      <c r="F5" s="2">
         <v>64</v>
       </c>
-      <c r="BX5" s="2">
+      <c r="G5" s="2">
         <v>34</v>
       </c>
-      <c r="BY5" s="2">
+      <c r="H5" s="2">
         <v>67</v>
       </c>
-      <c r="BZ5" s="2">
+      <c r="I5" s="2">
         <v>71</v>
       </c>
-      <c r="CA5" s="2">
+      <c r="J5" s="2">
         <v>61</v>
       </c>
-      <c r="CB5" s="2">
+      <c r="K5" s="2">
         <v>57</v>
       </c>
-      <c r="CC5" s="2">
+      <c r="L5" s="2">
         <v>67</v>
       </c>
-      <c r="CD5" s="2">
+      <c r="M5" s="2">
         <v>41</v>
       </c>
-      <c r="CE5" s="2">
+      <c r="N5" s="2">
         <v>70</v>
       </c>
-      <c r="CF5" s="2">
+      <c r="O5" s="2">
         <v>39</v>
       </c>
-      <c r="CG5" s="2">
+      <c r="P5" s="2">
         <v>-4</v>
       </c>
-      <c r="CH5" s="2">
+      <c r="Q5" s="2">
         <v>67</v>
       </c>
-      <c r="CI5" s="2">
+      <c r="R5" s="2">
         <v>28</v>
       </c>
-      <c r="CJ5" s="2">
+      <c r="S5" s="2">
         <v>48</v>
       </c>
-      <c r="CK5" s="2">
+      <c r="T5" s="2">
         <v>85</v>
       </c>
-      <c r="CL5" s="2">
+      <c r="U5" s="2">
         <v>58</v>
       </c>
-      <c r="CM5" s="2">
+      <c r="V5" s="2">
         <v>-3</v>
       </c>
-      <c r="CN5" s="2">
+      <c r="W5" s="2">
         <v>48</v>
       </c>
-      <c r="CO5" s="2">
+      <c r="X5" s="2">
         <v>22</v>
       </c>
-      <c r="CP5" s="2">
+      <c r="Y5" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="70:94">
-      <c r="BR6" t="s">
+    <row r="6" spans="1:25">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="BS6" s="2">
+      <c r="B6" s="2">
         <v>10</v>
       </c>
-      <c r="BT6" s="2">
+      <c r="C6" s="2">
         <v>26</v>
       </c>
-      <c r="BU6" s="2">
+      <c r="D6" s="2">
         <v>19</v>
       </c>
-      <c r="BV6" s="2">
+      <c r="E6" s="2">
         <v>13</v>
       </c>
-      <c r="BW6" s="2">
+      <c r="F6" s="2">
         <v>27</v>
       </c>
-      <c r="BX6" s="2">
+      <c r="G6" s="2">
         <v>31</v>
       </c>
-      <c r="BY6" s="2">
+      <c r="H6" s="2">
         <v>42</v>
       </c>
-      <c r="BZ6" s="2">
+      <c r="I6" s="2">
         <v>16</v>
       </c>
-      <c r="CA6" s="2">
+      <c r="J6" s="2">
         <v>-8</v>
       </c>
-      <c r="CB6" s="2">
+      <c r="K6" s="2">
         <v>4</v>
       </c>
-      <c r="CC6" s="2">
+      <c r="L6" s="2">
         <v>-36</v>
       </c>
-      <c r="CD6" s="2">
+      <c r="M6" s="2">
         <v>16</v>
       </c>
-      <c r="CE6" s="2">
+      <c r="N6" s="2">
         <v>27</v>
       </c>
-      <c r="CF6" s="2">
+      <c r="O6" s="2">
         <v>24</v>
       </c>
-      <c r="CG6" s="2">
+      <c r="P6" s="2">
         <v>35</v>
       </c>
-      <c r="CH6" s="2">
+      <c r="Q6" s="2">
         <v>23</v>
       </c>
-      <c r="CI6" s="2">
+      <c r="R6" s="2">
         <v>46</v>
       </c>
-      <c r="CJ6" s="2">
+      <c r="S6" s="2">
         <v>5</v>
       </c>
-      <c r="CK6" s="2">
+      <c r="T6" s="2">
         <v>27</v>
       </c>
-      <c r="CL6" s="2">
+      <c r="U6" s="2">
         <v>29</v>
       </c>
-      <c r="CM6" s="2">
+      <c r="V6" s="2">
         <v>42</v>
       </c>
-      <c r="CN6" s="2">
+      <c r="W6" s="2">
         <v>9</v>
       </c>
-      <c r="CO6" s="2">
+      <c r="X6" s="2">
         <v>39</v>
       </c>
-      <c r="CP6" s="2">
+      <c r="Y6" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="70:94">
-      <c r="BR7" t="s">
+    <row r="7" spans="1:25">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="BS7" s="2">
+      <c r="B7" s="2">
         <v>14</v>
       </c>
-      <c r="BT7" s="2">
+      <c r="C7" s="2">
         <v>47</v>
       </c>
-      <c r="BU7" s="2">
+      <c r="D7" s="2">
         <v>10</v>
       </c>
-      <c r="BV7" s="2">
+      <c r="E7" s="2">
         <v>40</v>
       </c>
-      <c r="BW7" s="2">
+      <c r="F7" s="2">
         <v>12</v>
       </c>
-      <c r="BX7" s="2">
+      <c r="G7" s="2">
         <v>8</v>
       </c>
-      <c r="BY7" s="2">
+      <c r="H7" s="2">
         <v>-13</v>
       </c>
-      <c r="BZ7" s="2">
+      <c r="I7" s="2">
         <v>25</v>
       </c>
-      <c r="CA7" s="2">
+      <c r="J7" s="2">
         <v>6</v>
       </c>
-      <c r="CB7" s="2">
+      <c r="K7" s="2">
         <v>22</v>
       </c>
-      <c r="CC7" s="2">
+      <c r="L7" s="2">
         <v>37</v>
       </c>
-      <c r="CD7" s="2">
+      <c r="M7" s="2">
         <v>25</v>
       </c>
-      <c r="CE7" s="2">
+      <c r="N7" s="2">
         <v>15</v>
       </c>
-      <c r="CF7" s="2">
+      <c r="O7" s="2">
         <v>-9</v>
       </c>
-      <c r="CG7" s="2">
+      <c r="P7" s="2">
         <v>43</v>
       </c>
-      <c r="CH7" s="2">
+      <c r="Q7" s="2">
         <v>7</v>
       </c>
-      <c r="CI7" s="2">
+      <c r="R7" s="2">
         <v>13</v>
       </c>
-      <c r="CJ7" s="2">
+      <c r="S7" s="2">
         <v>15</v>
       </c>
-      <c r="CK7" s="2">
+      <c r="T7" s="2">
         <v>13</v>
       </c>
-      <c r="CL7" s="2">
+      <c r="U7" s="2">
         <v>45</v>
       </c>
-      <c r="CM7" s="2">
+      <c r="V7" s="2">
         <v>54</v>
       </c>
-      <c r="CN7" s="2">
+      <c r="W7" s="2">
         <v>24</v>
       </c>
-      <c r="CO7" s="2">
+      <c r="X7" s="2">
         <v>-5</v>
       </c>
-      <c r="CP7" s="2">
+      <c r="Y7" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="70:94">
-      <c r="BR8" t="s">
+    <row r="8" spans="1:25">
+      <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="BS8" s="2">
+      <c r="B8" s="2">
         <v>-10</v>
       </c>
-      <c r="BT8" s="2">
+      <c r="C8" s="2">
         <v>42</v>
       </c>
-      <c r="BU8" s="2">
+      <c r="D8" s="2">
         <v>14</v>
       </c>
-      <c r="BV8" s="2">
+      <c r="E8" s="2">
         <v>22</v>
       </c>
-      <c r="BW8" s="2">
+      <c r="F8" s="2">
         <v>18</v>
       </c>
-      <c r="BX8" s="2">
+      <c r="G8" s="2">
         <v>-6</v>
       </c>
-      <c r="BY8" s="2">
+      <c r="H8" s="2">
         <v>24</v>
       </c>
-      <c r="BZ8" s="2">
+      <c r="I8" s="2">
         <v>31</v>
       </c>
-      <c r="CA8" s="2">
+      <c r="J8" s="2">
         <v>35</v>
       </c>
-      <c r="CB8" s="2">
+      <c r="K8" s="2">
         <v>-4</v>
       </c>
-      <c r="CC8" s="2">
+      <c r="L8" s="2">
         <v>34</v>
       </c>
-      <c r="CD8" s="2">
+      <c r="M8" s="2">
         <v>-35</v>
       </c>
-      <c r="CE8" s="2">
+      <c r="N8" s="2">
         <v>17</v>
       </c>
-      <c r="CF8" s="2">
+      <c r="O8" s="2">
         <v>29</v>
       </c>
-      <c r="CG8" s="2">
+      <c r="P8" s="2">
         <v>38</v>
       </c>
-      <c r="CH8" s="2">
+      <c r="Q8" s="2">
         <v>27</v>
       </c>
-      <c r="CI8" s="2">
+      <c r="R8" s="2">
         <v>41</v>
       </c>
-      <c r="CJ8" s="2">
+      <c r="S8" s="2">
         <v>16</v>
       </c>
-      <c r="CK8" s="2">
+      <c r="T8" s="2">
         <v>34</v>
       </c>
-      <c r="CL8" s="2">
+      <c r="U8" s="2">
         <v>-10</v>
       </c>
-      <c r="CM8" s="2">
+      <c r="V8" s="2">
         <v>47</v>
       </c>
-      <c r="CN8" s="2">
+      <c r="W8" s="2">
         <v>30</v>
       </c>
-      <c r="CO8" s="2">
+      <c r="X8" s="2">
         <v>22</v>
       </c>
-      <c r="CP8" s="2">
+      <c r="Y8" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="70:94">
-      <c r="BR9" t="s">
+    <row r="9" spans="1:25">
+      <c r="A9" t="s">
         <v>1</v>
       </c>
-      <c r="BS9" s="2">
+      <c r="B9" s="2">
         <v>1</v>
       </c>
-      <c r="BT9" s="2">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="BU9" s="2">
+      <c r="D9" s="2">
         <v>9</v>
       </c>
-      <c r="BV9" s="2">
+      <c r="E9" s="2">
         <v>18</v>
       </c>
-      <c r="BW9" s="2">
+      <c r="F9" s="2">
         <v>11</v>
       </c>
-      <c r="BX9" s="2">
+      <c r="G9" s="2">
         <v>13</v>
       </c>
-      <c r="BY9" s="2">
+      <c r="H9" s="2">
         <v>14</v>
       </c>
-      <c r="BZ9" s="2">
+      <c r="I9" s="2">
         <v>-4</v>
       </c>
-      <c r="CA9" s="2">
+      <c r="J9" s="2">
         <v>1</v>
       </c>
-      <c r="CB9" s="2">
+      <c r="K9" s="2">
         <v>31</v>
       </c>
-      <c r="CC9" s="2">
+      <c r="L9" s="2">
         <v>24</v>
       </c>
-      <c r="CD9" s="2">
+      <c r="M9" s="2">
         <v>33</v>
       </c>
-      <c r="CE9" s="2">
+      <c r="N9" s="2">
         <v>20</v>
       </c>
-      <c r="CF9" s="2">
+      <c r="O9" s="2">
         <v>45</v>
       </c>
-      <c r="CG9" s="2">
+      <c r="P9" s="2">
         <v>41</v>
       </c>
-      <c r="CH9" s="2">
+      <c r="Q9" s="2">
         <v>-11</v>
       </c>
-      <c r="CI9" s="2">
+      <c r="R9" s="2">
         <v>-2</v>
       </c>
-      <c r="CJ9" s="2">
+      <c r="S9" s="2">
         <v>37</v>
       </c>
-      <c r="CK9" s="2">
+      <c r="T9" s="2">
         <v>-12</v>
       </c>
-      <c r="CL9" s="2">
+      <c r="U9" s="2">
         <v>2</v>
       </c>
-      <c r="CM9" s="2">
+      <c r="V9" s="2">
         <v>9</v>
       </c>
-      <c r="CN9" s="2">
+      <c r="W9" s="2">
         <v>-8</v>
       </c>
-      <c r="CO9" s="2">
+      <c r="X9" s="2">
         <v>21</v>
       </c>
-      <c r="CP9" s="2">
+      <c r="Y9" s="2">
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="70:94">
-      <c r="BR10" t="s">
+    <row r="10" spans="1:25">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="BS10" s="2">
+      <c r="B10" s="2">
         <v>3</v>
       </c>
-      <c r="BT10" s="2">
+      <c r="C10" s="2">
         <v>12</v>
       </c>
-      <c r="BU10" s="2">
+      <c r="D10" s="2">
         <v>0</v>
       </c>
-      <c r="BV10" s="2">
+      <c r="E10" s="2">
         <v>-22</v>
       </c>
-      <c r="BW10" s="2">
+      <c r="F10" s="2">
         <v>10</v>
       </c>
-      <c r="BX10" s="2">
+      <c r="G10" s="2">
         <v>9</v>
       </c>
-      <c r="BY10" s="2">
+      <c r="H10" s="2">
         <v>13</v>
       </c>
-      <c r="BZ10" s="2">
+      <c r="I10" s="2">
         <v>7</v>
       </c>
-      <c r="CA10" s="2">
+      <c r="J10" s="2">
         <v>52</v>
       </c>
-      <c r="CB10" s="2">
+      <c r="K10" s="2">
         <v>26</v>
       </c>
-      <c r="CC10" s="2">
+      <c r="L10" s="2">
         <v>45</v>
       </c>
-      <c r="CD10" s="2">
+      <c r="M10" s="2">
         <v>14</v>
       </c>
-      <c r="CE10" s="2">
+      <c r="N10" s="2">
         <v>24</v>
       </c>
-      <c r="CF10" s="2">
+      <c r="O10" s="2">
         <v>35</v>
       </c>
-      <c r="CG10" s="2">
+      <c r="P10" s="2">
         <v>14</v>
       </c>
-      <c r="CH10" s="2">
+      <c r="Q10" s="2">
         <v>-2</v>
       </c>
-      <c r="CI10" s="2">
+      <c r="R10" s="2">
         <v>17</v>
       </c>
-      <c r="CJ10" s="2">
+      <c r="S10" s="2">
         <v>-4</v>
       </c>
-      <c r="CK10" s="2">
+      <c r="T10" s="2">
         <v>25</v>
       </c>
-      <c r="CL10" s="2">
+      <c r="U10" s="2">
         <v>2</v>
       </c>
-      <c r="CM10" s="2">
+      <c r="V10" s="2">
         <v>-9</v>
       </c>
-      <c r="CN10" s="2">
+      <c r="W10" s="2">
         <v>-8</v>
       </c>
-      <c r="CO10" s="2">
+      <c r="X10" s="2">
         <v>4</v>
       </c>
-      <c r="CP10" s="2">
+      <c r="Y10" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="70:94">
-      <c r="BR11" t="s">
+    <row r="11" spans="1:25">
+      <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="BS11" s="2">
+      <c r="B11" s="2">
         <v>-14</v>
       </c>
-      <c r="BT11" s="2">
+      <c r="C11" s="2">
         <v>-6</v>
       </c>
-      <c r="BU11" s="2">
+      <c r="D11" s="2">
         <v>9</v>
       </c>
-      <c r="BV11" s="2">
+      <c r="E11" s="2">
         <v>22</v>
       </c>
-      <c r="BW11" s="2">
+      <c r="F11" s="2">
         <v>-6</v>
       </c>
-      <c r="BX11" s="2">
+      <c r="G11" s="2">
         <v>10</v>
       </c>
-      <c r="BY11" s="2">
+      <c r="H11" s="2">
         <v>10</v>
       </c>
-      <c r="BZ11" s="2">
+      <c r="I11" s="2">
         <v>-11</v>
       </c>
-      <c r="CA11" s="2">
+      <c r="J11" s="2">
         <v>31</v>
       </c>
-      <c r="CB11" s="2">
+      <c r="K11" s="2">
         <v>11</v>
       </c>
-      <c r="CC11" s="2">
+      <c r="L11" s="2">
         <v>17</v>
       </c>
-      <c r="CD11" s="2">
+      <c r="M11" s="2">
         <v>5</v>
       </c>
-      <c r="CE11" s="2">
+      <c r="N11" s="2">
         <v>-13</v>
       </c>
-      <c r="CF11" s="2">
+      <c r="O11" s="2">
         <v>2</v>
       </c>
-      <c r="CG11" s="2">
+      <c r="P11" s="2">
         <v>14</v>
       </c>
-      <c r="CH11" s="2">
+      <c r="Q11" s="2">
         <v>6</v>
       </c>
-      <c r="CI11" s="2">
+      <c r="R11" s="2">
         <v>7</v>
       </c>
-      <c r="CJ11" s="2">
+      <c r="S11" s="2">
         <v>6</v>
       </c>
-      <c r="CK11" s="2">
+      <c r="T11" s="2">
         <v>18</v>
       </c>
-      <c r="CL11" s="2">
+      <c r="U11" s="2">
         <v>14</v>
       </c>
-      <c r="CM11" s="2">
+      <c r="V11" s="2">
         <v>12</v>
       </c>
-      <c r="CN11" s="2">
+      <c r="W11" s="2">
         <v>3</v>
       </c>
-      <c r="CO11" s="2">
+      <c r="X11" s="2">
         <v>14</v>
       </c>
-      <c r="CP11" s="2">
+      <c r="Y11" s="2">
         <v>4</v>
       </c>
     </row>
@@ -15493,13 +15529,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="B1">
         <v>1</v>
       </c>
@@ -15509,8 +15545,11 @@
       <c r="D1">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -15523,8 +15562,11 @@
       <c r="D2">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -15537,8 +15579,11 @@
       <c r="D3">
         <v>72</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -15551,8 +15596,11 @@
       <c r="D4">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -15565,8 +15613,11 @@
       <c r="D5">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15579,8 +15630,11 @@
       <c r="D6">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -15593,8 +15647,11 @@
       <c r="D7">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -15607,8 +15664,11 @@
       <c r="D8">
         <v>-12</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -15621,8 +15681,11 @@
       <c r="D9">
         <v>-4</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -15635,8 +15698,11 @@
       <c r="D10">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -15649,8 +15715,11 @@
       <c r="D11">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -15662,6 +15731,9 @@
       </c>
       <c r="D12">
         <v>5</v>
+      </c>
+      <c r="E12">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3DB95D-C8CE-4418-8532-9F9FAC556734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3D94F4-1DE9-4EAA-B3B4-0BEA363766A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="1650" windowWidth="21600" windowHeight="11055" tabRatio="864" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="7" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="2026DriverPrice" sheetId="8" r:id="rId15"/>
     <sheet name="2026DriverPoints" sheetId="16" r:id="rId16"/>
     <sheet name="TEAMCONFIG" sheetId="17" r:id="rId17"/>
+    <sheet name="WEEKLY BUDGET" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="85">
   <si>
     <t>Red Bull Racing</t>
   </si>
@@ -295,6 +296,21 @@
   </si>
   <si>
     <t>Zhou Guanyu</t>
+  </si>
+  <si>
+    <t>6_Guppies</t>
+  </si>
+  <si>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>6_Guppies2</t>
+  </si>
+  <si>
+    <t>NOR</t>
+  </si>
+  <si>
+    <t>budget</t>
   </si>
 </sst>
 </file>
@@ -10778,7 +10794,10 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{008844FF-9942-4BA0-9033-82ED2D862880}">
-  <dimension ref="A1:L7"/>
+  <sheetPr>
+    <tabColor theme="5" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -11045,6 +11064,161 @@
       </c>
       <c r="L7" t="s">
         <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8">
+        <v>2026</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" t="s">
+        <v>81</v>
+      </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" t="s">
+        <v>76</v>
+      </c>
+      <c r="L8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9">
+        <v>2026</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" t="s">
+        <v>83</v>
+      </c>
+      <c r="L9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C30D3F4-D296-4157-946B-4590DD34B78B}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2026</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>100.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>2026</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>103.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>2026</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>104.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>2026</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>105.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3D94F4-1DE9-4EAA-B3B4-0BEA363766A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FA67B4-8435-4B01-8737-879E137EAA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="7" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="864" firstSheet="10" activeTab="16" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -10799,6 +10799,9 @@
   </sheetPr>
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FA67B4-8435-4B01-8737-879E137EAA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DFD566-76F8-485C-9648-6FD827505BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21697" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="864" firstSheet="10" activeTab="16" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="1" activeTab="3" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="88">
   <si>
     <t>Red Bull Racing</t>
   </si>
@@ -311,6 +311,15 @@
   </si>
   <si>
     <t>budget</t>
+  </si>
+  <si>
+    <t>BOT</t>
+  </si>
+  <si>
+    <t>ANT</t>
+  </si>
+  <si>
+    <t>PER</t>
   </si>
 </sst>
 </file>
@@ -9920,13 +9929,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1">
         <v>1</v>
       </c>
@@ -9942,8 +9951,11 @@
       <c r="F1">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -9962,8 +9974,11 @@
       <c r="F2">
         <v>28.3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9982,8 +9997,11 @@
       <c r="F3">
         <v>28.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -10002,8 +10020,11 @@
       <c r="F4">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -10022,8 +10043,11 @@
       <c r="F5">
         <v>24.7</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -10042,8 +10066,11 @@
       <c r="F6">
         <v>24.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -10062,8 +10089,11 @@
       <c r="F7">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -10082,8 +10112,11 @@
       <c r="F8">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -10102,8 +10135,11 @@
       <c r="F9">
         <v>12.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10122,8 +10158,11 @@
       <c r="F10">
         <v>12.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -10142,8 +10181,11 @@
       <c r="F11">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -10162,8 +10204,11 @@
       <c r="F12">
         <v>9.6</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -10182,8 +10227,11 @@
       <c r="F13">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -10202,8 +10250,11 @@
       <c r="F14">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -10222,8 +10273,11 @@
       <c r="F15">
         <v>9.4</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -10242,8 +10296,11 @@
       <c r="F16">
         <v>9.6999999999999993</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10262,8 +10319,11 @@
       <c r="F17">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -10282,8 +10342,11 @@
       <c r="F18">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -10302,8 +10365,11 @@
       <c r="F19">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -10322,8 +10388,11 @@
       <c r="F20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -10342,8 +10411,11 @@
       <c r="F21">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -10362,8 +10434,11 @@
       <c r="F22">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -10381,6 +10456,9 @@
       </c>
       <c r="F23">
         <v>3.9</v>
+      </c>
+      <c r="G23">
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -10393,13 +10471,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1">
         <v>1</v>
       </c>
@@ -10412,8 +10490,11 @@
       <c r="E1">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -10429,8 +10510,11 @@
       <c r="E2">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -10446,8 +10530,11 @@
       <c r="E3">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -10463,8 +10550,11 @@
       <c r="E4">
         <v>54</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -10480,8 +10570,11 @@
       <c r="E5">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -10497,8 +10590,11 @@
       <c r="E6">
         <v>42</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -10514,8 +10610,11 @@
       <c r="E7">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -10531,8 +10630,11 @@
       <c r="E8">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -10548,8 +10650,11 @@
       <c r="E9">
         <v>-16</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10565,8 +10670,11 @@
       <c r="E10">
         <v>-8</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -10582,8 +10690,11 @@
       <c r="E11">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -10599,8 +10710,11 @@
       <c r="E12">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -10616,8 +10730,11 @@
       <c r="E13">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -10633,8 +10750,11 @@
       <c r="E14">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -10650,8 +10770,11 @@
       <c r="E15">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -10667,8 +10790,11 @@
       <c r="E16">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10684,8 +10810,11 @@
       <c r="E17">
         <v>-29</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -10701,8 +10830,11 @@
       <c r="E18">
         <v>-12</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -10718,8 +10850,11 @@
       <c r="E19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -10735,8 +10870,11 @@
       <c r="E20">
         <v>-4</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -10752,8 +10890,11 @@
       <c r="E21">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -10769,8 +10910,11 @@
       <c r="E22">
         <v>19</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -10785,6 +10929,9 @@
       </c>
       <c r="E23">
         <v>4</v>
+      </c>
+      <c r="F23">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -10797,7 +10944,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -11142,6 +11289,82 @@
         <v>83</v>
       </c>
       <c r="L9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10">
+        <v>2026</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11">
+        <v>2026</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" t="s">
         <v>67</v>
       </c>
     </row>
@@ -11155,7 +11378,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -11222,6 +11445,17 @@
       </c>
       <c r="C6">
         <v>105.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+      <c r="C7">
+        <v>105.6</v>
       </c>
     </row>
   </sheetData>
@@ -12951,10 +13185,10 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1">
         <v>1</v>
       </c>
@@ -12970,8 +13204,11 @@
       <c r="F1">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -12990,8 +13227,11 @@
       <c r="F2">
         <v>30.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -13010,8 +13250,11 @@
       <c r="F3">
         <v>28.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -13030,8 +13273,11 @@
       <c r="F4">
         <v>29.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -13050,8 +13296,11 @@
       <c r="F5">
         <v>24.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13070,8 +13319,11 @@
       <c r="F6">
         <v>14.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -13090,8 +13342,11 @@
       <c r="F7">
         <v>14.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -13110,8 +13365,11 @@
       <c r="F8">
         <v>7.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -13130,8 +13388,11 @@
       <c r="F9">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -13150,8 +13411,11 @@
       <c r="F10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -13170,8 +13434,11 @@
       <c r="F11">
         <v>8.6999999999999993</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -13189,6 +13456,9 @@
       </c>
       <c r="F12">
         <v>5.6</v>
+      </c>
+      <c r="G12">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -15706,13 +15976,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="B1">
         <v>1</v>
       </c>
@@ -15725,8 +15995,11 @@
       <c r="E1">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -15742,8 +16015,11 @@
       <c r="E2">
         <v>104</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -15759,8 +16035,11 @@
       <c r="E3">
         <v>110</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -15776,8 +16055,11 @@
       <c r="E4">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -15793,8 +16075,11 @@
       <c r="E5">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -15810,8 +16095,11 @@
       <c r="E6">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -15827,8 +16115,11 @@
       <c r="E7">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -15844,8 +16135,11 @@
       <c r="E8">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -15861,8 +16155,11 @@
       <c r="E9">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -15878,8 +16175,11 @@
       <c r="E10">
         <v>-27</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -15895,8 +16195,11 @@
       <c r="E11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -15911,6 +16214,9 @@
       </c>
       <c r="E12">
         <v>24</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DFD566-76F8-485C-9648-6FD827505BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62438A3D-2263-46AB-8609-31523894EAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="1" activeTab="3" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="864" firstSheet="10" activeTab="16" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="89">
   <si>
     <t>Red Bull Racing</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>PER</t>
+  </si>
+  <si>
+    <t>race_id</t>
   </si>
 </sst>
 </file>
@@ -10944,427 +10947,460 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>52</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>53</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>54</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
         <v>56</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>2026</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>58</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>59</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>60</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>61</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>62</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>58</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
         <v>64</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>2026</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>65</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>58</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>66</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>60</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>61</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>62</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>58</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
         <v>68</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>2026</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>69</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>58</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>70</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>60</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>61</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>62</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>58</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>2026</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>69</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>58</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>70</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>72</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>73</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>74</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>58</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13">
+      <c r="A6">
         <v>75</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6">
         <v>2026</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>69</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>76</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>70</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>66</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>60</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>62</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>76</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13">
+      <c r="A7">
+        <v>75</v>
+      </c>
+      <c r="B7" t="s">
         <v>77</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>2026</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>3</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>69</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>78</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>70</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>72</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>73</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>74</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>78</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
         <v>80</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>2026</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>6</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>69</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>76</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>70</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>66</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>81</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>62</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>76</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13">
+      <c r="A9">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>82</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>2026</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>6</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>69</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>83</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>70</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>72</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>74</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>60</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>83</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
         <v>80</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>2026</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>7</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>69</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>57</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>76</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>73</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>60</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>81</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>85</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>76</v>
       </c>
-      <c r="L10" t="s">
+      <c r="M10" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13">
+      <c r="A11">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
         <v>82</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>2026</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>7</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>69</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>10</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>86</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>62</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>74</v>
       </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>87</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>70</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>86</v>
       </c>
-      <c r="L11" t="s">
+      <c r="M11" t="s">
         <v>67</v>
       </c>
     </row>
@@ -11378,83 +11414,104 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
         <v>45</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2">
+        <v>73</v>
+      </c>
+      <c r="B2">
         <v>2026</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3">
+        <v>74</v>
+      </c>
+      <c r="B3">
         <v>2026</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>100.9</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4">
+        <v>75</v>
+      </c>
+      <c r="B4">
         <v>2026</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>103.1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5">
+        <v>76</v>
+      </c>
+      <c r="B5">
         <v>2026</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>104.2</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6">
+        <v>77</v>
+      </c>
+      <c r="B6">
         <v>2026</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>7</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>105.1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7">
+        <v>78</v>
+      </c>
+      <c r="B7">
         <v>2026</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>8</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>105.6</v>
       </c>
     </row>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62438A3D-2263-46AB-8609-31523894EAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC657F98-5CFA-48BC-ADB1-41B19B40E7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="864" firstSheet="10" activeTab="16" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="9503" windowHeight="12863" tabRatio="864" firstSheet="15" activeTab="16" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="91">
   <si>
     <t>Red Bull Racing</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>race_id</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>HAM</t>
   </si>
 </sst>
 </file>
@@ -717,9 +723,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -790,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -861,7 +867,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -932,7 +938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1003,7 +1009,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1145,7 +1151,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1216,7 +1222,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1287,7 +1293,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1358,7 +1364,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1429,7 +1435,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1511,9 +1517,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1584,7 +1590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1655,7 +1661,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1726,7 +1732,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1797,7 +1803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1868,7 +1874,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -1939,7 +1945,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +2016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2081,7 +2087,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2152,7 +2158,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2223,7 +2229,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2294,7 +2300,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -2365,7 +2371,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -2436,7 +2442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -2477,7 +2483,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -2548,7 +2554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2619,7 +2625,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -2690,7 +2696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -2727,7 +2733,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -2798,7 +2804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -2869,7 +2875,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -2916,7 +2922,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -2987,7 +2993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -3069,9 +3075,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -3148,7 +3154,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -3225,7 +3231,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3302,7 +3308,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -3379,7 +3385,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -3456,7 +3462,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -3533,7 +3539,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3610,7 +3616,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3685,7 +3691,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3762,7 +3768,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -3839,7 +3845,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -3872,7 +3878,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -3903,7 +3909,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -3980,7 +3986,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -4011,7 +4017,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -4052,7 +4058,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -4127,7 +4133,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -4200,7 +4206,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -4265,7 +4271,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -4342,7 +4348,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4419,7 +4425,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -4496,7 +4502,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4573,7 +4579,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -4650,7 +4656,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -4727,7 +4733,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -4774,7 +4780,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>41</v>
       </c>
@@ -4842,9 +4848,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -4921,7 +4927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -4998,7 +5004,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -5075,7 +5081,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -5152,7 +5158,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -5183,7 +5189,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5260,7 +5266,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -5335,7 +5341,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -5412,7 +5418,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -5489,7 +5495,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -5566,7 +5572,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -5599,7 +5605,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -5630,7 +5636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -5703,7 +5709,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -5780,7 +5786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -5821,7 +5827,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -5896,7 +5902,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -5973,7 +5979,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -6038,7 +6044,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -6115,7 +6121,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -6192,7 +6198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -6269,7 +6275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -6346,7 +6352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -6423,7 +6429,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -6470,7 +6476,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -6527,7 +6533,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -6615,9 +6621,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -6694,7 +6700,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6771,7 +6777,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -6848,7 +6854,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -6925,7 +6931,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -7002,7 +7008,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -7079,7 +7085,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -7156,7 +7162,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -7233,7 +7239,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -7310,7 +7316,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -7387,7 +7393,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -7464,7 +7470,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -7541,7 +7547,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -7618,7 +7624,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -7695,7 +7701,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -7772,7 +7778,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -7849,7 +7855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -7926,7 +7932,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -8003,7 +8009,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -8044,7 +8050,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -8121,7 +8127,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8198,7 +8204,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -8274,9 +8280,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -9932,13 +9938,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1">
         <v>1</v>
       </c>
@@ -9957,8 +9963,11 @@
       <c r="G1">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -9980,8 +9989,11 @@
       <c r="G2">
         <v>28.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>28.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -10003,8 +10015,11 @@
       <c r="G3">
         <v>28.5</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -10026,8 +10041,11 @@
       <c r="G4">
         <v>26.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -10049,8 +10067,11 @@
       <c r="G5">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -10072,8 +10093,11 @@
       <c r="G6">
         <v>24.7</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -10095,8 +10119,11 @@
       <c r="G7">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -10118,8 +10145,11 @@
       <c r="G8">
         <v>23.6</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -10141,8 +10171,11 @@
       <c r="G9">
         <v>12.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10164,8 +10197,11 @@
       <c r="G10">
         <v>12.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -10187,8 +10223,11 @@
       <c r="G11">
         <v>12.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -10210,8 +10249,11 @@
       <c r="G12">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -10233,8 +10275,11 @@
       <c r="G13">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -10256,8 +10301,11 @@
       <c r="G14">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -10279,8 +10327,11 @@
       <c r="G15">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -10302,8 +10353,11 @@
       <c r="G16">
         <v>9.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10325,8 +10379,11 @@
       <c r="G17">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -10348,8 +10405,11 @@
       <c r="G18">
         <v>7.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -10371,8 +10431,11 @@
       <c r="G19">
         <v>5.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -10394,8 +10457,11 @@
       <c r="G20">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -10417,8 +10483,11 @@
       <c r="G21">
         <v>8.8000000000000007</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -10440,8 +10509,11 @@
       <c r="G22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -10462,6 +10534,9 @@
       </c>
       <c r="G23">
         <v>4.5</v>
+      </c>
+      <c r="H23">
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
@@ -10474,13 +10549,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1">
         <v>1</v>
       </c>
@@ -10496,8 +10571,11 @@
       <c r="F1">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -10516,8 +10594,11 @@
       <c r="F2">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -10536,8 +10617,11 @@
       <c r="F3">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -10556,8 +10640,11 @@
       <c r="F4">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -10576,8 +10663,11 @@
       <c r="F5">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -10596,8 +10686,11 @@
       <c r="F6">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -10616,8 +10709,11 @@
       <c r="F7">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -10636,8 +10732,11 @@
       <c r="F8">
         <v>42</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -10656,8 +10755,11 @@
       <c r="F9">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -10676,8 +10778,11 @@
       <c r="F10">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -10696,8 +10801,11 @@
       <c r="F11">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -10716,8 +10824,11 @@
       <c r="F12">
         <v>-8</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -10736,8 +10847,11 @@
       <c r="F13">
         <v>-26</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -10756,8 +10870,11 @@
       <c r="F14">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -10776,8 +10893,11 @@
       <c r="F15">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -10796,8 +10916,11 @@
       <c r="F16">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -10816,8 +10939,11 @@
       <c r="F17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -10836,8 +10962,11 @@
       <c r="F18">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -10856,8 +10985,11 @@
       <c r="F19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -10876,8 +11008,11 @@
       <c r="F20">
         <v>-4</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -10896,8 +11031,11 @@
       <c r="F21">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -10916,8 +11054,11 @@
       <c r="F22">
         <v>-11</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -10935,6 +11076,9 @@
       </c>
       <c r="F23">
         <v>12</v>
+      </c>
+      <c r="G23">
+        <v>-20</v>
       </c>
     </row>
   </sheetData>
@@ -10947,10 +11091,10 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -11401,6 +11545,88 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12">
+        <v>2026</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" t="s">
+        <v>76</v>
+      </c>
+      <c r="M12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13">
+        <v>2026</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" t="s">
+        <v>85</v>
+      </c>
+      <c r="J13" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" t="s">
+        <v>86</v>
+      </c>
+      <c r="M13" t="s">
         <v>67</v>
       </c>
     </row>
@@ -11414,8 +11640,8 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -11513,6 +11739,20 @@
       </c>
       <c r="D7">
         <v>105.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>79</v>
+      </c>
+      <c r="B8">
+        <v>2026</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>104.3</v>
       </c>
     </row>
   </sheetData>
@@ -11526,9 +11766,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -11605,7 +11845,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11682,7 +11922,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -11759,7 +11999,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11836,7 +12076,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11913,7 +12153,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -11990,7 +12230,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -12067,7 +12307,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -12144,7 +12384,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -12221,7 +12461,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -12298,7 +12538,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -12386,7 +12626,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -12462,7 +12702,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -12539,7 +12779,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -12616,7 +12856,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -12693,7 +12933,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -12770,7 +13010,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -12847,7 +13087,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -12924,7 +13164,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -13001,7 +13241,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -13078,7 +13318,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -13155,7 +13395,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -13242,10 +13482,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="12.86328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="B1">
         <v>1</v>
       </c>
@@ -13264,8 +13507,11 @@
       <c r="G1">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -13287,8 +13533,11 @@
       <c r="G2">
         <v>30.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2">
+        <v>31.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -13310,8 +13559,11 @@
       <c r="G3">
         <v>29.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -13333,8 +13585,11 @@
       <c r="G4">
         <v>29.3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -13356,8 +13611,11 @@
       <c r="G5">
         <v>24.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -13379,8 +13637,11 @@
       <c r="G6">
         <v>15.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -13402,8 +13663,11 @@
       <c r="G7">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -13425,8 +13689,11 @@
       <c r="G8">
         <v>7.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -13448,8 +13715,11 @@
       <c r="G9">
         <v>10.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -13471,8 +13741,11 @@
       <c r="G10">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -13494,8 +13767,11 @@
       <c r="G11">
         <v>9.3000000000000007</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -13516,6 +13792,9 @@
       </c>
       <c r="G12">
         <v>6.2</v>
+      </c>
+      <c r="H12">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -13529,7 +13808,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:23">
       <c r="B1">
@@ -13599,7 +13878,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -13670,7 +13949,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -13741,7 +14020,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13812,7 +14091,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -13883,7 +14162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -13954,7 +14233,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -14025,7 +14304,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -14096,7 +14375,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -14167,7 +14446,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -14238,7 +14517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -14320,7 +14599,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -14396,7 +14675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -14473,7 +14752,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -14550,7 +14829,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -14627,7 +14906,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -14704,7 +14983,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -14781,7 +15060,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -14858,7 +15137,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -14935,7 +15214,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -15012,7 +15291,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -15089,7 +15368,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -15177,7 +15456,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -16033,13 +16312,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="B1">
         <v>1</v>
       </c>
@@ -16055,8 +16334,11 @@
       <c r="F1">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -16075,8 +16357,11 @@
       <c r="F2">
         <v>76</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -16095,8 +16380,11 @@
       <c r="F3">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -16115,8 +16403,11 @@
       <c r="F4">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -16135,8 +16426,11 @@
       <c r="F5">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -16155,8 +16449,11 @@
       <c r="F6">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -16175,8 +16472,11 @@
       <c r="F7">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -16195,8 +16495,11 @@
       <c r="F8">
         <v>-14</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -16215,8 +16518,11 @@
       <c r="F9">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -16235,8 +16541,11 @@
       <c r="F10">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -16255,8 +16564,11 @@
       <c r="F11">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -16274,6 +16586,9 @@
       </c>
       <c r="F12">
         <v>2</v>
+      </c>
+      <c r="G12">
+        <v>-13</v>
       </c>
     </row>
   </sheetData>
@@ -16287,9 +16602,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1">
@@ -16360,7 +16675,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -16431,7 +16746,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -16502,7 +16817,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -16573,7 +16888,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -16644,7 +16959,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -16715,7 +17030,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -16786,7 +17101,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -16857,7 +17172,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -16928,7 +17243,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -16999,7 +17314,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -17070,7 +17385,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -17141,7 +17456,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -17212,7 +17527,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -17283,7 +17598,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -17354,7 +17669,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -17425,7 +17740,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -17496,7 +17811,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -17567,7 +17882,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -17604,7 +17919,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -17645,7 +17960,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -17692,7 +18007,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -17763,7 +18078,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>41</v>
       </c>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90EBE17C-C5AC-4B95-AF21-05C9BEC416DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912F3697-E44E-491F-8D8F-3790A1056677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" tabRatio="864" firstSheet="14" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="10418" yWindow="0" windowWidth="11265" windowHeight="12863" tabRatio="864" firstSheet="12" activeTab="12" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -6607,13 +6607,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6635,8 +6635,11 @@
       <c r="H1">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6661,8 +6664,11 @@
       <c r="H2">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6687,8 +6693,11 @@
       <c r="H3">
         <v>67</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6713,8 +6722,11 @@
       <c r="H4">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6739,8 +6751,11 @@
       <c r="H5">
         <v>58</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6765,8 +6780,11 @@
       <c r="H6">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6791,8 +6809,11 @@
       <c r="H7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6817,8 +6838,11 @@
       <c r="H8">
         <v>-36</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6843,8 +6867,11 @@
       <c r="H9">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6869,8 +6896,11 @@
       <c r="H10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -6895,8 +6925,11 @@
       <c r="H11">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6920,6 +6953,9 @@
       </c>
       <c r="H12">
         <v>-9</v>
+      </c>
+      <c r="I12">
+        <v>-35</v>
       </c>
     </row>
   </sheetData>
@@ -6932,13 +6968,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6963,8 +6999,11 @@
       <c r="I1">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6992,8 +7031,11 @@
       <c r="I2">
         <v>31.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7021,8 +7063,11 @@
       <c r="I3">
         <v>29.8</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>30.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -7050,8 +7095,11 @@
       <c r="I4">
         <v>29.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7079,8 +7127,11 @@
       <c r="I5">
         <v>25.4</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7108,8 +7159,11 @@
       <c r="I6">
         <v>16.7</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7137,8 +7191,11 @@
       <c r="I7">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -7166,8 +7223,11 @@
       <c r="I8">
         <v>6.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7195,8 +7255,11 @@
       <c r="I9">
         <v>10.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7224,8 +7287,11 @@
       <c r="I10">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7253,8 +7319,11 @@
       <c r="I11">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7281,6 +7350,9 @@
       </c>
       <c r="I12">
         <v>5.4</v>
+      </c>
+      <c r="J12">
+        <v>4.8</v>
       </c>
     </row>
   </sheetData>
@@ -7293,13 +7365,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7321,8 +7393,11 @@
       <c r="H1">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7347,8 +7422,11 @@
       <c r="H2">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7373,8 +7451,11 @@
       <c r="H3">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7399,8 +7480,11 @@
       <c r="H4">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7425,8 +7509,11 @@
       <c r="H5">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7451,8 +7538,11 @@
       <c r="H6">
         <v>-4</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -7477,8 +7567,11 @@
       <c r="H7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -7503,8 +7596,11 @@
       <c r="H8">
         <v>56</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -7529,8 +7625,11 @@
       <c r="H9">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -7555,8 +7654,11 @@
       <c r="H10">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -7581,8 +7683,11 @@
       <c r="H11">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -7607,8 +7712,11 @@
       <c r="H12">
         <v>-16</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -7633,8 +7741,11 @@
       <c r="H13">
         <v>-17</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -7659,8 +7770,11 @@
       <c r="H14">
         <v>-20</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -7685,8 +7799,11 @@
       <c r="H15">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -7711,8 +7828,11 @@
       <c r="H16">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -7737,8 +7857,11 @@
       <c r="H17">
         <v>-15</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -7763,8 +7886,11 @@
       <c r="H18">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -7789,8 +7915,11 @@
       <c r="H19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -7815,8 +7944,11 @@
       <c r="H20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -7841,8 +7973,11 @@
       <c r="H21">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -7867,8 +8002,11 @@
       <c r="H22">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -7892,6 +8030,9 @@
       </c>
       <c r="H23">
         <v>-18</v>
+      </c>
+      <c r="I23">
+        <v>-17</v>
       </c>
     </row>
   </sheetData>
@@ -7904,13 +8045,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7935,8 +8076,11 @@
       <c r="I1">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7964,8 +8108,11 @@
       <c r="I2">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7993,8 +8140,11 @@
       <c r="I3">
         <v>27.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8022,8 +8172,11 @@
       <c r="I4">
         <v>25.9</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8051,8 +8204,11 @@
       <c r="I5">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8080,8 +8236,11 @@
       <c r="I6">
         <v>25.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8109,8 +8268,11 @@
       <c r="I7">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7">
+        <v>23.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8138,8 +8300,11 @@
       <c r="I8">
         <v>24.2</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8167,8 +8332,11 @@
       <c r="I9">
         <v>12.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8196,8 +8364,11 @@
       <c r="I10">
         <v>12.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8225,8 +8396,11 @@
       <c r="I11">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8254,8 +8428,11 @@
       <c r="I12">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8283,8 +8460,11 @@
       <c r="I13">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8312,8 +8492,11 @@
       <c r="I14">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8341,8 +8524,11 @@
       <c r="I15">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8370,8 +8556,11 @@
       <c r="I16">
         <v>10.3</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8399,8 +8588,11 @@
       <c r="I17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8428,8 +8620,11 @@
       <c r="I18">
         <v>8.6999999999999993</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8457,8 +8652,11 @@
       <c r="I19">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8486,8 +8684,11 @@
       <c r="I20">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8515,8 +8716,11 @@
       <c r="I21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8544,8 +8748,11 @@
       <c r="I22">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8572,6 +8779,9 @@
       </c>
       <c r="I23">
         <v>3.3</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -9133,7 +9343,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9260,6 +9470,20 @@
       </c>
       <c r="D9">
         <v>106.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>81</v>
+      </c>
+      <c r="B10">
+        <v>2026</v>
+      </c>
+      <c r="C10">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>108.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912F3697-E44E-491F-8D8F-3790A1056677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D359F21-70BA-4B78-B72C-0C0593F22969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10418" yWindow="0" windowWidth="11265" windowHeight="12863" tabRatio="864" firstSheet="12" activeTab="12" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="11070" yWindow="0" windowWidth="10613" windowHeight="12863" tabRatio="864" firstSheet="12" activeTab="13" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -6607,13 +6607,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6638,8 +6638,11 @@
       <c r="I1">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6667,8 +6670,11 @@
       <c r="I2">
         <v>85</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6696,8 +6702,11 @@
       <c r="I3">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6725,8 +6734,11 @@
       <c r="I4">
         <v>68</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6754,8 +6766,11 @@
       <c r="I5">
         <v>56</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6783,8 +6798,11 @@
       <c r="I6">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6812,8 +6830,11 @@
       <c r="I7">
         <v>-6</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6841,8 +6862,11 @@
       <c r="I8">
         <v>-11</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6870,8 +6894,11 @@
       <c r="I9">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6899,8 +6926,11 @@
       <c r="I10">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -6928,8 +6958,11 @@
       <c r="I11">
         <v>38</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6956,6 +6989,9 @@
       </c>
       <c r="I12">
         <v>-35</v>
+      </c>
+      <c r="J12">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -6968,13 +7004,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7002,8 +7038,11 @@
       <c r="J1">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7034,8 +7073,11 @@
       <c r="J2">
         <v>31.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7066,8 +7108,11 @@
       <c r="J3">
         <v>30.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -7098,8 +7143,11 @@
       <c r="J4">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>30.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7130,8 +7178,11 @@
       <c r="J5">
         <v>25.7</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7162,8 +7213,11 @@
       <c r="J6">
         <v>17.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7194,8 +7248,11 @@
       <c r="J7">
         <v>14.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -7226,8 +7283,11 @@
       <c r="J8">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7258,8 +7318,11 @@
       <c r="J9">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7290,8 +7353,11 @@
       <c r="J10">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7322,8 +7388,11 @@
       <c r="J11">
         <v>11.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7353,6 +7422,9 @@
       </c>
       <c r="J12">
         <v>4.8</v>
+      </c>
+      <c r="K12">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>
@@ -7365,13 +7437,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7396,8 +7468,11 @@
       <c r="I1">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7425,8 +7500,11 @@
       <c r="I2">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7454,8 +7532,11 @@
       <c r="I3">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7483,8 +7564,11 @@
       <c r="I4">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:9">
+      <c r="J4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7512,8 +7596,11 @@
       <c r="I5">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7541,8 +7628,11 @@
       <c r="I6">
         <v>35</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -7570,8 +7660,11 @@
       <c r="I7">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -7599,8 +7692,11 @@
       <c r="I8">
         <v>27</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -7628,8 +7724,11 @@
       <c r="I9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -7657,8 +7756,11 @@
       <c r="I10">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -7686,8 +7788,11 @@
       <c r="I11">
         <v>-17</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -7715,8 +7820,11 @@
       <c r="I12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -7744,8 +7852,11 @@
       <c r="I13">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -7773,8 +7884,11 @@
       <c r="I14">
         <v>-17</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -7802,8 +7916,11 @@
       <c r="I15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -7831,8 +7948,11 @@
       <c r="I16">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -7860,8 +7980,11 @@
       <c r="I17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -7889,8 +8012,11 @@
       <c r="I18">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -7918,8 +8044,11 @@
       <c r="I19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -7947,8 +8076,11 @@
       <c r="I20">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -7976,8 +8108,11 @@
       <c r="I21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8005,8 +8140,11 @@
       <c r="I22">
         <v>-17</v>
       </c>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8033,6 +8171,9 @@
       </c>
       <c r="I23">
         <v>-17</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8045,13 +8186,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="B1">
         <v>1</v>
       </c>
@@ -8079,8 +8220,11 @@
       <c r="J1">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8111,8 +8255,11 @@
       <c r="J2">
         <v>27.9</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8143,8 +8290,11 @@
       <c r="J3">
         <v>27.8</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8175,8 +8325,11 @@
       <c r="J4">
         <v>25.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8207,8 +8360,11 @@
       <c r="J5">
         <v>24.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8239,8 +8395,11 @@
       <c r="J6">
         <v>25.4</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8271,8 +8430,11 @@
       <c r="J7">
         <v>23.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8303,8 +8465,11 @@
       <c r="J8">
         <v>24.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8335,8 +8500,11 @@
       <c r="J9">
         <v>12.7</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8367,8 +8535,11 @@
       <c r="J10">
         <v>12.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8399,8 +8570,11 @@
       <c r="J11">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8431,8 +8605,11 @@
       <c r="J12">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8463,8 +8640,11 @@
       <c r="J13">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8495,8 +8675,11 @@
       <c r="J14">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8527,8 +8710,11 @@
       <c r="J15">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8559,8 +8745,11 @@
       <c r="J16">
         <v>10.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8591,8 +8780,11 @@
       <c r="J17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8623,8 +8815,11 @@
       <c r="J18">
         <v>8.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8655,8 +8850,11 @@
       <c r="J19">
         <v>6</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8687,8 +8885,11 @@
       <c r="J20">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8719,8 +8920,11 @@
       <c r="J21">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8751,8 +8955,11 @@
       <c r="J22">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8781,6 +8988,9 @@
         <v>3.3</v>
       </c>
       <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
         <v>3</v>
       </c>
     </row>
@@ -9343,7 +9553,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9484,6 +9694,20 @@
       </c>
       <c r="D10">
         <v>108.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>82</v>
+      </c>
+      <c r="B11">
+        <v>2026</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>110.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D359F21-70BA-4B78-B72C-0C0593F22969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5B5ECF-C6AE-43E0-8E52-FE9AC9E4FCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11070" yWindow="0" windowWidth="10613" windowHeight="12863" tabRatio="864" firstSheet="12" activeTab="13" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="9" activeTab="12" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -723,9 +723,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -796,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -867,7 +867,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -938,7 +938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1517,9 +1517,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1596,7 +1596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1858,7 +1858,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.4">
+    <row r="23" spans="1:25" ht="15.75">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.4">
+    <row r="24" spans="1:25" ht="15.75">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.4">
+    <row r="25" spans="1:25" ht="15.75">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="15.4">
+    <row r="26" spans="1:25" ht="15.75">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -3290,9 +3290,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -3369,7 +3369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4949,9 +4949,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -6607,13 +6607,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6641,8 +6641,11 @@
       <c r="J1">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6673,8 +6676,11 @@
       <c r="J2">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6705,8 +6711,11 @@
       <c r="J3">
         <v>72</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6737,8 +6746,11 @@
       <c r="J4">
         <v>32</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6769,8 +6781,11 @@
       <c r="J5">
         <v>92</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6801,8 +6816,11 @@
       <c r="J6">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6833,8 +6851,11 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6865,8 +6886,11 @@
       <c r="J8">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6897,8 +6921,11 @@
       <c r="J9">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6929,8 +6956,11 @@
       <c r="J10">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -6961,8 +6991,11 @@
       <c r="J11">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6992,6 +7025,9 @@
       </c>
       <c r="J12">
         <v>13</v>
+      </c>
+      <c r="K12">
+        <v>-17</v>
       </c>
     </row>
   </sheetData>
@@ -7004,13 +7040,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.86328125" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7041,8 +7077,11 @@
       <c r="K1">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7076,8 +7115,11 @@
       <c r="K2">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7111,8 +7153,11 @@
       <c r="K3">
         <v>30.4</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -7146,8 +7191,11 @@
       <c r="K4">
         <v>30.3</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7181,8 +7229,11 @@
       <c r="K5">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7216,8 +7267,11 @@
       <c r="K6">
         <v>17.899999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7251,8 +7305,11 @@
       <c r="K7">
         <v>13.8</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -7286,8 +7343,11 @@
       <c r="K8">
         <v>5.7</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7321,8 +7381,11 @@
       <c r="K9">
         <v>10.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7356,8 +7419,11 @@
       <c r="K10">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7391,8 +7457,11 @@
       <c r="K11">
         <v>11.7</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7425,6 +7494,9 @@
       </c>
       <c r="K12">
         <v>4.2</v>
+      </c>
+      <c r="L12">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
@@ -7437,13 +7509,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7471,8 +7543,11 @@
       <c r="J1">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7503,8 +7578,11 @@
       <c r="J2">
         <v>-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7535,8 +7613,11 @@
       <c r="J3">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="K3">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7567,8 +7648,11 @@
       <c r="J4">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7599,8 +7683,11 @@
       <c r="J5">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7631,8 +7718,11 @@
       <c r="J6">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -7663,8 +7753,11 @@
       <c r="J7">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -7695,8 +7788,11 @@
       <c r="J8">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -7727,8 +7823,11 @@
       <c r="J9">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -7759,8 +7858,11 @@
       <c r="J10">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -7791,8 +7893,11 @@
       <c r="J11">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -7823,8 +7928,11 @@
       <c r="J12">
         <v>-13</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -7855,8 +7963,11 @@
       <c r="J13">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -7887,8 +7998,11 @@
       <c r="J14">
         <v>7</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -7919,8 +8033,11 @@
       <c r="J15">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -7951,8 +8068,11 @@
       <c r="J16">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -7983,8 +8103,11 @@
       <c r="J17">
         <v>-7</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8015,8 +8138,11 @@
       <c r="J18">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8047,8 +8173,11 @@
       <c r="J19">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8079,8 +8208,11 @@
       <c r="J20">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8111,8 +8243,11 @@
       <c r="J21">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8143,8 +8278,11 @@
       <c r="J22">
         <v>7</v>
       </c>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22">
+        <v>-17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8174,6 +8312,9 @@
       </c>
       <c r="J23">
         <v>5</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8186,13 +8327,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="B1">
         <v>1</v>
       </c>
@@ -8223,8 +8364,11 @@
       <c r="K1">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8258,8 +8402,11 @@
       <c r="K2">
         <v>27.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8293,8 +8440,11 @@
       <c r="K3">
         <v>28.1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8328,8 +8478,11 @@
       <c r="K4">
         <v>25.7</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8363,8 +8516,11 @@
       <c r="K5">
         <v>24.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8398,8 +8554,11 @@
       <c r="K6">
         <v>25.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8433,8 +8592,11 @@
       <c r="K7">
         <v>23.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8468,8 +8630,11 @@
       <c r="K8">
         <v>24.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8503,8 +8668,11 @@
       <c r="K9">
         <v>13.3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8538,8 +8706,11 @@
       <c r="K10">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8573,8 +8744,11 @@
       <c r="K11">
         <v>10.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8608,8 +8782,11 @@
       <c r="K12">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8643,8 +8820,11 @@
       <c r="K13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8678,8 +8858,11 @@
       <c r="K14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8713,8 +8896,11 @@
       <c r="K15">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8748,8 +8934,11 @@
       <c r="K16">
         <v>10.3</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8783,8 +8972,11 @@
       <c r="K17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8818,8 +9010,11 @@
       <c r="K18">
         <v>9.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8853,8 +9048,11 @@
       <c r="K19">
         <v>6.6</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8888,8 +9086,11 @@
       <c r="K20">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8923,8 +9124,11 @@
       <c r="K21">
         <v>10.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8958,8 +9162,11 @@
       <c r="K22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8991,6 +9198,9 @@
         <v>3</v>
       </c>
       <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
         <v>3</v>
       </c>
     </row>
@@ -9005,9 +9215,9 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -9553,8 +9763,8 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -9708,6 +9918,20 @@
       </c>
       <c r="D11">
         <v>110.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>83</v>
+      </c>
+      <c r="B12">
+        <v>2026</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>113.3</v>
       </c>
     </row>
   </sheetData>
@@ -9721,9 +9945,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -9800,7 +10024,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9877,7 +10101,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -9954,7 +10178,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10031,7 +10255,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -10108,7 +10332,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -10185,7 +10409,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -10262,7 +10486,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -10339,7 +10563,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -10416,7 +10640,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -10493,7 +10717,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -10581,7 +10805,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -10657,7 +10881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -10734,7 +10958,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -10811,7 +11035,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -10888,7 +11112,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -10965,7 +11189,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -11042,7 +11266,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -11119,7 +11343,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -11196,7 +11420,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -11273,7 +11497,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -11350,7 +11574,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -11438,7 +11662,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
       <c r="B1">
@@ -11508,7 +11732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -11579,7 +11803,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -11650,7 +11874,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -11721,7 +11945,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -11792,7 +12016,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -11863,7 +12087,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -11934,7 +12158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -12005,7 +12229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -12076,7 +12300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -12147,7 +12371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -12229,7 +12453,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -12305,7 +12529,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -12382,7 +12606,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -12459,7 +12683,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12536,7 +12760,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -12613,7 +12837,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -12690,7 +12914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -12767,7 +12991,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -12844,7 +13068,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -12921,7 +13145,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -12998,7 +13222,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -13086,7 +13310,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -13943,9 +14167,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1">
@@ -14016,7 +14240,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -14087,7 +14311,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -14158,7 +14382,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -14229,7 +14453,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -14300,7 +14524,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -14371,7 +14595,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -14442,7 +14666,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -14513,7 +14737,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -14584,7 +14808,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -14655,7 +14879,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -14726,7 +14950,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.4">
+    <row r="12" spans="1:23" ht="15.75">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -14797,7 +15021,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.4">
+    <row r="13" spans="1:23" ht="15.75">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -14868,7 +15092,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.4">
+    <row r="14" spans="1:23" ht="15.75">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -14939,7 +15163,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.4">
+    <row r="15" spans="1:23" ht="15.75">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -15010,7 +15234,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.4">
+    <row r="16" spans="1:23" ht="15.75">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -15081,7 +15305,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.4">
+    <row r="17" spans="1:23" ht="15.75">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -15152,7 +15376,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.4">
+    <row r="18" spans="1:23" ht="15.75">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -15223,7 +15447,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.4">
+    <row r="19" spans="1:23" ht="15.75">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -15260,7 +15484,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" ht="15.4">
+    <row r="20" spans="1:23" ht="15.75">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -15301,7 +15525,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.4">
+    <row r="21" spans="1:23" ht="15.75">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -15348,7 +15572,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.4">
+    <row r="22" spans="1:23" ht="15.75">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -15419,7 +15643,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.4">
+    <row r="23" spans="1:23" ht="15.75">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -15501,9 +15725,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -15574,7 +15798,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.4">
+    <row r="2" spans="1:23" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -15645,7 +15869,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.4">
+    <row r="3" spans="1:23" ht="15.75">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -15716,7 +15940,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.4">
+    <row r="4" spans="1:23" ht="15.75">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -15787,7 +16011,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.4">
+    <row r="5" spans="1:23" ht="15.75">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -15858,7 +16082,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.4">
+    <row r="6" spans="1:23" ht="15.75">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -15929,7 +16153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.4">
+    <row r="7" spans="1:23" ht="15.75">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -16000,7 +16224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.4">
+    <row r="8" spans="1:23" ht="15.75">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -16071,7 +16295,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.4">
+    <row r="9" spans="1:23" ht="15.75">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -16142,7 +16366,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.4">
+    <row r="10" spans="1:23" ht="15.75">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -16213,7 +16437,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.4">
+    <row r="11" spans="1:23" ht="15.75">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -16284,7 +16508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.4">
+    <row r="12" spans="1:23" ht="15.75">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -16355,7 +16579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.4">
+    <row r="13" spans="1:23" ht="15.75">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -16426,7 +16650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.4">
+    <row r="14" spans="1:23" ht="15.75">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -16467,7 +16691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.4">
+    <row r="15" spans="1:23" ht="15.75">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -16538,7 +16762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.4">
+    <row r="16" spans="1:23" ht="15.75">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -16609,7 +16833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.4">
+    <row r="17" spans="1:23" ht="15.75">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -16680,7 +16904,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.4">
+    <row r="18" spans="1:23" ht="15.75">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -16717,7 +16941,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="15.4">
+    <row r="19" spans="1:23" ht="15.75">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -16788,7 +17012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.4">
+    <row r="20" spans="1:23" ht="15.75">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -16859,7 +17083,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.4">
+    <row r="21" spans="1:23" ht="15.75">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -16906,7 +17130,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.4">
+    <row r="22" spans="1:23" ht="15.75">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -16977,7 +17201,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.4">
+    <row r="23" spans="1:23" ht="15.75">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -17059,9 +17283,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -17138,7 +17362,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.4">
+    <row r="2" spans="1:25" ht="15.75">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -17215,7 +17439,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.4">
+    <row r="3" spans="1:25" ht="15.75">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -17292,7 +17516,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.4">
+    <row r="4" spans="1:25" ht="15.75">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -17369,7 +17593,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.4">
+    <row r="5" spans="1:25" ht="15.75">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -17446,7 +17670,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.4">
+    <row r="6" spans="1:25" ht="15.75">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -17523,7 +17747,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.4">
+    <row r="7" spans="1:25" ht="15.75">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -17600,7 +17824,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.4">
+    <row r="8" spans="1:25" ht="15.75">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -17675,7 +17899,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.4">
+    <row r="9" spans="1:25" ht="15.75">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -17752,7 +17976,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.4">
+    <row r="10" spans="1:25" ht="15.75">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -17829,7 +18053,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.4">
+    <row r="11" spans="1:25" ht="15.75">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -17862,7 +18086,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.4">
+    <row r="12" spans="1:25" ht="15.75">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -17893,7 +18117,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.4">
+    <row r="13" spans="1:25" ht="15.75">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -17970,7 +18194,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.4">
+    <row r="14" spans="1:25" ht="15.75">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -18001,7 +18225,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.4">
+    <row r="15" spans="1:25" ht="15.75">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -18042,7 +18266,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.4">
+    <row r="16" spans="1:25" ht="15.75">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -18117,7 +18341,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.4">
+    <row r="17" spans="1:25" ht="15.75">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -18190,7 +18414,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.4">
+    <row r="18" spans="1:25" ht="15.75">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -18255,7 +18479,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.4">
+    <row r="19" spans="1:25" ht="15.75">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -18332,7 +18556,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.4">
+    <row r="20" spans="1:25" ht="15.75">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -18409,7 +18633,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.4">
+    <row r="21" spans="1:25" ht="15.75">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -18486,7 +18710,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.4">
+    <row r="22" spans="1:25" ht="15.75">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -18563,7 +18787,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.4">
+    <row r="23" spans="1:25" ht="15.75">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -18640,7 +18864,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.4">
+    <row r="24" spans="1:25" ht="15.75">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -18717,7 +18941,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.4">
+    <row r="25" spans="1:25" ht="15.75">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -18764,7 +18988,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.4">
+    <row r="26" spans="1:25" ht="15.75">
       <c r="A26" t="s">
         <v>41</v>
       </c>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5B5ECF-C6AE-43E0-8E52-FE9AC9E4FCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F901374D-A862-4917-8FA8-774038935C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="9" activeTab="12" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="28680" yWindow="-225" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="14" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="WEEKLY BUDGET" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6607,13 +6608,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6644,8 +6645,11 @@
       <c r="K1">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6679,8 +6683,11 @@
       <c r="K2">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6714,8 +6721,11 @@
       <c r="K3">
         <v>71</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6749,8 +6759,11 @@
       <c r="K4">
         <v>79</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6784,8 +6797,11 @@
       <c r="K5">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6819,8 +6835,11 @@
       <c r="K6">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6854,8 +6873,11 @@
       <c r="K7">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6889,8 +6911,11 @@
       <c r="K8">
         <v>-13</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6924,8 +6949,11 @@
       <c r="K9">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6959,8 +6987,11 @@
       <c r="K10">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -6994,8 +7025,11 @@
       <c r="K11">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7028,6 +7062,9 @@
       </c>
       <c r="K12">
         <v>-17</v>
+      </c>
+      <c r="L12">
+        <v>-37</v>
       </c>
     </row>
   </sheetData>
@@ -7509,13 +7546,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7546,8 +7583,11 @@
       <c r="K1">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7581,8 +7621,11 @@
       <c r="K2">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7616,8 +7659,11 @@
       <c r="K3">
         <v>-11</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7651,8 +7697,11 @@
       <c r="K4">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7686,8 +7735,11 @@
       <c r="K5">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7721,8 +7773,11 @@
       <c r="K6">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -7756,8 +7811,11 @@
       <c r="K7">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -7791,8 +7849,11 @@
       <c r="K8">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -7826,8 +7887,11 @@
       <c r="K9">
         <v>38</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -7861,8 +7925,11 @@
       <c r="K10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -7896,8 +7963,11 @@
       <c r="K11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -7931,8 +8001,11 @@
       <c r="K12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -7966,8 +8039,11 @@
       <c r="K13">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8001,8 +8077,11 @@
       <c r="K14">
         <v>-19</v>
       </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="L14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8036,8 +8115,11 @@
       <c r="K15">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8071,8 +8153,11 @@
       <c r="K16">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8106,8 +8191,11 @@
       <c r="K17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8141,8 +8229,11 @@
       <c r="K18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8176,8 +8267,11 @@
       <c r="K19">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8211,8 +8305,11 @@
       <c r="K20">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8246,8 +8343,11 @@
       <c r="K21">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8281,8 +8381,11 @@
       <c r="K22">
         <v>-17</v>
       </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8315,6 +8418,9 @@
       </c>
       <c r="K23">
         <v>1</v>
+      </c>
+      <c r="L23">
+        <v>-16</v>
       </c>
     </row>
   </sheetData>
@@ -8327,13 +8433,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1">
         <v>1</v>
       </c>
@@ -8367,8 +8473,11 @@
       <c r="L1">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8405,8 +8514,11 @@
       <c r="L2">
         <v>27.7</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8443,8 +8555,11 @@
       <c r="L3">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8481,8 +8596,11 @@
       <c r="L4">
         <v>25.8</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8519,8 +8637,11 @@
       <c r="L5">
         <v>24.7</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8557,8 +8678,11 @@
       <c r="L6">
         <v>25.6</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8595,8 +8719,11 @@
       <c r="L7">
         <v>23.6</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8633,8 +8760,11 @@
       <c r="L8">
         <v>24.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8671,8 +8801,11 @@
       <c r="L9">
         <v>13.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8709,8 +8842,11 @@
       <c r="L10">
         <v>12.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8747,8 +8883,11 @@
       <c r="L11">
         <v>10.199999999999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8785,8 +8924,11 @@
       <c r="L12">
         <v>6.4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8823,8 +8965,11 @@
       <c r="L13">
         <v>5.6</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8861,8 +9006,11 @@
       <c r="L14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8899,8 +9047,11 @@
       <c r="L15">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8937,8 +9088,11 @@
       <c r="L16">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8975,8 +9129,11 @@
       <c r="L17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -9013,8 +9170,11 @@
       <c r="L18">
         <v>9.6999999999999993</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -9051,8 +9211,11 @@
       <c r="L19">
         <v>7.2</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -9089,8 +9252,11 @@
       <c r="L20">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -9127,8 +9293,11 @@
       <c r="L21">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -9165,8 +9334,11 @@
       <c r="L22">
         <v>4.4000000000000004</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -9201,6 +9373,9 @@
         <v>3</v>
       </c>
       <c r="L23">
+        <v>3</v>
+      </c>
+      <c r="M23">
         <v>3</v>
       </c>
     </row>
@@ -9763,7 +9938,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -9932,6 +10107,20 @@
       </c>
       <c r="D12">
         <v>113.3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>84</v>
+      </c>
+      <c r="B13">
+        <v>2026</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
+      <c r="D13">
+        <v>115.6</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F901374D-A862-4917-8FA8-774038935C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C0FAC-7FCC-4E78-93F7-ECDC9BB6EBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-225" windowWidth="29040" windowHeight="15720" tabRatio="864" firstSheet="14" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="33180" yWindow="1830" windowWidth="21600" windowHeight="11055" tabRatio="864" firstSheet="8" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,6 @@
     <sheet name="WEEKLY BUDGET" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="91">
   <si>
     <t>Red Bull Racing</t>
   </si>
@@ -6608,13 +6607,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6648,8 +6647,11 @@
       <c r="L1">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6686,8 +6688,11 @@
       <c r="L2">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6724,8 +6729,11 @@
       <c r="L3">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6762,8 +6770,11 @@
       <c r="L4">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6800,8 +6811,11 @@
       <c r="L5">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6838,8 +6852,11 @@
       <c r="L6">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6876,8 +6893,11 @@
       <c r="L7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6914,8 +6934,11 @@
       <c r="L8">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6952,8 +6975,11 @@
       <c r="L9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -6990,8 +7016,11 @@
       <c r="L10">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7028,8 +7057,11 @@
       <c r="L11">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7065,6 +7097,9 @@
       </c>
       <c r="L12">
         <v>-37</v>
+      </c>
+      <c r="M12">
+        <v>-9</v>
       </c>
     </row>
   </sheetData>
@@ -7077,13 +7112,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7117,8 +7152,14 @@
       <c r="L1">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1">
+        <v>14</v>
+      </c>
+      <c r="N1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7155,8 +7196,14 @@
       <c r="L2">
         <v>32.299999999999997</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2">
+        <v>32.6</v>
+      </c>
+      <c r="N2">
+        <v>32.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7193,8 +7240,14 @@
       <c r="L3">
         <v>30.7</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3">
+        <v>31</v>
+      </c>
+      <c r="N3">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -7231,8 +7284,14 @@
       <c r="L4">
         <v>30.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4">
+        <v>30.9</v>
+      </c>
+      <c r="N4">
+        <v>31.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7269,8 +7328,14 @@
       <c r="L5">
         <v>26.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>26.6</v>
+      </c>
+      <c r="N5">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7307,8 +7372,14 @@
       <c r="L6">
         <v>18.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6">
+        <v>18.8</v>
+      </c>
+      <c r="N6">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7345,8 +7416,14 @@
       <c r="L7">
         <v>13.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7">
+        <v>13</v>
+      </c>
+      <c r="N7">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -7383,8 +7460,14 @@
       <c r="L8">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8">
+        <v>5.7</v>
+      </c>
+      <c r="N8">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7421,8 +7504,14 @@
       <c r="L9">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="M9">
+        <v>12</v>
+      </c>
+      <c r="N9">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7459,8 +7548,14 @@
       <c r="L10">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10">
+        <v>6.8</v>
+      </c>
+      <c r="N10">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7497,8 +7592,14 @@
       <c r="L11">
         <v>12.3</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11">
+        <v>12.9</v>
+      </c>
+      <c r="N11">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7534,6 +7635,12 @@
       </c>
       <c r="L12">
         <v>3.6</v>
+      </c>
+      <c r="M12">
+        <v>3</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7546,13 +7653,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7586,8 +7693,11 @@
       <c r="L1">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7624,8 +7734,11 @@
       <c r="L2">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="M2">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7662,8 +7775,11 @@
       <c r="L3">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="M3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7700,8 +7816,11 @@
       <c r="L4">
         <v>37</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="M4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7738,8 +7857,11 @@
       <c r="L5">
         <v>-11</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="M5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7776,8 +7898,11 @@
       <c r="L6">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="M6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -7814,8 +7939,11 @@
       <c r="L7">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="M7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -7852,8 +7980,11 @@
       <c r="L8">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="M8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -7891,7 +8022,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -7928,8 +8059,11 @@
       <c r="L10">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="M10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -7966,8 +8100,11 @@
       <c r="L11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="M11">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8004,8 +8141,11 @@
       <c r="L12">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12">
+      <c r="M12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8042,8 +8182,11 @@
       <c r="L13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="M13">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8080,8 +8223,11 @@
       <c r="L14">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="M14">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8118,8 +8264,11 @@
       <c r="L15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="M15">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8156,8 +8305,11 @@
       <c r="L16">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8194,8 +8346,11 @@
       <c r="L17">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8232,8 +8387,11 @@
       <c r="L18">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8270,8 +8428,11 @@
       <c r="L19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8308,8 +8469,11 @@
       <c r="L20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8346,8 +8510,11 @@
       <c r="L21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8384,8 +8551,11 @@
       <c r="L22">
         <v>-20</v>
       </c>
-    </row>
-    <row r="23" spans="1:12">
+      <c r="M22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8421,6 +8591,17 @@
       </c>
       <c r="L23">
         <v>-16</v>
+      </c>
+      <c r="M23">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="M24">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8433,13 +8614,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="B1">
         <v>1</v>
       </c>
@@ -8476,8 +8657,11 @@
       <c r="M1">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8517,8 +8701,11 @@
       <c r="M2">
         <v>27.6</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8558,8 +8745,11 @@
       <c r="M3">
         <v>27.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8599,8 +8789,11 @@
       <c r="M4">
         <v>26.1</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8640,8 +8833,11 @@
       <c r="M5">
         <v>24.4</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8681,8 +8877,11 @@
       <c r="M6">
         <v>25.7</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8722,8 +8921,11 @@
       <c r="M7">
         <v>23.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8763,8 +8965,11 @@
       <c r="M8">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8801,11 +9006,8 @@
       <c r="L9">
         <v>13.9</v>
       </c>
-      <c r="M9">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8845,8 +9047,11 @@
       <c r="M10">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8886,8 +9091,11 @@
       <c r="M11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8927,8 +9135,11 @@
       <c r="M12">
         <v>5.8</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8968,8 +9179,11 @@
       <c r="M13">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -9009,8 +9223,11 @@
       <c r="M14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -9050,8 +9267,11 @@
       <c r="M15">
         <v>7.6</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -9091,8 +9311,11 @@
       <c r="M16">
         <v>10.7</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -9132,8 +9355,11 @@
       <c r="M17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -9171,10 +9397,13 @@
         <v>9.6999999999999993</v>
       </c>
       <c r="M18">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>14.5</v>
+      </c>
+      <c r="N18">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -9214,8 +9443,11 @@
       <c r="M19">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -9255,8 +9487,11 @@
       <c r="M20">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -9296,8 +9531,11 @@
       <c r="M21">
         <v>11.2</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -9337,8 +9575,11 @@
       <c r="M22">
         <v>3.8</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -9377,6 +9618,20 @@
       </c>
       <c r="M23">
         <v>3</v>
+      </c>
+      <c r="N23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="M24">
+        <v>10.3</v>
+      </c>
+      <c r="N24">
+        <v>10.7</v>
       </c>
     </row>
   </sheetData>
@@ -9938,7 +10193,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10121,6 +10376,20 @@
       </c>
       <c r="D13">
         <v>115.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>85</v>
+      </c>
+      <c r="B14">
+        <v>2026</v>
+      </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>116.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jackg\code\F1Fantasy\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{082C0FAC-7FCC-4E78-93F7-ECDC9BB6EBDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379090C6-7BB2-4D78-B44C-0A43B686B981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33180" yWindow="1830" windowWidth="21600" windowHeight="11055" tabRatio="864" firstSheet="8" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" tabRatio="864" firstSheet="14" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
@@ -723,9 +723,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -796,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -867,7 +867,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -938,7 +938,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>14.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -1222,7 +1222,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1364,7 +1364,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1517,9 +1517,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -1596,7 +1596,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1858,7 +1858,7 @@
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>-18</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2274,7 +2274,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -2305,7 +2305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -3290,9 +3290,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -3369,7 +3369,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -3523,7 +3523,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>21.9</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -4370,7 +4370,7 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -4447,7 +4447,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -4678,7 +4678,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="X19" s="1"/>
       <c r="Y19" s="1"/>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4949,9 +4949,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -6607,13 +6607,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="B1">
         <v>1</v>
       </c>
@@ -6650,8 +6650,11 @@
       <c r="M1">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -6691,8 +6694,11 @@
       <c r="M2">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -6732,8 +6738,11 @@
       <c r="M3">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -6773,8 +6782,11 @@
       <c r="M4">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6814,8 +6826,11 @@
       <c r="M5">
         <v>74</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -6855,8 +6870,11 @@
       <c r="M6">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6896,8 +6914,11 @@
       <c r="M7">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -6937,8 +6958,11 @@
       <c r="M8">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -6978,8 +7002,11 @@
       <c r="M9">
         <v>-20</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7019,8 +7046,11 @@
       <c r="M10">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7060,8 +7090,11 @@
       <c r="M11">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7100,6 +7133,9 @@
       </c>
       <c r="M12">
         <v>-9</v>
+      </c>
+      <c r="N12">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -7112,13 +7148,13 @@
   <sheetPr>
     <tabColor theme="5"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7158,8 +7194,11 @@
       <c r="N1">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -7202,8 +7241,11 @@
       <c r="N2">
         <v>32.9</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>33.200000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -7246,8 +7288,11 @@
       <c r="N3">
         <v>31.3</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -7290,8 +7335,11 @@
       <c r="N4">
         <v>31.2</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -7334,8 +7382,11 @@
       <c r="N5">
         <v>26.9</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -7378,8 +7429,11 @@
       <c r="N6">
         <v>18.899999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7422,8 +7476,11 @@
       <c r="N7">
         <v>13.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>13.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -7466,8 +7523,11 @@
       <c r="N8">
         <v>6.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -7510,8 +7570,11 @@
       <c r="N9">
         <v>11.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -7554,8 +7617,11 @@
       <c r="N10">
         <v>7.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7598,8 +7664,11 @@
       <c r="N11">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -7640,6 +7709,9 @@
         <v>3</v>
       </c>
       <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="O12">
         <v>3</v>
       </c>
     </row>
@@ -7653,13 +7725,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="B1">
         <v>1</v>
       </c>
@@ -7696,8 +7768,11 @@
       <c r="M1">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -7737,8 +7812,11 @@
       <c r="M2">
         <v>-13</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -7778,8 +7856,11 @@
       <c r="M3">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -7819,8 +7900,11 @@
       <c r="M4">
         <v>57</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -7860,8 +7944,11 @@
       <c r="M5">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -7901,8 +7988,11 @@
       <c r="M6">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -7942,8 +8032,11 @@
       <c r="M7">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -7983,8 +8076,11 @@
       <c r="M8">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -8022,7 +8118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -8062,8 +8158,11 @@
       <c r="M10">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -8103,8 +8202,11 @@
       <c r="M11">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -8144,8 +8246,11 @@
       <c r="M12">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -8185,8 +8290,11 @@
       <c r="M13">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -8226,8 +8334,11 @@
       <c r="M14">
         <v>-10</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -8267,8 +8378,11 @@
       <c r="M15">
         <v>-13</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -8308,8 +8422,11 @@
       <c r="M16">
         <v>-10</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -8349,8 +8466,11 @@
       <c r="M17">
         <v>5</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -8390,8 +8510,11 @@
       <c r="M18">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -8431,8 +8554,11 @@
       <c r="M19">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -8472,8 +8598,11 @@
       <c r="M20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -8513,8 +8642,11 @@
       <c r="M21">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -8554,8 +8686,11 @@
       <c r="M22">
         <v>8</v>
       </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="N22">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -8595,13 +8730,19 @@
       <c r="M23">
         <v>-18</v>
       </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="N23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>36</v>
       </c>
       <c r="M24">
         <v>5</v>
+      </c>
+      <c r="N24">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8614,13 +8755,13 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="B1">
         <v>1</v>
       </c>
@@ -8660,8 +8801,11 @@
       <c r="N1">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -8704,8 +8848,11 @@
       <c r="N2">
         <v>27.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -8748,8 +8895,11 @@
       <c r="N3">
         <v>27.6</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -8792,8 +8942,11 @@
       <c r="N4">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -8836,8 +8989,11 @@
       <c r="N5">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -8880,8 +9036,11 @@
       <c r="N6">
         <v>26</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -8924,8 +9083,11 @@
       <c r="N7">
         <v>24.2</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>24.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -8968,8 +9130,11 @@
       <c r="N8">
         <v>25.1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -9007,7 +9172,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -9050,8 +9215,11 @@
       <c r="N10">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -9094,8 +9262,11 @@
       <c r="N11">
         <v>9.8000000000000007</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -9138,8 +9309,11 @@
       <c r="N12">
         <v>5.2</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -9182,8 +9356,11 @@
       <c r="N13">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -9226,8 +9403,11 @@
       <c r="N14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -9270,8 +9450,11 @@
       <c r="N15">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -9314,8 +9497,11 @@
       <c r="N16">
         <v>10.1</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -9358,8 +9544,11 @@
       <c r="N17">
         <v>3.6</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -9402,8 +9591,11 @@
       <c r="N18">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -9446,8 +9638,11 @@
       <c r="N19">
         <v>8</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -9490,8 +9685,11 @@
       <c r="N20">
         <v>7.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -9534,8 +9732,11 @@
       <c r="N21">
         <v>10.6</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -9578,8 +9779,11 @@
       <c r="N22">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -9622,8 +9826,11 @@
       <c r="N23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -9632,6 +9839,9 @@
       </c>
       <c r="N24">
         <v>10.7</v>
+      </c>
+      <c r="O24">
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>
@@ -9645,9 +9855,9 @@
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -10193,8 +10403,8 @@
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -10390,6 +10600,20 @@
       </c>
       <c r="D14">
         <v>116.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>86</v>
+      </c>
+      <c r="B15">
+        <v>2026</v>
+      </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>118.6</v>
       </c>
     </row>
   </sheetData>
@@ -10403,9 +10627,9 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -10482,7 +10706,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -10559,7 +10783,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -10636,7 +10860,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -10713,7 +10937,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -10790,7 +11014,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -10867,7 +11091,7 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -10944,7 +11168,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -11021,7 +11245,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -11098,7 +11322,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -11175,7 +11399,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -11263,7 +11487,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -11339,7 +11563,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -11416,7 +11640,7 @@
         <v>36.1</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -11493,7 +11717,7 @@
         <v>31.8</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -11570,7 +11794,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -11647,7 +11871,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -11724,7 +11948,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -11801,7 +12025,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -11878,7 +12102,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -11955,7 +12179,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -12032,7 +12256,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -12120,7 +12344,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:23">
       <c r="B1">
@@ -12190,7 +12414,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -12261,7 +12485,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -12332,7 +12556,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -12403,7 +12627,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -12474,7 +12698,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -12545,7 +12769,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -12616,7 +12840,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -12687,7 +12911,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -12758,7 +12982,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -12829,7 +13053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -12911,7 +13135,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -12987,7 +13211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -13064,7 +13288,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -13141,7 +13365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -13218,7 +13442,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -13295,7 +13519,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -13372,7 +13596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -13449,7 +13673,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -13526,7 +13750,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -13603,7 +13827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -13680,7 +13904,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -13768,7 +13992,7 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="A1:Y11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:25">
       <c r="B1">
@@ -14625,9 +14849,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18.75" customHeight="1">
@@ -14698,7 +14922,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -14769,7 +14993,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -14840,7 +15064,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -14911,7 +15135,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -14982,7 +15206,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -15053,7 +15277,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -15124,7 +15348,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -15195,7 +15419,7 @@
         <v>19.8</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -15266,7 +15490,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -15337,7 +15561,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>24</v>
       </c>
@@ -15408,7 +15632,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -15479,7 +15703,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -15550,7 +15774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -15621,7 +15845,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -15692,7 +15916,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -15763,7 +15987,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -15834,7 +16058,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -15905,7 +16129,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -15942,7 +16166,7 @@
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -15983,7 +16207,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -16030,7 +16254,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -16101,7 +16325,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -16183,9 +16407,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -16256,7 +16480,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="15.75">
+    <row r="2" spans="1:23" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -16327,7 +16551,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15.75">
+    <row r="3" spans="1:23" ht="15.4">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -16398,7 +16622,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.75">
+    <row r="4" spans="1:23" ht="15.4">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -16469,7 +16693,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15.75">
+    <row r="5" spans="1:23" ht="15.4">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -16540,7 +16764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15.75">
+    <row r="6" spans="1:23" ht="15.4">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -16611,7 +16835,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15.75">
+    <row r="7" spans="1:23" ht="15.4">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -16682,7 +16906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15.75">
+    <row r="8" spans="1:23" ht="15.4">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -16753,7 +16977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15.75">
+    <row r="9" spans="1:23" ht="15.4">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -16824,7 +17048,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75">
+    <row r="10" spans="1:23" ht="15.4">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -16895,7 +17119,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15.75">
+    <row r="11" spans="1:23" ht="15.4">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -16966,7 +17190,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15.75">
+    <row r="12" spans="1:23" ht="15.4">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -17037,7 +17261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15.75">
+    <row r="13" spans="1:23" ht="15.4">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -17108,7 +17332,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15.75">
+    <row r="14" spans="1:23" ht="15.4">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -17149,7 +17373,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15.75">
+    <row r="15" spans="1:23" ht="15.4">
       <c r="A15" t="s">
         <v>79</v>
       </c>
@@ -17220,7 +17444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15.75">
+    <row r="16" spans="1:23" ht="15.4">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -17291,7 +17515,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="15.75">
+    <row r="17" spans="1:23" ht="15.4">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -17362,7 +17586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75">
+    <row r="18" spans="1:23" ht="15.4">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -17399,7 +17623,7 @@
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
     </row>
-    <row r="19" spans="1:23" ht="15.75">
+    <row r="19" spans="1:23" ht="15.4">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -17470,7 +17694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.75">
+    <row r="20" spans="1:23" ht="15.4">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -17541,7 +17765,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="15.75">
+    <row r="21" spans="1:23" ht="15.4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -17588,7 +17812,7 @@
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
     </row>
-    <row r="22" spans="1:23" ht="15.75">
+    <row r="22" spans="1:23" ht="15.4">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -17659,7 +17883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="15.75">
+    <row r="23" spans="1:23" ht="15.4">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -17741,9 +17965,9 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:Y26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25">
@@ -17820,7 +18044,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="15.75">
+    <row r="2" spans="1:25" ht="15.4">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -17897,7 +18121,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15.75">
+    <row r="3" spans="1:25" ht="15.4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -17974,7 +18198,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15.75">
+    <row r="4" spans="1:25" ht="15.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -18051,7 +18275,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15.75">
+    <row r="5" spans="1:25" ht="15.4">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -18128,7 +18352,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15.75">
+    <row r="6" spans="1:25" ht="15.4">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -18205,7 +18429,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15.75">
+    <row r="7" spans="1:25" ht="15.4">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -18282,7 +18506,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.75">
+    <row r="8" spans="1:25" ht="15.4">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -18357,7 +18581,7 @@
         <v>24.4</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15.75">
+    <row r="9" spans="1:25" ht="15.4">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -18434,7 +18658,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.75">
+    <row r="10" spans="1:25" ht="15.4">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -18511,7 +18735,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="15.75">
+    <row r="11" spans="1:25" ht="15.4">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -18544,7 +18768,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="15.75">
+    <row r="12" spans="1:25" ht="15.4">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -18575,7 +18799,7 @@
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="15.75">
+    <row r="13" spans="1:25" ht="15.4">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -18652,7 +18876,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="15.75">
+    <row r="14" spans="1:25" ht="15.4">
       <c r="A14" t="s">
         <v>38</v>
       </c>
@@ -18683,7 +18907,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="15.75">
+    <row r="15" spans="1:25" ht="15.4">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -18724,7 +18948,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="15.75">
+    <row r="16" spans="1:25" ht="15.4">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -18799,7 +19023,7 @@
       </c>
       <c r="Y16" s="1"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75">
+    <row r="17" spans="1:25" ht="15.4">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -18872,7 +19096,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="15.75">
+    <row r="18" spans="1:25" ht="15.4">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -18937,7 +19161,7 @@
       <c r="X18" s="1"/>
       <c r="Y18" s="1"/>
     </row>
-    <row r="19" spans="1:25" ht="15.75">
+    <row r="19" spans="1:25" ht="15.4">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -19014,7 +19238,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="15.75">
+    <row r="20" spans="1:25" ht="15.4">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -19091,7 +19315,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="15.75">
+    <row r="21" spans="1:25" ht="15.4">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -19168,7 +19392,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75">
+    <row r="22" spans="1:25" ht="15.4">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -19245,7 +19469,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75">
+    <row r="23" spans="1:25" ht="15.4">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -19322,7 +19546,7 @@
         <v>9.6</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75">
+    <row r="24" spans="1:25" ht="15.4">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -19399,7 +19623,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="15.75">
+    <row r="25" spans="1:25" ht="15.4">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -19446,7 +19670,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.75">
+    <row r="26" spans="1:25" ht="15.4">
       <c r="A26" t="s">
         <v>41</v>
       </c>

--- a/data/raw/newHistPointAndPrice.xlsx
+++ b/data/raw/newHistPointAndPrice.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379090C6-7BB2-4D78-B44C-0A43B686B981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" tabRatio="864" firstSheet="14" activeTab="17" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
+    <workbookView xWindow="0" yWindow="368" windowWidth="21600" windowHeight="11054" tabRatio="864" firstSheet="11" activeTab="15" xr2:uid="{2D04FC15-E09F-4251-B381-E10D89E9EC62}"/>
   </bookViews>
   <sheets>
     <sheet name="2023ConstructorPrice" sheetId="1" r:id="rId1"/>
